--- a/SCIE용/excel/30_g4_auto_retrieval_results.xlsx
+++ b/SCIE용/excel/30_g4_auto_retrieval_results.xlsx
@@ -130,7 +130,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>자동 G4 적용</t>
+          <t>G4 적용</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -1224,12 +1224,12 @@
 2. page_179_img_1_0.jpeg | score=1.297 | stage=0.698 | page=1.00; keyword=backdrive,recovery; section=backdrive
 3. page_181_img_0_0.jpeg | score=0.986 | stage=0.614 | page=1.00; keyword=recovery
 4. page_89_img_1_0.jpeg | score=0.899 | stage=0.341 | 
-5. page_177_img_1_0.jpeg | score=0.862 | stage=0.580 | page=1.00
+5. page_177_img_1_0.jpeg | score=0.864 | stage=0.580 | page=1.00
 6. page_125_img_0_0.jpeg | score=0.859 | stage=0.328 | 
 7. page_89_img_0_0.jpeg | score=0.840 | stage=0.337 | 
 8. page_24_img_0_0.jpeg | score=0.725 | stage=0.289 | keyword=emergency
-9. page_169_img_2_0.jpeg | score=0.709 | stage=0.698 | page=1.00; keyword=backdrive,recovery; section=backdrive
-10. page_174_img_1_0.jpeg | score=0.699 | stage=0.580 | page=1.00</t>
+9. page_169_img_2_0.jpeg | score=0.712 | stage=0.698 | page=1.00; keyword=backdrive,recovery; section=backdrive
+10. page_174_img_1_0.jpeg | score=0.701 | stage=0.580 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
 6. page_330_img_0_0.jpeg | score=0.764 | stage=0.236 | 
 7. page_343_img_0_0.jpeg | score=0.745 | stage=0.651 | page=1.00; keyword=account; section=account
 8. page_147_img_0_0.jpeg | score=0.730 | stage=0.293 | 
-9. page_354_img_0_0.jpeg | score=0.680 | stage=0.580 | page=1.00
+9. page_354_img_0_0.jpeg | score=0.682 | stage=0.580 | page=1.00
 10. page_349_img_0_0.jpeg | score=0.647 | stage=0.647 | page=1.00; keyword=lock,setting</t>
         </is>
       </c>
@@ -5707,14 +5707,14 @@
       <c r="P63" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">1. page_196_img_0_0.jpeg | score=1.059 | stage=0.614 | page=1.00; keyword=setting
-2. page_195_img_2_0.jpeg | score=0.958 | stage=0.614 | page=1.00; keyword=setting
-3. page_192_img_0_0.jpeg | score=0.937 | stage=0.614 | page=1.00; keyword=setting
-4. page_190_img_1_0.jpeg | score=0.902 | stage=0.614 | page=1.00; keyword=setting
-5. page_190_img_0_0.jpeg | score=0.874 | stage=0.614 | page=1.00; keyword=setting
+2. page_195_img_2_0.jpeg | score=0.956 | stage=0.614 | page=1.00; keyword=setting
+3. page_192_img_0_0.jpeg | score=0.934 | stage=0.614 | page=1.00; keyword=setting
+4. page_190_img_1_0.jpeg | score=0.900 | stage=0.614 | page=1.00; keyword=setting
+5. page_190_img_0_0.jpeg | score=0.872 | stage=0.614 | page=1.00; keyword=setting
 6. page_220_img_0_0.jpeg | score=0.796 | stage=0.226 | keyword=setting
 7. page_224_img_0_0.jpeg | score=0.771 | stage=0.227 | keyword=setting
-8. page_195_img_0_0.jpeg | score=0.749 | stage=0.614 | page=1.00; keyword=setting
-9. page_376_img_0_0.jpeg | score=0.744 | stage=0.249 | 
+8. page_195_img_0_0.jpeg | score=0.746 | stage=0.614 | page=1.00; keyword=setting
+9. page_376_img_0_0.jpeg | score=0.742 | stage=0.245 | 
 10. page_235_img_1_0.jpeg | score=0.741 | stage=0.225 | keyword=setting</t>
         </is>
       </c>

--- a/SCIE용/excel/30_g4_auto_retrieval_results.xlsx
+++ b/SCIE용/excel/30_g4_auto_retrieval_results.xlsx
@@ -231,24 +231,28 @@
           <t>page_403_img_0_0.jpeg</t>
         </is>
       </c>
-      <c r="N2" s="0"/>
+      <c r="N2" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O2" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_104_img_0_0.jpeg | score=0.716 | stage=0.000 | 
-2. page_116_img_0_0.jpeg | score=0.658 | stage=0.000 | 
-3. page_84_img_0_0.jpeg | score=0.635 | stage=0.000 | 
-4. page_83_img_0_0.jpeg | score=0.553 | stage=0.000 | 
-5. page_174_img_1_0.jpeg | score=0.543 | stage=0.000 | 
-6. page_114_img_0_0.jpeg | score=0.531 | stage=0.000 | 
-7. page_118_img_0_0.jpeg | score=0.484 | stage=0.000 | 
-8. page_115_img_0_0.jpeg | score=0.471 | stage=0.000 | 
-9. page_103_img_0_0.jpeg | score=0.466 | stage=0.000 | 
-10. page_98_img_2_0.jpeg | score=0.466 | stage=0.000 | </t>
+          <t xml:space="preserve">1. page_403_img_0_0.jpeg | score=0.732 | stage=0.000
+2. page_48_img_0_0.jpeg | score=0.696 | stage=0.000
+3. page_116_img_0_0.jpeg | score=0.628 | stage=0.000
+4. page_104_img_0_0.jpeg | score=0.593 | stage=0.000
+5. page_98_img_0_0.jpeg | score=0.591 | stage=0.000
+6. page_98_img_1_0.jpeg | score=0.590 | stage=0.000
+7. page_174_img_1_0.jpeg | score=0.515 | stage=0.000
+8. page_105_img_0_0.jpeg | score=0.514 | stage=0.000
+9. page_402_img_0_0.jpeg | score=0.500 | stage=0.000
+10. page_402_img_1_0.jpeg | score=0.500 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -290,7 +294,7 @@
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>0.0501</t>
+          <t>0.0502</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
@@ -320,7 +324,7 @@
       </c>
       <c r="N3" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O3" s="0" t="inlineStr">
@@ -330,16 +334,16 @@
       </c>
       <c r="P3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_86_img_0_0.jpeg | score=1.264 | stage=0.580 | page=1.00
-2. page_125_img_0_0.jpeg | score=1.127 | stage=0.580 | page=1.00
-3. page_88_img_1_0.jpeg | score=1.112 | stage=0.580 | page=1.00
-4. page_88_img_0_0.jpeg | score=1.098 | stage=0.580 | page=1.00
-5. page_403_img_0_0.jpeg | score=0.990 | stage=0.630 | page=1.00; section=cs-12p
-6. page_120_img_0_0.jpeg | score=0.970 | stage=0.580 | page=1.00
-7. page_121_img_0_0.jpeg | score=0.968 | stage=0.580 | page=1.00
-8. page_402_img_0_0.jpeg | score=0.931 | stage=0.630 | page=1.00; section=cs-12p
-9. page_402_img_1_0.jpeg | score=0.928 | stage=0.630 | page=1.00; section=cs-12p
-10. page_147_img_0_0.jpeg | score=0.891 | stage=0.341 | keyword=controller,safety</t>
+          <t xml:space="preserve">1. page_403_img_0_0.jpeg | score=1.391 | stage=0.633 | page=1.00; section=cs-12p
+2. page_86_img_0_0.jpeg | score=1.359 | stage=0.500 | page=1.00
+3. page_121_img_0_0.jpeg | score=1.346 | stage=0.500 | page=1.00
+4. page_120_img_0_0.jpeg | score=1.091 | stage=0.500 | page=1.00
+5. page_124_img_0_0.jpeg | score=0.958 | stage=0.500 | page=1.00
+6. page_402_img_0_0.jpeg | score=0.940 | stage=0.633 | page=1.00; section=cs-12p
+7. page_125_img_0_0.jpeg | score=0.939 | stage=0.225 | page=0.45
+8. page_402_img_1_0.jpeg | score=0.937 | stage=0.633 | page=1.00; section=cs-12p
+9. page_88_img_1_0.jpeg | score=0.930 | stage=0.500 | page=1.00
+10. page_85_img_0_0.jpeg | score=0.901 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -421,16 +425,16 @@
       </c>
       <c r="P4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_115_img_0_0.jpeg | score=1.347 | stage=0.647 | page=1.00; keyword=m8,20nm
-2. page_84_img_0_0.jpeg | score=1.281 | stage=0.580 | page=1.00
-3. page_123_img_0_0.jpeg | score=1.270 | stage=0.580 | page=1.00
-4. page_116_img_0_0.jpeg | score=1.221 | stage=0.580 | page=1.00
-5. page_88_img_0_0.jpeg | score=1.153 | stage=0.580 | page=1.00
-6. page_88_img_1_0.jpeg | score=1.150 | stage=0.580 | page=1.00
-7. page_114_img_0_0.jpeg | score=1.133 | stage=0.580 | page=1.00
-8. page_118_img_0_0.jpeg | score=1.036 | stage=0.580 | page=1.00
-9. page_86_img_0_0.jpeg | score=1.033 | stage=0.580 | page=1.00
-10. page_85_img_0_0.jpeg | score=1.033 | stage=0.614 | page=1.00; keyword=m8</t>
+          <t xml:space="preserve">1. page_115_img_0_0.jpeg | score=1.383 | stage=0.525 | page=1.00; keyword=m8,20nm
+2. page_84_img_0_0.jpeg | score=1.317 | stage=0.500 | page=1.00
+3. page_116_img_0_0.jpeg | score=1.284 | stage=0.500 | page=1.00
+4. page_85_img_0_0.jpeg | score=1.236 | stage=0.525 | page=1.00; keyword=robot base,base
+5. page_114_img_0_0.jpeg | score=1.183 | stage=0.500 | page=1.00
+6. page_86_img_0_0.jpeg | score=1.164 | stage=0.500 | page=1.00
+7. page_121_img_0_0.jpeg | score=1.042 | stage=0.350 | page=0.70
+8. page_83_img_0_0.jpeg | score=0.908 | stage=0.500 | page=1.00
+9. page_113_img_0_0.jpeg | score=0.905 | stage=0.350 | page=0.70
+10. page_93_img_0_0.jpeg | score=0.858 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -502,7 +506,7 @@
       </c>
       <c r="N5" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O5" s="0" t="inlineStr">
@@ -512,16 +516,16 @@
       </c>
       <c r="P5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_145_img_0_0.jpeg | score=1.315 | stage=0.722 | page=1.00; keyword=safety i,o; section=safety i,o
-2. page_147_img_0_0.jpeg | score=1.310 | stage=0.651 | page=1.00; keyword=o; section=o
-3. page_142_img_0_0.jpeg | score=1.262 | stage=0.651 | page=1.00; keyword=o; section=o
-4. page_142_img_1_0.jpeg | score=1.232 | stage=0.651 | page=1.00; keyword=o; section=o
-5. page_144_img_0_0.jpeg | score=1.131 | stage=0.651 | page=1.00; keyword=o; section=o
-6. page_144_img_1_0.jpeg | score=1.114 | stage=0.651 | page=1.00; keyword=o; section=o
-7. page_143_img_0_0.jpeg | score=1.020 | stage=0.651 | page=1.00; keyword=o; section=o
-8. page_143_img_1_0.jpeg | score=1.016 | stage=0.651 | page=1.00; keyword=o; section=o
-9. page_141_img_1_0.jpeg | score=0.996 | stage=0.651 | page=1.00; keyword=o; section=o
-10. page_148_img_0_0.jpeg | score=0.965 | stage=0.651 | page=1.00; keyword=o; section=o</t>
+          <t xml:space="preserve">1. page_143_img_1_0.jpeg | score=1.502 | stage=0.838 | page=1.00; keyword=safety i,o,tbsft; section=safety i,o,tbsft
+2. page_145_img_0_0.jpeg | score=1.495 | stage=0.738 | page=1.00; keyword=safety i,o,em; section=safety i,o
+3. page_143_img_0_0.jpeg | score=1.493 | stage=0.838 | page=1.00; keyword=safety i,o,tbsft; section=safety i,o,tbsft
+4. page_147_img_0_0.jpeg | score=1.360 | stage=0.738 | page=1.00; keyword=o,em,emergency stop; section=o,emergency stop
+5. page_144_img_0_0.jpeg | score=1.319 | stage=0.725 | page=1.00; keyword=safety i,o; section=safety i,o
+6. page_144_img_1_0.jpeg | score=1.312 | stage=0.725 | page=1.00; keyword=safety i,o; section=safety i,o
+7. page_148_img_0_0.jpeg | score=1.171 | stage=0.612 | page=1.00; keyword=o; section=o
+8. page_142_img_1_0.jpeg | score=1.161 | stage=0.612 | page=1.00; keyword=o; section=o
+9. page_142_img_0_0.jpeg | score=1.153 | stage=0.612 | page=1.00; keyword=o; section=o
+10. page_133_img_0_0.jpeg | score=0.891 | stage=0.113 | keyword=o; section=o</t>
         </is>
       </c>
     </row>
@@ -595,16 +599,16 @@
       </c>
       <c r="P6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_127_img_0_0.jpeg | score=0.855 | stage=0.000 | 
-2. page_94_img_0_0.jpeg | score=0.833 | stage=0.000 | 
-3. page_95_img_0_0.jpeg | score=0.764 | stage=0.000 | 
-4. page_130_img_0_0.jpeg | score=0.752 | stage=0.000 | 
-5. page_137_img_0_0.jpeg | score=0.733 | stage=0.000 | 
-6. page_93_img_0_0.jpeg | score=0.728 | stage=0.000 | 
-7. page_123_img_0_0.jpeg | score=0.691 | stage=0.000 | 
-8. page_136_img_0_0.png | score=0.685 | stage=0.000 | 
-9. page_136_img_1_0.jpeg | score=0.669 | stage=0.000 | 
-10. page_104_img_0_0.jpeg | score=0.668 | stage=0.000 | </t>
+          <t xml:space="preserve">1. page_94_img_0_0.jpeg | score=0.865 | stage=0.000
+2. page_127_img_0_0.jpeg | score=0.851 | stage=0.000
+3. page_336_img_0_0.jpeg | score=0.808 | stage=0.000
+4. page_95_img_0_0.jpeg | score=0.775 | stage=0.000
+5. page_130_img_0_0.jpeg | score=0.753 | stage=0.000
+6. page_132_img_0_0.png | score=0.736 | stage=0.000
+7. page_101_img_0_0.jpeg | score=0.711 | stage=0.000
+8. page_93_img_0_0.jpeg | score=0.706 | stage=0.000
+9. page_137_img_0_0.jpeg | score=0.670 | stage=0.000
+10. page_136_img_0_0.png | score=0.653 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -676,26 +680,26 @@
       </c>
       <c r="N7" s="0" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O7" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_89_img_1_0.jpeg | score=1.279 | stage=0.580 | page=1.00
-2. page_89_img_0_0.jpeg | score=1.220 | stage=0.580 | page=1.00
-3. page_88_img_1_0.jpeg | score=1.131 | stage=0.580 | page=1.00
-4. page_88_img_0_0.jpeg | score=1.112 | stage=0.580 | page=1.00
-5. page_104_img_0_0.jpeg | score=1.078 | stage=0.580 | page=1.00
-6. page_103_img_0_0.jpeg | score=1.028 | stage=0.580 | page=1.00
-7. page_24_img_0_0.jpeg | score=0.965 | stage=0.350 | keyword=emergency stop
-8. page_163_img_0_0.jpeg | score=0.876 | stage=0.328 | 
-9. page_94_img_0_0.jpeg | score=0.851 | stage=0.324 | 
-10. page_163_img_1_0.jpeg | score=0.828 | stage=0.332 | </t>
+          <t xml:space="preserve">1. page_89_img_1_0.jpeg | score=1.329 | stage=0.500 | page=1.00
+2. page_89_img_0_0.jpeg | score=1.304 | stage=0.500 | page=1.00
+3. page_88_img_1_0.jpeg | score=1.165 | stage=0.500 | page=1.00
+4. page_103_img_0_0.jpeg | score=1.149 | stage=0.500 | page=1.00
+5. page_104_img_0_0.jpeg | score=1.096 | stage=0.500 | page=1.00
+6. page_88_img_0_0.jpeg | score=1.017 | stage=0.500 | page=1.00
+7. page_24_img_0_0.jpeg | score=0.881 | stage=0.000
+8. page_220_img_0_0.jpeg | score=0.807 | stage=0.000
+9. page_102_img_0_0.jpeg | score=0.777 | stage=0.500 | page=1.00
+10. page_163_img_0_0.jpeg | score=0.737 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -767,7 +771,7 @@
       </c>
       <c r="N8" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O8" s="0" t="inlineStr">
@@ -777,16 +781,16 @@
       </c>
       <c r="P8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_195_img_2_0.jpeg | score=1.176 | stage=0.580 | page=1.00
-2. page_195_img_0_0.jpeg | score=0.995 | stage=0.580 | page=1.00
-3. page_323_img_0_0.jpeg | score=0.904 | stage=0.229 | 
-4. page_325_img_0_0.jpeg | score=0.870 | stage=0.229 | 
-5. page_323_img_1_0.jpeg | score=0.865 | stage=0.297 | 
-6. page_123_img_0_0.jpeg | score=0.845 | stage=0.324 | 
-7. page_324_img_0_0.jpeg | score=0.824 | stage=0.229 | 
-8. page_88_img_1_0.jpeg | score=0.791 | stage=0.337 | 
-9. page_88_img_0_0.jpeg | score=0.777 | stage=0.328 | 
-10. page_93_img_0_0.jpeg | score=0.750 | stage=0.319 | </t>
+          <t xml:space="preserve">1. page_195_img_0_0.jpeg | score=1.304 | stage=0.500 | page=1.00
+2. page_195_img_2_0.jpeg | score=1.274 | stage=0.500 | page=1.00
+3. page_196_img_0_0.jpeg | score=1.181 | stage=0.500 | page=1.00
+4. page_325_img_0_0.jpeg | score=0.944 | stage=0.213 | keyword=cockpit; section=cockpit
+5. page_101_img_0_0.jpeg | score=0.892 | stage=0.225 | keyword=cockpit,tool flange; section=cockpit
+6. page_324_img_0_0.jpeg | score=0.778 | stage=0.000
+7. page_123_img_0_0.jpeg | score=0.732 | stage=0.000
+8. page_88_img_1_0.jpeg | score=0.678 | stage=0.000
+9. page_103_img_0_0.jpeg | score=0.633 | stage=0.000
+10. page_281_img_1_0.jpeg | score=0.581 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -858,7 +862,7 @@
       </c>
       <c r="N9" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O9" s="0" t="inlineStr">
@@ -868,16 +872,16 @@
       </c>
       <c r="P9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_137_img_0_0.jpeg | score=1.313 | stage=0.664 | page=1.00; keyword=o; section=o
-2. page_139_img_0_0.jpeg | score=1.304 | stage=0.664 | page=1.00; keyword=o; section=o
-3. page_142_img_0_0.jpeg | score=1.292 | stage=0.698 | page=1.00; keyword=o,tbco; section=o
-4. page_138_img_0_0.jpeg | score=1.275 | stage=0.664 | page=1.00; keyword=o; section=o
-5. page_142_img_1_0.jpeg | score=1.264 | stage=0.698 | page=1.00; keyword=o,tbco; section=o
-6. page_144_img_0_0.jpeg | score=1.218 | stage=0.799 | page=1.00; keyword=o,vcc,vio,gnd; section=o
-7. page_144_img_1_0.jpeg | score=1.198 | stage=0.799 | page=1.00; keyword=o,vcc,vio,gnd; section=o
-8. page_133_img_0_0.jpeg | score=1.125 | stage=0.664 | page=1.00; keyword=o; section=o
-9. page_145_img_0_0.jpeg | score=1.109 | stage=0.664 | page=1.00; keyword=o; section=o
-10. page_147_img_0_0.jpeg | score=1.075 | stage=0.664 | page=1.00; keyword=o; section=o</t>
+          <t xml:space="preserve">1. page_140_img_0_0.jpeg | score=1.413 | stage=0.646 | page=1.00; keyword=o; section=o
+2. page_138_img_1_0.jpeg | score=1.395 | stage=0.671 | page=1.00; keyword=o,npn,pnp; section=o
+3. page_138_img_0_0.jpeg | score=1.392 | stage=0.671 | page=1.00; keyword=o,npn,pnp; section=o
+4. page_141_img_1_0.jpeg | score=1.347 | stage=0.683 | page=1.00; keyword=o,vio,gio,tbco; section=o
+5. page_142_img_1_0.jpeg | score=1.308 | stage=0.671 | page=1.00; keyword=o,gio,tbco; section=o
+6. page_142_img_0_0.jpeg | score=1.300 | stage=0.671 | page=1.00; keyword=o,gio,tbco; section=o
+7. page_137_img_0_0.jpeg | score=1.262 | stage=0.525 | page=1.00; keyword=npn,pnp
+8. page_132_img_0_0.png | score=1.241 | stage=0.646 | page=1.00; keyword=o; section=o
+9. page_130_img_0_0.jpeg | score=1.198 | stage=0.508 | page=0.70; keyword=o,pnp; section=o
+10. page_139_img_0_0.jpeg | score=1.196 | stage=0.671 | page=1.00; keyword=o,npn,pnp; section=o</t>
         </is>
       </c>
     </row>
@@ -945,7 +949,7 @@
       </c>
       <c r="N10" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O10" s="0" t="inlineStr">
@@ -955,16 +959,16 @@
       </c>
       <c r="P10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_147_img_0_0.jpeg | score=0.896 | stage=0.000 | 
-2. page_145_img_0_0.jpeg | score=0.849 | stage=0.000 | 
-3. page_133_img_0_0.jpeg | score=0.818 | stage=0.000 | 
-4. page_142_img_0_0.jpeg | score=0.801 | stage=0.000 | 
-5. page_142_img_1_0.jpeg | score=0.777 | stage=0.000 | 
-6. page_144_img_0_0.jpeg | score=0.772 | stage=0.000 | 
-7. page_144_img_1_0.jpeg | score=0.758 | stage=0.000 | 
-8. page_241_img_0_0.jpeg | score=0.719 | stage=0.000 | 
-9. page_242_img_0_0.jpeg | score=0.715 | stage=0.000 | 
-10. page_139_img_0_0.jpeg | score=0.707 | stage=0.000 | </t>
+          <t xml:space="preserve">1. page_145_img_0_0.jpeg | score=0.881 | stage=0.000
+2. page_147_img_0_0.jpeg | score=0.843 | stage=0.000
+3. page_133_img_0_0.jpeg | score=0.838 | stage=0.000
+4. page_143_img_1_0.jpeg | score=0.816 | stage=0.000
+5. page_143_img_0_0.jpeg | score=0.814 | stage=0.000
+6. page_144_img_0_0.jpeg | score=0.754 | stage=0.000
+7. page_144_img_1_0.jpeg | score=0.751 | stage=0.000
+8. page_255_img_0_0.jpeg | score=0.748 | stage=0.000
+9. page_334_img_0_0.jpeg | score=0.733 | stage=0.000
+10. page_148_img_0_0.jpeg | score=0.727 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1025,7 @@
       </c>
       <c r="K11" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L11" s="0" t="inlineStr">
@@ -1042,16 +1046,16 @@
       </c>
       <c r="P11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_195_img_2_0.jpeg | score=0.936 | stage=0.306 | keyword=i; section=i
-2. page_104_img_0_0.jpeg | score=0.883 | stage=0.244 | keyword=i; section=i
-3. page_386_img_1_0.jpeg | score=0.868 | stage=0.254 | keyword=i; section=i
-4. page_384_img_0_0.jpeg | score=0.852 | stage=0.239 | keyword=i; section=i
-5. page_192_img_0_0.jpeg | score=0.813 | stage=0.084 | keyword=i; section=i
-6. page_96_img_0_0.jpeg | score=0.806 | stage=0.293 | keyword=i; section=i
-7. page_376_img_0_0.jpeg | score=0.792 | stage=0.238 | keyword=i; section=i
-8. page_196_img_0_0.jpeg | score=0.717 | stage=0.084 | keyword=i; section=i
-9. page_98_img_0_0.jpeg | score=0.703 | stage=0.237 | keyword=i; section=i
-10. page_98_img_1_0.jpeg | score=0.666 | stage=0.237 | keyword=i; section=i</t>
+          <t xml:space="preserve">1. page_188_img_0_0.jpeg | score=0.928 | stage=0.146 | keyword=i; section=i
+2. page_195_img_0_0.jpeg | score=0.923 | stage=0.146 | keyword=i; section=i
+3. page_388_img_2_0.jpeg | score=0.878 | stage=0.146 | keyword=i; section=i
+4. page_104_img_0_0.jpeg | score=0.870 | stage=0.146 | keyword=i; section=i
+5. page_189_img_0_0.jpeg | score=0.861 | stage=0.146 | keyword=i; section=i
+6. page_195_img_2_0.jpeg | score=0.834 | stage=0.146 | keyword=i; section=i
+7. page_196_img_0_0.jpeg | score=0.828 | stage=0.146 | keyword=i; section=i
+8. page_389_img_0_0.jpeg | score=0.792 | stage=0.146 | keyword=i; section=i
+9. page_165_img_0_0.jpeg | score=0.791 | stage=0.146 | keyword=i; section=i
+10. page_105_img_0_0.jpeg | score=0.777 | stage=0.146 | keyword=i; section=i</t>
         </is>
       </c>
     </row>
@@ -1121,24 +1125,28 @@
           <t>page_188_img_0_0.jpeg</t>
         </is>
       </c>
-      <c r="N12" s="0"/>
+      <c r="N12" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O12" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_192_img_0_0.jpeg | score=1.333 | stage=0.722 | page=1.00; keyword=robot settings,y; section=robot settings
-2. page_195_img_2_0.jpeg | score=1.119 | stage=0.831 | page=1.00; keyword=mount,robot settings,y; section=robot settings,mount
-3. page_191_img_0_0.jpeg | score=1.062 | stage=0.722 | page=1.00; keyword=robot settings,y; section=robot settings
-4. page_196_img_0_0.jpeg | score=1.056 | stage=0.722 | page=1.00; keyword=robot settings,y; section=robot settings
-5. page_189_img_0_0.jpeg | score=1.052 | stage=0.722 | page=1.00; keyword=robot settings,y; section=robot settings
-6. page_190_img_0_0.jpeg | score=1.015 | stage=0.722 | page=1.00; keyword=robot settings,y; section=robot settings
-7. page_184_img_0_0.jpeg | score=0.907 | stage=0.580 | page=1.00
-8. page_378_img_2_0.jpeg | score=0.900 | stage=0.276 | keyword=y
-9. page_181_img_0_0.jpeg | score=0.892 | stage=0.324 | keyword=y
-10. page_378_img_0_0.jpeg | score=0.874 | stage=0.328 | keyword=y</t>
+          <t xml:space="preserve">1. page_188_img_0_0.jpeg | score=1.578 | stage=0.925 | page=1.00; keyword=mount,robot settings; section=robot settings,mount
+2. page_189_img_0_0.jpeg | score=1.505 | stage=0.938 | page=1.00; keyword=mount,robot settings,y; section=robot settings,mount
+3. page_187_img_0_0.jpeg | score=1.261 | stage=0.925 | page=1.00; keyword=mount,robot settings; section=robot settings,mount
+4. page_187_img_1_0.jpeg | score=1.248 | stage=0.925 | page=1.00; keyword=mount,robot settings; section=robot settings,mount
+5. page_181_img_0_0.jpeg | score=0.813 | stage=0.013 | keyword=y
+6. page_289_img_0_0.jpeg | score=0.808 | stage=0.013 | keyword=y
+7. page_378_img_2_0.jpeg | score=0.806 | stage=0.025 | keyword=y,z
+8. page_182_img_0_0.jpeg | score=0.780 | stage=0.013 | keyword=y
+9. page_184_img_0_0.jpeg | score=0.745 | stage=0.225 | page=0.45
+10. page_195_img_0_0.jpeg | score=0.734 | stage=0.725 | page=1.00; keyword=robot settings,z; section=robot settings</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1218,7 @@
       </c>
       <c r="N13" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O13" s="0" t="inlineStr">
@@ -1220,16 +1228,16 @@
       </c>
       <c r="P13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_178_img_0_0.jpeg | score=1.318 | stage=0.698 | page=1.00; keyword=backdrive,recovery; section=backdrive
-2. page_179_img_1_0.jpeg | score=1.297 | stage=0.698 | page=1.00; keyword=backdrive,recovery; section=backdrive
-3. page_181_img_0_0.jpeg | score=0.986 | stage=0.614 | page=1.00; keyword=recovery
-4. page_89_img_1_0.jpeg | score=0.899 | stage=0.341 | 
-5. page_177_img_1_0.jpeg | score=0.864 | stage=0.580 | page=1.00
-6. page_125_img_0_0.jpeg | score=0.859 | stage=0.328 | 
-7. page_89_img_0_0.jpeg | score=0.840 | stage=0.337 | 
-8. page_24_img_0_0.jpeg | score=0.725 | stage=0.289 | keyword=emergency
-9. page_169_img_2_0.jpeg | score=0.712 | stage=0.698 | page=1.00; keyword=backdrive,recovery; section=backdrive
-10. page_174_img_1_0.jpeg | score=0.701 | stage=0.580 | page=1.00</t>
+          <t xml:space="preserve">1. page_179_img_1_0.jpeg | score=1.408 | stage=0.646 | page=1.00; keyword=backdrive; section=backdrive
+2. page_178_img_0_0.jpeg | score=1.394 | stage=0.671 | page=1.00; keyword=backdrive,joint,recovery; section=backdrive
+3. page_177_img_1_0.jpeg | score=1.044 | stage=0.512 | page=1.00; keyword=servo off
+4. page_125_img_0_0.jpeg | score=0.789 | stage=0.000
+5. page_89_img_1_0.jpeg | score=0.778 | stage=0.000
+6. page_89_img_0_0.jpeg | score=0.752 | stage=0.000
+7. page_195_img_0_0.jpeg | score=0.658 | stage=0.000
+8. page_220_img_0_0.jpeg | score=0.654 | stage=0.000
+9. page_195_img_2_0.jpeg | score=0.632 | stage=0.000
+10. page_403_img_0_0.jpeg | score=0.599 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1279,7 @@
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t>0.0619</t>
+          <t>0.0620</t>
         </is>
       </c>
       <c r="I14" s="0" t="inlineStr">
@@ -1301,7 +1309,7 @@
       </c>
       <c r="N14" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O14" s="0" t="inlineStr">
@@ -1311,16 +1319,16 @@
       </c>
       <c r="P14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_94_img_0_0.jpeg | score=1.302 | stage=0.580 | page=1.00
-2. page_95_img_0_0.jpeg | score=1.235 | stage=0.580 | page=1.00
-3. page_96_img_0_0.jpeg | score=1.207 | stage=0.580 | page=1.00
-4. page_104_img_0_0.jpeg | score=1.092 | stage=0.580 | page=1.00
-5. page_103_img_0_0.jpeg | score=1.069 | stage=0.580 | page=1.00
-6. page_163_img_0_0.jpeg | score=0.994 | stage=0.350 | 
-7. page_163_img_1_0.jpeg | score=0.942 | stage=0.346 | 
-8. page_24_img_0_0.jpeg | score=0.904 | stage=0.332 | 
-9. page_89_img_1_0.jpeg | score=0.889 | stage=0.328 | 
-10. page_88_img_1_0.jpeg | score=0.844 | stage=0.315 | </t>
+          <t xml:space="preserve">1. page_94_img_0_0.jpeg | score=1.371 | stage=0.500 | page=1.00
+2. page_95_img_0_0.jpeg | score=1.329 | stage=0.500 | page=1.00
+3. page_96_img_0_0.jpeg | score=1.217 | stage=0.500 | page=1.00
+4. page_103_img_0_0.jpeg | score=1.150 | stage=0.500 | page=1.00
+5. page_104_img_0_0.jpeg | score=1.099 | stage=0.500 | page=1.00
+6. page_93_img_0_0.jpeg | score=1.057 | stage=0.500 | page=1.00
+7. page_163_img_0_0.jpeg | score=0.879 | stage=0.000
+8. page_163_img_1_0.jpeg | score=0.861 | stage=0.000
+9. page_24_img_0_0.jpeg | score=0.823 | stage=0.000
+10. page_220_img_0_0.jpeg | score=0.776 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -1402,16 +1410,16 @@
       </c>
       <c r="P15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_173_img_1_0.jpeg | score=1.359 | stage=0.689 | page=1.00; keyword=singularity; section=singularity
-2. page_174_img_1_0.jpeg | score=1.302 | stage=0.580 | page=1.00
-3. page_175_img_1_0.jpeg | score=0.994 | stage=0.580 | page=1.00
-4. page_175_img_4_0.jpeg | score=0.991 | stage=0.580 | page=1.00
-5. page_175_img_3_0.jpeg | score=0.986 | stage=0.580 | page=1.00
-6. page_175_img_2_0.jpeg | score=0.981 | stage=0.580 | page=1.00
-7. page_176_img_1_0.png | score=0.929 | stage=0.580 | page=1.00
-8. page_176_img_3_0.jpeg | score=0.925 | stage=0.580 | page=1.00
-9. page_176_img_2_0.jpeg | score=0.922 | stage=0.580 | page=1.00
-10. page_176_img_0_0.png | score=0.919 | stage=0.580 | page=1.00</t>
+          <t xml:space="preserve">1. page_173_img_1_0.jpeg | score=1.501 | stage=0.712 | page=1.00; keyword=singularity; section=singularity
+2. page_174_img_1_0.jpeg | score=1.370 | stage=0.512 | page=1.00; keyword=wrist
+3. page_175_img_1_0.jpeg | score=1.240 | stage=0.500 | page=1.00
+4. page_175_img_4_0.jpeg | score=1.057 | stage=0.500 | page=1.00
+5. page_175_img_3_0.jpeg | score=1.048 | stage=0.500 | page=1.00
+6. page_175_img_2_0.jpeg | score=1.042 | stage=0.500 | page=1.00
+7. page_277_img_0_0.jpeg | score=0.797 | stage=0.000
+8. page_242_img_0_0.jpeg | score=0.718 | stage=0.000
+9. page_278_img_1_0.jpeg | score=0.608 | stage=0.000
+10. page_276_img_0_0.jpeg | score=0.608 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -1477,24 +1485,28 @@
           <t>page_340_img_0_0.jpeg</t>
         </is>
       </c>
-      <c r="N16" s="0"/>
+      <c r="N16" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O16" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_366_img_0_0.jpeg | score=0.817 | stage=0.000 | 
-2. page_342_img_0_0.jpeg | score=0.809 | stage=0.000 | 
-3. page_368_img_0_0.jpeg | score=0.783 | stage=0.000 | 
-4. page_182_img_0_0.jpeg | score=0.773 | stage=0.000 | 
-5. page_363_img_0_0.jpeg | score=0.763 | stage=0.000 | 
-6. page_369_img_0_0.jpeg | score=0.756 | stage=0.000 | 
-7. page_370_img_0_0.jpeg | score=0.748 | stage=0.000 | 
-8. page_364_img_1_0.jpeg | score=0.744 | stage=0.000 | 
-9. page_342_img_2_0.jpeg | score=0.741 | stage=0.000 | 
-10. page_169_img_2_0.jpeg | score=0.713 | stage=0.000 | </t>
+          <t xml:space="preserve">1. page_363_img_0_0.jpeg | score=0.808 | stage=0.000
+2. page_182_img_0_0.jpeg | score=0.765 | stage=0.000
+3. page_340_img_0_0.jpeg | score=0.734 | stage=0.000
+4. page_368_img_0_0.jpeg | score=0.726 | stage=0.000
+5. page_364_img_1_0.jpeg | score=0.724 | stage=0.000
+6. page_169_img_2_0.jpeg | score=0.702 | stage=0.000
+7. page_342_img_2_0.jpeg | score=0.690 | stage=0.000
+8. page_349_img_0_0.jpeg | score=0.688 | stage=0.000
+9. page_369_img_0_0.jpeg | score=0.641 | stage=0.000
+10. page_361_img_0_0.jpeg | score=0.639 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -1576,16 +1588,16 @@
       </c>
       <c r="P17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_116_img_0_0.jpeg | score=1.262 | stage=0.580 | page=1.00
-2. page_119_img_1_0.jpeg | score=1.237 | stage=0.580 | page=1.00
-3. page_121_img_0_0.jpeg | score=1.160 | stage=0.580 | page=1.00
-4. page_123_img_0_0.jpeg | score=1.055 | stage=0.580 | page=1.00
-5. page_115_img_0_0.jpeg | score=0.997 | stage=0.580 | page=1.00
-6. page_119_img_0_0.jpeg | score=0.972 | stage=0.580 | page=1.00
-7. page_124_img_0_0.jpeg | score=0.895 | stage=0.580 | page=1.00
-8. page_88_img_1_0.jpeg | score=0.875 | stage=0.258 | 
-9. page_88_img_0_0.jpeg | score=0.872 | stage=0.276 | 
-10. page_120_img_0_0.jpeg | score=0.866 | stage=0.406 | page=0.70</t>
+          <t xml:space="preserve">1. page_116_img_0_0.jpeg | score=1.371 | stage=0.500 | page=1.00
+2. page_119_img_0_0.jpeg | score=1.277 | stage=0.500 | page=1.00
+3. page_120_img_0_0.jpeg | score=1.192 | stage=0.500 | page=1.00
+4. page_119_img_1_0.jpeg | score=1.094 | stage=0.500 | page=1.00
+5. page_115_img_0_0.jpeg | score=1.040 | stage=0.500 | page=1.00
+6. page_118_img_0_0.jpeg | score=0.992 | stage=0.500 | page=1.00
+7. page_402_img_0_0.jpeg | score=0.861 | stage=0.000
+8. page_121_img_0_0.jpeg | score=0.849 | stage=0.350 | page=0.70
+9. page_401_img_0_0.jpeg | score=0.779 | stage=0.000
+10. page_401_img_1_0.jpeg | score=0.775 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1669,7 @@
       </c>
       <c r="N18" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O18" s="0" t="inlineStr">
@@ -1667,16 +1679,16 @@
       </c>
       <c r="P18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_127_img_0_0.jpeg | score=1.274 | stage=0.617 | page=1.00; section=o
-2. page_128_img_0_0.jpeg | score=1.259 | stage=0.617 | page=1.00; section=o
-3. page_130_img_0_0.jpeg | score=1.192 | stage=0.617 | page=1.00; section=o
-4. page_123_img_0_0.jpeg | score=1.026 | stage=0.443 | page=0.70; section=o
-5. page_132_img_0_0.png | score=0.986 | stage=0.617 | page=1.00; section=o
-6. page_133_img_0_0.jpeg | score=0.972 | stage=0.617 | page=1.00; section=o
-7. page_201_img_1_0.jpeg | score=0.876 | stage=0.297 | section=o
-8. page_124_img_0_0.jpeg | score=0.762 | stage=0.443 | page=0.70; section=o
-9. page_125_img_0_0.jpeg | score=0.758 | stage=0.443 | page=0.70; section=o
-10. page_141_img_1_0.jpeg | score=0.745 | stage=0.337 | section=o</t>
+          <t xml:space="preserve">1. page_128_img_0_0.jpeg | score=1.424 | stage=0.612 | page=1.00; keyword=x1; section=o
+2. page_127_img_0_0.jpeg | score=1.311 | stage=0.600 | page=1.00; section=o
+3. page_132_img_0_0.png | score=1.195 | stage=0.600 | page=1.00; section=o
+4. page_130_img_0_0.jpeg | score=1.154 | stage=0.600 | page=1.00; section=o
+5. page_201_img_1_0.jpeg | score=0.777 | stage=0.100 | section=o
+6. page_336_img_0_0.jpeg | score=0.762 | stage=0.100 | section=o
+7. page_124_img_0_0.jpeg | score=0.754 | stage=0.350 | page=0.70
+8. page_94_img_0_0.jpeg | score=0.697 | stage=0.100 | section=o
+9. page_95_img_0_0.jpeg | score=0.680 | stage=0.200 | section=flange i,o
+10. page_199_img_0_0.jpeg | score=0.637 | stage=0.113 | keyword=x1; section=o</t>
         </is>
       </c>
     </row>
@@ -1758,16 +1770,16 @@
       </c>
       <c r="P19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_242_img_0_0.jpeg | score=1.311 | stage=0.655 | page=1.00; section=safety settings
-2. page_241_img_0_0.jpeg | score=1.083 | stage=0.655 | page=1.00; section=safety settings
-3. page_243_img_0_0.jpeg | score=1.049 | stage=0.655 | page=1.00; section=safety settings
-4. page_224_img_0_0.jpeg | score=1.014 | stage=0.655 | page=1.00; section=safety settings
-5. page_243_img_1_0.jpeg | score=1.000 | stage=0.655 | page=1.00; section=safety settings
-6. page_240_img_0_0.jpeg | score=0.952 | stage=0.655 | page=1.00; section=safety settings
-7. page_245_img_0_0.jpeg | score=0.949 | stage=0.655 | page=1.00; section=safety settings
-8. page_244_img_0_0.jpeg | score=0.937 | stage=0.655 | page=1.00; section=safety settings
-9. page_225_img_0_0.jpeg | score=0.861 | stage=0.655 | page=1.00; section=safety settings
-10. page_24_img_0_0.jpeg | score=0.860 | stage=0.319 | </t>
+          <t xml:space="preserve">1. page_242_img_0_0.jpeg | score=1.475 | stage=0.700 | page=1.00; section=safety settings
+2. page_241_img_0_0.jpeg | score=1.350 | stage=0.700 | page=1.00; section=safety settings
+3. page_243_img_0_0.jpeg | score=1.276 | stage=0.700 | page=1.00; section=safety settings
+4. page_243_img_1_0.jpeg | score=1.181 | stage=0.700 | page=1.00; section=safety settings
+5. page_244_img_0_0.jpeg | score=1.149 | stage=0.700 | page=1.00; section=safety settings
+6. page_240_img_0_0.jpeg | score=1.103 | stage=0.700 | page=1.00; section=safety settings
+7. page_245_img_0_0.jpeg | score=1.097 | stage=0.700 | page=1.00; section=safety settings
+8. page_224_img_0_0.jpeg | score=0.806 | stage=0.213 | keyword=safety zone; section=safety settings
+9. page_238_img_0_0.jpeg | score=0.716 | stage=0.700 | page=1.00; section=safety settings
+10. page_225_img_0_0.jpeg | score=0.712 | stage=0.200 | section=safety settings</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1821,7 @@
       </c>
       <c r="H20" s="0" t="inlineStr">
         <is>
-          <t>0.1313</t>
+          <t>0.1312</t>
         </is>
       </c>
       <c r="I20" s="0" t="inlineStr">
@@ -1839,26 +1851,26 @@
       </c>
       <c r="N20" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O20" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_374_img_1_0.jpeg | score=1.313 | stage=0.698 | page=1.00; keyword=jog,manual; section=jog
-2. page_375_img_0_0.jpeg | score=1.307 | stage=0.698 | page=1.00; keyword=jog,manual; section=jog
-3. page_384_img_0_0.jpeg | score=1.094 | stage=0.614 | page=1.00; keyword=manual
-4. page_379_img_2_0.jpeg | score=1.063 | stage=0.614 | page=1.00; keyword=manual
-5. page_374_img_0_0.jpeg | score=1.044 | stage=0.614 | page=1.00; keyword=manual
-6. page_379_img_1_0.jpeg | score=1.015 | stage=0.614 | page=1.00; keyword=manual
-7. page_378_img_2_0.jpeg | score=0.977 | stage=0.614 | page=1.00; keyword=manual
-8. page_373_img_0_0.jpeg | score=0.976 | stage=0.580 | page=1.00
-9. page_376_img_0_0.jpeg | score=0.961 | stage=0.580 | page=1.00
-10. page_378_img_0_0.jpeg | score=0.917 | stage=0.614 | page=1.00; keyword=manual</t>
+          <t xml:space="preserve">1. page_375_img_0_0.jpeg | score=1.364 | stage=0.646 | page=1.00; keyword=jog; section=jog
+2. page_374_img_1_0.jpeg | score=1.286 | stage=0.500 | page=1.00
+3. page_374_img_0_0.jpeg | score=1.284 | stage=0.500 | page=1.00
+4. page_376_img_0_0.jpeg | score=1.199 | stage=0.646 | page=1.00; keyword=jog; section=jog
+5. page_373_img_0_0.jpeg | score=1.165 | stage=0.500 | page=1.00
+6. page_379_img_2_0.jpeg | score=1.014 | stage=0.500 | page=1.00
+7. page_379_img_1_0.jpeg | score=0.975 | stage=0.500 | page=1.00
+8. page_378_img_2_0.jpeg | score=0.898 | stage=0.500 | page=1.00
+9. page_379_img_0_0.jpeg | score=0.895 | stage=0.500 | page=1.00
+10. page_381_img_0_0.jpeg | score=0.886 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1942,7 @@
       </c>
       <c r="N21" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O21" s="0" t="inlineStr">
@@ -1940,16 +1952,16 @@
       </c>
       <c r="P21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_201_img_1_0.jpeg | score=1.371 | stage=0.861 | page=1.00; keyword=tool settings,tcp,tool center point,x; section=tool settings,tool center point,tcp
-2. page_203_img_0_0.jpeg | score=1.319 | stage=0.752 | page=1.00; keyword=tool settings,x,y,z; section=tool settings
-3. page_202_img_0_0.jpeg | score=1.284 | stage=0.752 | page=1.00; keyword=tool settings,x,y,z; section=tool settings
-4. page_201_img_0_0.jpeg | score=1.283 | stage=0.861 | page=1.00; keyword=tool settings,tcp,tool center point,x; section=tool settings,tool center point,tcp
-5. page_208_img_0_0.jpeg | score=1.267 | stage=0.752 | page=1.00; keyword=tool settings,x,y,z; section=tool settings
-6. page_204_img_1_0.jpeg | score=1.251 | stage=0.790 | page=1.00; keyword=tool settings,tcp,x,y; section=tool settings,tcp
-7. page_244_img_0_0.jpeg | score=1.180 | stage=0.473 | page=0.70; keyword=x,y
-8. page_202_img_1_0.jpeg | score=1.114 | stage=0.861 | page=1.00; keyword=tool settings,tcp,tool center point,x; section=tool settings,tool center point,tcp
-9. page_209_img_0_0.jpeg | score=1.070 | stage=0.752 | page=1.00; keyword=tool settings,x,y,z; section=tool settings
-10. page_205_img_1_0.jpeg | score=1.041 | stage=0.719 | page=1.00; keyword=tool settings,x,y; section=tool settings</t>
+          <t xml:space="preserve">1. page_202_img_1_0.jpeg | score=1.548 | stage=0.875 | page=1.00; keyword=tool settings,tcp,tool center point,x; section=tool settings,tool center point,tcp
+2. page_201_img_1_0.jpeg | score=1.524 | stage=0.875 | page=1.00; keyword=tool settings,tcp,tool center point,x; section=tool settings,tool center point,tcp
+3. page_203_img_0_0.jpeg | score=1.400 | stage=0.762 | page=1.00; keyword=tool settings,tcp,x,y; section=tool settings,tcp
+4. page_202_img_0_0.jpeg | score=1.331 | stage=0.875 | page=1.00; keyword=tool settings,tcp,tool center point,x; section=tool settings,tool center point,tcp
+5. page_201_img_0_0.jpeg | score=1.309 | stage=0.875 | page=1.00; keyword=tool settings,tcp,tool center point,x; section=tool settings,tool center point,tcp
+6. page_208_img_0_0.jpeg | score=1.154 | stage=0.637 | page=1.00; keyword=tool settings,y,simulation; section=tool settings
+7. page_204_img_0_0.jpeg | score=1.082 | stage=0.762 | page=1.00; keyword=tool settings,tcp,x,y; section=tool settings,tcp
+8. page_204_img_1_0.jpeg | score=1.011 | stage=0.762 | page=1.00; keyword=tool settings,tcp,x,y; section=tool settings,tcp
+9. page_244_img_0_0.jpeg | score=0.945 | stage=0.138 | keyword=tcp,y,z; section=tcp
+10. page_206_img_0_0.jpeg | score=0.913 | stage=0.625 | page=1.00; keyword=tool settings,y; section=tool settings</t>
         </is>
       </c>
     </row>
@@ -2002,7 +2014,7 @@
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
@@ -2017,7 +2029,7 @@
       </c>
       <c r="N22" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O22" s="0" t="inlineStr">
@@ -2027,16 +2039,16 @@
       </c>
       <c r="P22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_224_img_0_0.jpeg | score=0.858 | stage=0.000 | 
-2. page_242_img_0_0.jpeg | score=0.811 | stage=0.000 | 
-3. page_240_img_0_0.jpeg | score=0.803 | stage=0.000 | 
-4. page_241_img_0_0.jpeg | score=0.781 | stage=0.000 | 
-5. page_236_img_0_0.jpeg | score=0.709 | stage=0.000 | 
-6. page_244_img_0_0.jpeg | score=0.659 | stage=0.000 | 
-7. page_226_img_2_0.jpeg | score=0.658 | stage=0.000 | 
-8. page_245_img_0_0.jpeg | score=0.651 | stage=0.000 | 
-9. page_243_img_0_0.jpeg | score=0.643 | stage=0.000 | 
-10. page_235_img_1_0.jpeg | score=0.634 | stage=0.000 | </t>
+          <t xml:space="preserve">1. page_225_img_0_0.jpeg | score=0.888 | stage=0.000
+2. page_224_img_0_0.jpeg | score=0.869 | stage=0.000
+3. page_241_img_0_0.jpeg | score=0.835 | stage=0.000
+4. page_240_img_0_0.jpeg | score=0.814 | stage=0.000
+5. page_242_img_0_0.jpeg | score=0.797 | stage=0.000
+6. page_226_img_0_0.jpeg | score=0.797 | stage=0.000
+7. page_239_img_0_0.jpeg | score=0.707 | stage=0.000
+8. page_220_img_0_0.jpeg | score=0.664 | stage=0.000
+9. page_237_img_0_0.jpeg | score=0.621 | stage=0.000
+10. page_226_img_2_0.jpeg | score=0.603 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2105,7 @@
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L23" s="0" t="inlineStr">
@@ -2114,16 +2126,16 @@
       </c>
       <c r="P23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_278_img_1_0.jpeg | score=1.165 | stage=0.580 | page=1.00
-2. page_275_img_0_0.jpeg | score=1.057 | stage=0.747 | page=1.00; keyword=movej,movel; section=movej,movel
-3. page_271_img_1_0.jpeg | score=0.945 | stage=0.614 | page=1.00; keyword=radius
-4. page_277_img_0_0.jpeg | score=0.927 | stage=0.580 | page=1.00
-5. page_316_img_0_0.jpeg | score=0.906 | stage=0.346 | 
-6. page_312_img_0_0.jpeg | score=0.831 | stage=0.341 | 
-7. page_267_img_1_0.jpeg | score=0.744 | stage=0.747 | page=1.00; keyword=movej,movel; section=movej,movel
-8. page_276_img_0_0.jpeg | score=0.721 | stage=0.580 | page=1.00
-9. page_265_img_1_0.jpeg | score=0.702 | stage=0.580 | page=1.00
-10. page_174_img_1_0.jpeg | score=0.686 | stage=0.276 | </t>
+          <t xml:space="preserve">1. page_271_img_1_0.jpeg | score=1.072 | stage=0.512 | page=1.00; keyword=radius
+2. page_271_img_0_0.jpeg | score=1.056 | stage=0.512 | page=1.00; keyword=radius
+3. page_277_img_0_0.jpeg | score=1.013 | stage=0.500 | page=1.00
+4. page_316_img_0_0.jpeg | score=0.833 | stage=0.000
+5. page_278_img_1_0.jpeg | score=0.821 | stage=0.500 | page=1.00
+6. page_276_img_0_0.jpeg | score=0.814 | stage=0.500 | page=1.00
+7. page_312_img_0_0.jpeg | score=0.743 | stage=0.013 | keyword=tcp
+8. page_313_img_0_0.jpeg | score=0.692 | stage=0.000
+9. page_104_img_0_0.jpeg | score=0.588 | stage=0.000
+10. page_398_img_0_0.jpeg | score=0.528 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2177,7 @@
       </c>
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t>0.0380</t>
+          <t>0.0381</t>
         </is>
       </c>
       <c r="I24" s="0" t="inlineStr">
@@ -2180,7 +2192,7 @@
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
@@ -2195,26 +2207,26 @@
       </c>
       <c r="N24" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O24" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
       <c r="P24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_168_img_0_0.jpeg | score=1.060 | stage=0.614 | page=1.00; keyword=dart-platform
-2. page_165_img_0_0.jpeg | score=1.005 | stage=0.580 | page=1.00
-3. page_357_img_0_0.jpeg | score=0.858 | stage=0.337 | 
-4. page_167_img_2_0.jpeg | score=0.845 | stage=0.614 | page=1.00; keyword=dart-platform
-5. page_167_img_3_0.jpeg | score=0.838 | stage=0.614 | page=1.00; keyword=dart-platform
-6. page_96_img_0_0.jpeg | score=0.798 | stage=0.328 | 
-7. page_168_img_1_0.png | score=0.797 | stage=0.614 | page=1.00; keyword=dart-platform
-8. page_169_img_1_0.png | score=0.794 | stage=0.614 | page=1.00; keyword=dart-platform
-9. page_173_img_1_0.jpeg | score=0.759 | stage=0.580 | page=1.00
-10. page_309_img_1_0.jpeg | score=0.712 | stage=0.271 | </t>
+          <t xml:space="preserve">1. page_165_img_0_0.jpeg | score=1.435 | stage=0.646 | page=1.00; keyword=header; section=header
+2. page_166_img_1_0.jpeg | score=1.338 | stage=0.646 | page=1.00; keyword=header; section=header
+3. page_168_img_0_0.jpeg | score=1.316 | stage=0.500 | page=1.00
+4. page_168_img_1_0.png | score=1.111 | stage=0.500 | page=1.00
+5. page_164_img_1_0.jpeg | score=1.078 | stage=0.500 | page=1.00
+6. page_169_img_2_0.jpeg | score=1.034 | stage=0.500 | page=1.00
+7. page_167_img_3_0.jpeg | score=1.030 | stage=0.500 | page=1.00
+8. page_169_img_1_0.png | score=1.003 | stage=0.500 | page=1.00
+9. page_167_img_2_0.jpeg | score=0.872 | stage=0.500 | page=1.00
+10. page_357_img_0_0.jpeg | score=0.813 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2268,7 @@
       </c>
       <c r="H25" s="0" t="inlineStr">
         <is>
-          <t>0.0562</t>
+          <t>0.0563</t>
         </is>
       </c>
       <c r="I25" s="0" t="inlineStr">
@@ -2286,26 +2298,26 @@
       </c>
       <c r="N25" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O25" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_277_img_0_0.jpeg | score=1.230 | stage=0.580 | page=1.00
-2. page_276_img_0_0.jpeg | score=1.217 | stage=0.580 | page=1.00
-3. page_281_img_1_0.jpeg | score=1.045 | stage=0.580 | page=1.00
-4. page_278_img_1_0.jpeg | score=1.038 | stage=0.580 | page=1.00
-5. page_280_img_0_0.jpeg | score=1.018 | stage=0.580 | page=1.00
-6. page_279_img_0_0.jpeg | score=0.977 | stage=0.580 | page=1.00
-7. page_275_img_0_0.jpeg | score=0.973 | stage=0.747 | page=1.00; keyword=movej,movel; section=movej,movel
-8. page_267_img_1_0.jpeg | score=0.909 | stage=0.747 | page=1.00; keyword=movej,movel; section=movej,movel
-9. page_299_img_0_0.jpeg | score=0.865 | stage=0.293 | 
-10. page_195_img_2_0.jpeg | score=0.818 | stage=0.226 | </t>
+          <t xml:space="preserve">1. page_276_img_0_0.jpeg | score=1.459 | stage=0.804 | page=1.00; keyword=movej,movel,tcp; section=movej,movel
+2. page_275_img_0_0.jpeg | score=1.348 | stage=0.829 | page=1.00; keyword=movej,movel,motion,linear; section=movej,movel
+3. page_277_img_0_0.jpeg | score=1.210 | stage=0.512 | page=1.00; keyword=tcp
+4. page_269_img_0_0.jpeg | score=0.994 | stage=0.512 | page=1.00; keyword=tcp
+5. page_267_img_1_0.jpeg | score=0.981 | stage=0.792 | page=1.00; keyword=movej,movel; section=movej,movel
+6. page_195_img_0_0.jpeg | score=0.817 | stage=0.000
+7. page_195_img_2_0.jpeg | score=0.791 | stage=0.000
+8. page_271_img_1_0.jpeg | score=0.769 | stage=0.512 | page=1.00; keyword=radius
+9. page_271_img_0_0.jpeg | score=0.754 | stage=0.512 | page=1.00; keyword=radius
+10. page_196_img_0_0.jpeg | score=0.715 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2370,7 @@
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L26" s="0" t="inlineStr">
@@ -2371,24 +2383,28 @@
           <t>page_275_img_0_0.jpeg</t>
         </is>
       </c>
-      <c r="N26" s="0"/>
+      <c r="N26" s="0" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="O26" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>△</t>
         </is>
       </c>
       <c r="P26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_378_img_2_0.jpeg | score=0.852 | stage=0.000 | 
-2. page_378_img_0_0.jpeg | score=0.815 | stage=0.000 | 
-3. page_374_img_1_0.jpeg | score=0.802 | stage=0.000 | 
-4. page_384_img_0_0.jpeg | score=0.779 | stage=0.000 | 
-5. page_379_img_2_0.jpeg | score=0.751 | stage=0.000 | 
-6. page_375_img_0_0.jpeg | score=0.717 | stage=0.000 | 
-7. page_379_img_1_0.jpeg | score=0.687 | stage=0.000 | 
-8. page_267_img_1_0.jpeg | score=0.679 | stage=0.000 | 
-9. page_288_img_0_0.jpeg | score=0.673 | stage=0.000 | 
-10. page_386_img_1_0.jpeg | score=0.641 | stage=0.000 | </t>
+          <t xml:space="preserve">1. page_378_img_2_0.jpeg | score=0.883 | stage=0.000
+2. page_374_img_1_0.jpeg | score=0.818 | stage=0.000
+3. page_374_img_0_0.jpeg | score=0.817 | stage=0.000
+4. page_379_img_2_0.jpeg | score=0.763 | stage=0.000
+5. page_375_img_0_0.jpeg | score=0.705 | stage=0.000
+6. page_275_img_0_0.jpeg | score=0.705 | stage=0.000
+7. page_378_img_0_0.jpeg | score=0.670 | stage=0.000
+8. page_373_img_0_0.jpeg | score=0.650 | stage=0.000
+9. page_379_img_1_0.jpeg | score=0.634 | stage=0.000
+10. page_269_img_0_0.jpeg | score=0.628 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2446,7 @@
       </c>
       <c r="H27" s="0" t="inlineStr">
         <is>
-          <t>0.1250</t>
+          <t>0.1249</t>
         </is>
       </c>
       <c r="I27" s="0" t="inlineStr">
@@ -2460,26 +2476,26 @@
       </c>
       <c r="N27" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O27" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
       <c r="P27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_361_img_0_0.jpeg | score=1.283 | stage=0.689 | page=1.00; keyword=robot update; section=robot update
-2. page_167_img_2_0.jpeg | score=1.241 | stage=0.580 | page=1.00
-3. page_360_img_0_0.jpeg | score=1.236 | stage=0.689 | page=1.00; keyword=robot update; section=robot update
-4. page_366_img_0_0.jpeg | score=1.219 | stage=0.580 | page=1.00
-5. page_167_img_3_0.jpeg | score=1.174 | stage=0.580 | page=1.00
-6. page_364_img_1_0.jpeg | score=1.084 | stage=0.689 | page=1.00; keyword=robot update; section=robot update
-7. page_363_img_0_0.jpeg | score=1.047 | stage=0.689 | page=1.00; keyword=robot update; section=robot update
-8. page_166_img_1_0.jpeg | score=1.024 | stage=0.580 | page=1.00
-9. page_361_img_1_0.jpeg | score=1.002 | stage=0.689 | page=1.00; keyword=robot update; section=robot update
-10. page_361_img_2_0.png | score=0.985 | stage=0.689 | page=1.00; keyword=robot update; section=robot update</t>
+          <t xml:space="preserve">1. page_167_img_3_0.jpeg | score=1.326 | stage=0.500 | page=1.00
+2. page_361_img_0_0.jpeg | score=1.321 | stage=0.712 | page=1.00; keyword=robot update; section=robot update
+3. page_361_img_1_0.jpeg | score=1.318 | stage=0.712 | page=1.00; keyword=robot update; section=robot update
+4. page_366_img_0_0.jpeg | score=1.287 | stage=0.500 | page=1.00
+5. page_168_img_0_0.jpeg | score=1.240 | stage=0.500 | page=1.00
+6. page_360_img_0_0.jpeg | score=1.203 | stage=0.712 | page=1.00; keyword=robot update; section=robot update
+7. page_367_img_0_0.jpeg | score=1.188 | stage=0.500 | page=1.00
+8. page_167_img_2_0.jpeg | score=1.138 | stage=0.500 | page=1.00
+9. page_361_img_2_0.png | score=1.081 | stage=0.712 | page=1.00; keyword=robot update; section=robot update
+10. page_166_img_1_0.jpeg | score=1.073 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2537,7 @@
       </c>
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t>0.2172</t>
+          <t>0.2173</t>
         </is>
       </c>
       <c r="I28" s="0" t="inlineStr">
@@ -2561,16 +2577,16 @@
       </c>
       <c r="P28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_370_img_0_0.jpeg | score=1.218 | stage=0.580 | page=1.00
-2. page_369_img_0_0.jpeg | score=1.185 | stage=0.580 | page=1.00
-3. page_363_img_0_0.jpeg | score=1.118 | stage=0.580 | page=1.00
-4. page_364_img_1_0.jpeg | score=1.102 | stage=0.580 | page=1.00
-5. page_368_img_0_0.jpeg | score=1.041 | stage=0.580 | page=1.00
-6. page_361_img_0_0.jpeg | score=0.991 | stage=0.580 | page=1.00
-7. page_361_img_1_0.jpeg | score=0.873 | stage=0.580 | page=1.00
-8. page_361_img_2_0.png | score=0.857 | stage=0.580 | page=1.00
-9. page_182_img_0_0.jpeg | score=0.814 | stage=0.337 | 
-10. page_360_img_0_0.jpeg | score=0.810 | stage=0.580 | page=1.00</t>
+          <t xml:space="preserve">1. page_370_img_0_0.jpeg | score=1.480 | stage=0.725 | page=1.00; keyword=factory reset,reset; section=factory reset
+2. page_369_img_0_0.jpeg | score=1.261 | stage=0.500 | page=1.00
+3. page_368_img_0_0.jpeg | score=1.098 | stage=0.500 | page=1.00
+4. page_364_img_1_0.jpeg | score=0.942 | stage=0.350 | page=0.70
+5. page_363_img_0_0.jpeg | score=0.908 | stage=0.225 | page=0.45
+6. page_367_img_0_0.jpeg | score=0.855 | stage=0.500 | page=1.00
+7. page_213_img_0_0.jpeg | score=0.734 | stage=0.013 | keyword=reset
+8. page_214_img_0_0.jpeg | score=0.713 | stage=0.013 | keyword=reset
+9. page_182_img_0_0.jpeg | score=0.694 | stage=0.000
+10. page_197_img_0_0.jpeg | score=0.656 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2643,7 @@
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
@@ -2640,24 +2656,28 @@
           <t>page_405_img_0_0.jpeg</t>
         </is>
       </c>
-      <c r="N29" s="0"/>
+      <c r="N29" s="0" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O29" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>△</t>
         </is>
       </c>
       <c r="P29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_397_img_0_0.jpeg | score=1.240 | stage=0.580 | page=1.00
-2. page_405_img_1_0.jpeg | score=1.231 | stage=0.664 | page=1.00; keyword=grommet; section=grommet
-3. page_405_img_5_0.jpeg | score=1.218 | stage=0.664 | page=1.00; keyword=grommet; section=grommet
-4. page_398_img_0_0.jpeg | score=1.215 | stage=0.580 | page=1.00
-5. page_402_img_0_0.jpeg | score=0.980 | stage=0.580 | page=1.00
-6. page_402_img_1_0.jpeg | score=0.977 | stage=0.580 | page=1.00
-7. page_405_img_3_0.jpeg | score=0.975 | stage=0.664 | page=1.00; keyword=grommet; section=grommet
-8. page_403_img_0_0.jpeg | score=0.975 | stage=0.580 | page=1.00
-9. page_405_img_2_0.jpeg | score=0.972 | stage=0.664 | page=1.00; keyword=grommet; section=grommet
-10. page_405_img_4_0.jpeg | score=0.969 | stage=0.664 | page=1.00; keyword=grommet; section=grommet</t>
+          <t xml:space="preserve">1. page_405_img_5_0.jpeg | score=1.294 | stage=0.646 | page=1.00; keyword=grommet; section=grommet
+2. page_405_img_3_0.jpeg | score=1.290 | stage=0.646 | page=1.00; keyword=grommet; section=grommet
+3. page_403_img_0_0.jpeg | score=1.224 | stage=0.350 | page=0.70
+4. page_405_img_4_0.jpeg | score=1.125 | stage=0.646 | page=1.00; keyword=grommet; section=grommet
+5. page_405_img_2_0.jpeg | score=1.123 | stage=0.646 | page=1.00; keyword=grommet; section=grommet
+6. page_405_img_1_0.jpeg | score=1.120 | stage=0.646 | page=1.00; keyword=grommet; section=grommet
+7. page_405_img_0_0.jpeg | score=1.106 | stage=0.646 | page=1.00; keyword=grommet; section=grommet
+8. page_401_img_1_0.jpeg | score=0.920 | stage=0.225 | page=0.45
+9. page_402_img_0_0.jpeg | score=0.911 | stage=0.350 | page=0.70
+10. page_402_img_1_0.jpeg | score=0.910 | stage=0.350 | page=0.70</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2715,7 @@
       </c>
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t>0.0169</t>
+          <t>0.0170</t>
         </is>
       </c>
       <c r="I30" s="0" t="inlineStr">
@@ -2723,28 +2743,24 @@
           <t>page_202_img_0_0.jpeg</t>
         </is>
       </c>
-      <c r="N30" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="N30" s="0"/>
       <c r="O30" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_201_img_1_0.jpeg | score=0.891 | stage=0.000 | 
-2. page_203_img_0_0.jpeg | score=0.845 | stage=0.000 | 
-3. page_201_img_0_0.jpeg | score=0.817 | stage=0.000 | 
-4. page_202_img_0_0.jpeg | score=0.812 | stage=0.000 | 
-5. page_176_img_3_0.jpeg | score=0.782 | stage=0.000 | 
-6. page_378_img_2_0.jpeg | score=0.767 | stage=0.000 | 
-7. page_110_img_0_0.jpeg | score=0.753 | stage=0.000 | 
-8. page_176_img_2_0.jpeg | score=0.753 | stage=0.000 | 
-9. page_379_img_2_0.jpeg | score=0.753 | stage=0.000 | 
-10. page_244_img_0_0.jpeg | score=0.721 | stage=0.000 | </t>
+          <t xml:space="preserve">1. page_201_img_1_0.jpeg | score=0.881 | stage=0.000
+2. page_202_img_1_0.jpeg | score=0.876 | stage=0.000
+3. page_110_img_0_0.jpeg | score=0.794 | stage=0.000
+4. page_175_img_1_0.jpeg | score=0.768 | stage=0.000
+5. page_175_img_3_0.jpeg | score=0.763 | stage=0.000
+6. page_203_img_0_0.jpeg | score=0.759 | stage=0.000
+7. page_244_img_0_0.jpeg | score=0.753 | stage=0.000
+8. page_378_img_2_0.jpeg | score=0.726 | stage=0.000
+9. page_389_img_0_0.jpeg | score=0.726 | stage=0.000
+10. page_201_img_0_0.jpeg | score=0.685 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -2816,26 +2832,26 @@
       </c>
       <c r="N31" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O31" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_397_img_0_0.jpeg | score=1.036 | stage=0.630 | page=1.00; section=cs-12p
-2. page_398_img_0_0.jpeg | score=1.006 | stage=0.630 | page=1.00; section=cs-12p
-3. page_121_img_0_0.jpeg | score=0.895 | stage=0.227 | 
-4. page_137_img_0_0.jpeg | score=0.868 | stage=0.337 | 
-5. page_86_img_0_0.jpeg | score=0.868 | stage=0.324 | 
-6. page_402_img_1_0.jpeg | score=0.847 | stage=0.630 | page=1.00; section=cs-12p
-7. page_402_img_0_0.jpeg | score=0.844 | stage=0.630 | page=1.00; section=cs-12p
-8. page_403_img_0_0.jpeg | score=0.841 | stage=0.630 | page=1.00; section=cs-12p
-9. page_138_img_0_0.jpeg | score=0.840 | stage=0.341 | 
-10. page_163_img_0_0.jpeg | score=0.833 | stage=0.230 | </t>
+          <t xml:space="preserve">1. page_403_img_0_0.jpeg | score=1.446 | stage=0.633 | page=1.00; section=cs-12p
+2. page_399_img_0_0.jpeg | score=1.345 | stage=0.633 | page=1.00; section=cs-12p
+3. page_400_img_0_0.jpeg | score=1.289 | stage=0.633 | page=1.00; section=cs-12p
+4. page_402_img_0_0.jpeg | score=1.205 | stage=0.633 | page=1.00; section=cs-12p
+5. page_402_img_1_0.jpeg | score=1.125 | stage=0.633 | page=1.00; section=cs-12p
+6. page_398_img_0_0.jpeg | score=1.061 | stage=0.633 | page=1.00; section=cs-12p
+7. page_401_img_1_0.jpeg | score=0.905 | stage=0.633 | page=1.00; section=cs-12p
+8. page_401_img_0_0.jpeg | score=0.881 | stage=0.633 | page=1.00; section=cs-12p
+9. page_121_img_0_0.jpeg | score=0.853 | stage=0.000
+10. page_120_img_0_0.jpeg | score=0.711 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2893,7 @@
       </c>
       <c r="H32" s="0" t="inlineStr">
         <is>
-          <t>0.0946</t>
+          <t>0.0947</t>
         </is>
       </c>
       <c r="I32" s="0" t="inlineStr">
@@ -2917,16 +2933,16 @@
       </c>
       <c r="P32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_102_img_0_0.jpeg | score=1.251 | stage=0.580 | page=1.00
-2. page_104_img_0_0.jpeg | score=1.167 | stage=0.580 | page=1.00
-3. page_103_img_0_0.jpeg | score=1.090 | stage=0.580 | page=1.00
-4. page_163_img_0_0.jpeg | score=0.908 | stage=0.346 | 
-5. page_119_img_1_0.jpeg | score=0.903 | stage=0.293 | 
-6. page_101_img_0_0.jpeg | score=0.901 | stage=0.580 | page=1.00
-7. page_95_img_0_0.jpeg | score=0.896 | stage=0.341 | 
-8. page_96_img_0_0.jpeg | score=0.873 | stage=0.332 | 
-9. page_163_img_1_0.jpeg | score=0.858 | stage=0.350 | 
-10. page_105_img_1_0.jpeg | score=0.825 | stage=0.580 | page=1.00</t>
+          <t xml:space="preserve">1. page_102_img_0_0.jpeg | score=1.423 | stage=0.712 | page=1.00; keyword=usb; section=usb
+2. page_104_img_0_0.jpeg | score=1.231 | stage=0.500 | page=1.00
+3. page_103_img_0_0.jpeg | score=1.187 | stage=0.500 | page=1.00
+4. page_105_img_0_0.jpeg | score=1.129 | stage=0.500 | page=1.00
+5. page_105_img_1_0.jpeg | score=0.957 | stage=0.500 | page=1.00
+6. page_101_img_0_0.jpeg | score=0.939 | stage=0.500 | page=1.00
+7. page_100_img_0_0.jpeg | score=0.894 | stage=0.500 | page=1.00
+8. page_401_img_0_0.jpeg | score=0.861 | stage=0.000
+9. page_401_img_1_0.jpeg | score=0.857 | stage=0.000
+10. page_119_img_0_0.jpeg | score=0.807 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -2979,12 +2995,12 @@
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="M33" s="0" t="inlineStr">
@@ -2992,28 +3008,24 @@
           <t>page_192_img_0_0.jpeg</t>
         </is>
       </c>
-      <c r="N33" s="0" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="N33" s="0"/>
       <c r="O33" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_181_img_0_0.jpeg | score=0.753 | stage=0.000 | 
-2. page_323_img_0_0.jpeg | score=0.738 | stage=0.000 | 
-3. page_84_img_0_0.jpeg | score=0.728 | stage=0.000 | 
-4. page_325_img_0_0.jpeg | score=0.681 | stage=0.000 | 
-5. page_323_img_1_0.jpeg | score=0.678 | stage=0.000 | 
-6. page_192_img_0_0.jpeg | score=0.659 | stage=0.000 | 
-7. page_324_img_0_0.jpeg | score=0.635 | stage=0.000 | 
-8. page_83_img_0_0.jpeg | score=0.587 | stage=0.000 | 
-9. page_196_img_0_0.jpeg | score=0.568 | stage=0.000 | 
-10. page_178_img_0_0.jpeg | score=0.536 | stage=0.000 | </t>
+          <t xml:space="preserve">1. page_181_img_0_0.jpeg | score=0.827 | stage=0.000
+2. page_182_img_0_0.jpeg | score=0.792 | stage=0.000
+3. page_195_img_0_0.jpeg | score=0.737 | stage=0.000
+4. page_195_img_2_0.jpeg | score=0.713 | stage=0.000
+5. page_178_img_0_0.jpeg | score=0.675 | stage=0.000
+6. page_188_img_0_0.jpeg | score=0.617 | stage=0.000
+7. page_189_img_0_0.jpeg | score=0.587 | stage=0.000
+8. page_184_img_0_0.jpeg | score=0.559 | stage=0.000
+9. page_298_img_2_0.jpeg | score=0.558 | stage=0.000
+10. page_293_img_1_0.jpeg | score=0.553 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -3095,16 +3107,16 @@
       </c>
       <c r="P34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_353_img_1_0.jpeg | score=1.368 | stage=0.685 | page=1.00; keyword=supervisor,password; section=supervisor password
-2. page_352_img_3_0.jpeg | score=1.274 | stage=0.614 | page=1.00; keyword=password
-3. page_353_img_0_0.png | score=1.091 | stage=0.685 | page=1.00; keyword=supervisor,password; section=supervisor password
-4. page_352_img_1_0.png | score=1.011 | stage=0.580 | page=1.00
-5. page_169_img_2_0.jpeg | score=0.828 | stage=0.332 | 
-6. page_330_img_0_0.jpeg | score=0.764 | stage=0.236 | 
-7. page_343_img_0_0.jpeg | score=0.745 | stage=0.651 | page=1.00; keyword=account; section=account
-8. page_147_img_0_0.jpeg | score=0.730 | stage=0.293 | 
-9. page_354_img_0_0.jpeg | score=0.682 | stage=0.580 | page=1.00
-10. page_349_img_0_0.jpeg | score=0.647 | stage=0.647 | page=1.00; keyword=lock,setting</t>
+          <t xml:space="preserve">1. page_353_img_1_0.jpeg | score=1.516 | stage=0.762 | page=1.00; keyword=supervisor,password,admin,safety password; section=supervisor password,safety password
+2. page_352_img_3_0.jpeg | score=1.431 | stage=0.662 | page=1.00; keyword=password,admin,safety password,lock; section=safety password
+3. page_353_img_0_0.png | score=1.320 | stage=0.762 | page=1.00; keyword=supervisor,password,admin,safety password; section=supervisor password,safety password
+4. page_352_img_1_0.png | score=1.242 | stage=0.662 | page=1.00; keyword=password,admin,safety password,lock; section=safety password
+5. page_354_img_0_0.jpeg | score=1.126 | stage=0.625 | page=1.00; keyword=supervisor,password; section=supervisor password
+6. page_350_img_0_0.jpeg | score=1.014 | stage=0.512 | page=1.00; keyword=setting
+7. page_285_img_0_0.jpeg | score=0.862 | stage=0.150 | keyword=password,admin,safety password,setting; section=safety password
+8. page_296_img_0_0.jpeg | score=0.756 | stage=0.013 | keyword=setting
+9. page_169_img_2_0.jpeg | score=0.742 | stage=0.000
+10. page_214_img_0_0.jpeg | score=0.726 | stage=0.150 | keyword=password,safety password,lock,setting; section=safety password</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3188,7 @@
       </c>
       <c r="N35" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O35" s="0" t="inlineStr">
@@ -3186,16 +3198,16 @@
       </c>
       <c r="P35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_181_img_0_0.jpeg | score=1.311 | stage=0.689 | page=1.00; keyword=recovery; section=recovery
-2. page_184_img_0_0.jpeg | score=1.199 | stage=0.580 | page=1.00
-3. page_178_img_0_0.jpeg | score=1.150 | stage=0.689 | page=1.00; keyword=recovery; section=recovery
-4. page_182_img_0_0.jpeg | score=1.006 | stage=0.689 | page=1.00; keyword=recovery; section=recovery
-5. page_179_img_1_0.jpeg | score=0.914 | stage=0.689 | page=1.00; keyword=recovery; section=recovery
-6. page_48_img_0_0.jpeg | score=0.811 | stage=0.346 | 
-7. page_49_img_0_0.jpeg | score=0.669 | stage=0.234 | 
-8. page_186_img_0_0.jpeg | score=0.664 | stage=0.580 | page=1.00
-9. page_92_img_1_0.jpeg | score=0.606 | stage=0.341 | 
-10. page_242_img_0_0.jpeg | score=0.577 | stage=0.231 | </t>
+          <t xml:space="preserve">1. page_181_img_0_0.jpeg | score=1.452 | stage=0.712 | page=1.00; keyword=recovery; section=recovery
+2. page_182_img_0_0.jpeg | score=1.413 | stage=0.712 | page=1.00; keyword=recovery; section=recovery
+3. page_184_img_0_0.jpeg | score=1.185 | stage=0.525 | page=1.00; keyword=joint,task
+4. page_186_img_0_0.jpeg | score=1.144 | stage=0.712 | page=1.00; keyword=recovery; section=recovery
+5. page_178_img_0_0.jpeg | score=0.972 | stage=0.450 | page=0.45; keyword=recovery,joint; section=recovery
+6. page_179_img_1_0.jpeg | score=0.785 | stage=0.350 | page=0.70
+7. page_177_img_1_0.jpeg | score=0.672 | stage=0.225 | page=0.45
+8. page_92_img_1_0.jpeg | score=0.619 | stage=0.213 | keyword=recovery; section=recovery
+9. page_48_img_0_0.jpeg | score=0.539 | stage=0.000
+10. page_24_img_0_0.jpeg | score=0.536 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3245,7 @@
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t>0.0129</t>
+          <t>0.0130</t>
         </is>
       </c>
       <c r="I36" s="0" t="inlineStr">
@@ -3273,16 +3285,16 @@
       </c>
       <c r="P36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_144_img_0_0.jpeg | score=0.837 | stage=0.000 | 
-2. page_144_img_1_0.jpeg | score=0.823 | stage=0.000 | 
-3. page_139_img_0_0.jpeg | score=0.802 | stage=0.000 | 
-4. page_133_img_0_0.jpeg | score=0.798 | stage=0.000 | 
-5. page_141_img_1_0.jpeg | score=0.793 | stage=0.000 | 
-6. page_142_img_1_0.jpeg | score=0.776 | stage=0.000 | 
-7. page_145_img_0_0.jpeg | score=0.768 | stage=0.000 | 
-8. page_142_img_0_0.jpeg | score=0.768 | stage=0.000 | 
-9. page_136_img_1_0.jpeg | score=0.755 | stage=0.000 | 
-10. page_136_img_0_0.png | score=0.750 | stage=0.000 | </t>
+          <t xml:space="preserve">1. page_144_img_0_0.jpeg | score=0.868 | stage=0.000
+2. page_144_img_1_0.jpeg | score=0.865 | stage=0.000
+3. page_140_img_0_0.jpeg | score=0.845 | stage=0.000
+4. page_141_img_1_0.jpeg | score=0.829 | stage=0.000
+5. page_133_img_0_0.jpeg | score=0.806 | stage=0.000
+6. page_136_img_0_0.png | score=0.789 | stage=0.000
+7. page_95_img_0_0.jpeg | score=0.755 | stage=0.000
+8. page_143_img_1_0.jpeg | score=0.740 | stage=0.000
+9. page_143_img_0_0.jpeg | score=0.739 | stage=0.000
+10. page_145_img_0_0.jpeg | score=0.734 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3336,7 @@
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t>0.0528</t>
+          <t>0.0529</t>
         </is>
       </c>
       <c r="I37" s="0" t="inlineStr">
@@ -3354,26 +3366,26 @@
       </c>
       <c r="N37" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O37" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_236_img_0_0.jpeg | score=1.185 | stage=0.630 | page=1.00; section=safety settings
-2. page_232_img_0_0.jpeg | score=1.180 | stage=0.781 | page=1.00; keyword=point 1,point 2,point; section=safety settings,point
-3. page_243_img_0_0.jpeg | score=1.127 | stage=0.630 | page=1.00; section=safety settings
-4. page_242_img_0_0.jpeg | score=1.109 | stage=0.630 | page=1.00; section=safety settings
-5. page_230_img_1_0.jpeg | score=1.088 | stage=0.630 | page=1.00; section=safety settings
-6. page_244_img_0_0.jpeg | score=1.081 | stage=0.630 | page=1.00; section=safety settings
-7. page_240_img_0_0.jpeg | score=1.052 | stage=0.630 | page=1.00; section=safety settings
-8. page_238_img_1_0.jpeg | score=1.040 | stage=0.698 | page=1.00; keyword=zone,safety zone; section=safety settings
-9. page_237_img_0_0.jpeg | score=1.024 | stage=0.630 | page=1.00; section=safety settings
-10. page_241_img_0_0.jpeg | score=1.007 | stage=0.630 | page=1.00; section=safety settings</t>
+          <t xml:space="preserve">1. page_238_img_0_0.jpeg | score=1.553 | stage=0.792 | page=1.00; keyword=space limit,zone; section=safety settings,space limit
+2. page_237_img_0_0.jpeg | score=1.506 | stage=0.792 | page=1.00; keyword=space limit,zone; section=safety settings,space limit
+3. page_239_img_0_0.jpeg | score=1.481 | stage=0.792 | page=1.00; keyword=space limit,zone; section=safety settings,space limit
+4. page_232_img_0_0.jpeg | score=1.427 | stage=0.817 | page=1.00; keyword=point 1,point 2,3 point,point; section=safety settings,point
+5. page_240_img_0_0.jpeg | score=1.388 | stage=0.633 | page=1.00; section=safety settings
+6. page_238_img_1_0.jpeg | score=1.329 | stage=0.792 | page=1.00; keyword=space limit,zone; section=safety settings,space limit
+7. page_233_img_1_0.jpeg | score=1.323 | stage=0.804 | page=1.00; keyword=point 1,point 2,point; section=safety settings,point
+8. page_235_img_1_0.jpeg | score=1.277 | stage=0.792 | page=1.00; keyword=point 1,point; section=safety settings,point
+9. page_235_img_0_0.jpeg | score=1.270 | stage=0.792 | page=1.00; keyword=point 1,point; section=safety settings,point
+10. page_236_img_0_0.jpeg | score=1.235 | stage=0.633 | page=1.00; section=safety settings</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3427,7 @@
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t>0.1408</t>
+          <t>0.1409</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
@@ -3445,26 +3457,26 @@
       </c>
       <c r="N38" s="0" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O38" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_309_img_1_0.jpeg | score=1.260 | stage=0.580 | page=1.00
-2. page_308_img_1_0.jpeg | score=1.245 | stage=0.580 | page=1.00
-3. page_299_img_0_0.jpeg | score=1.175 | stage=0.580 | page=1.00
-4. page_296_img_0_0.jpeg | score=1.092 | stage=0.580 | page=1.00
-5. page_311_img_0_0.jpeg | score=1.017 | stage=0.580 | page=1.00
-6. page_310_img_1_0.jpeg | score=1.012 | stage=0.580 | page=1.00
-7. page_309_img_0_0.jpeg | score=1.008 | stage=0.580 | page=1.00
-8. page_307_img_1_0.jpeg | score=0.968 | stage=0.580 | page=1.00
-9. page_307_img_0_0.jpeg | score=0.956 | stage=0.580 | page=1.00
-10. page_292_img_0_0.jpeg | score=0.937 | stage=0.580 | page=1.00</t>
+          <t xml:space="preserve">1. page_310_img_1_0.jpeg | score=1.401 | stage=0.658 | page=1.00; keyword=custom code,drl; section=custom code
+2. page_305_img_0_0.jpeg | score=1.258 | stage=0.500 | page=1.00
+3. page_304_img_0_0.jpeg | score=1.131 | stage=0.658 | page=1.00; keyword=force control,compliance; section=force control
+4. page_303_img_0_0.jpeg | score=1.127 | stage=0.512 | page=1.00; keyword=compliance
+5. page_306_img_0_0.jpeg | score=1.126 | stage=0.500 | page=1.00
+6. page_311_img_0_0.jpeg | score=1.124 | stage=0.512 | page=1.00; keyword=set_external_force_reset
+7. page_309_img_0_0.jpeg | score=1.122 | stage=0.646 | page=1.00; keyword=custom code; section=custom code
+8. page_309_img_1_0.jpeg | score=1.113 | stage=0.646 | page=1.00; keyword=custom code; section=custom code
+9. page_307_img_1_0.jpeg | score=1.047 | stage=0.500 | page=1.00
+10. page_302_img_1_0.jpeg | score=0.924 | stage=0.512 | page=1.00; keyword=compliance</t>
         </is>
       </c>
     </row>
@@ -3546,16 +3558,16 @@
       </c>
       <c r="P39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_154_img_1_0.jpeg | score=1.308 | stage=0.681 | page=1.00; keyword=ethernet,ip,adapter
-2. page_155_img_1_0.jpeg | score=1.300 | stage=0.681 | page=1.00; keyword=ethernet,ip,adapter
-3. page_168_img_0_0.jpeg | score=0.799 | stage=0.284 | 
-4. page_357_img_0_0.jpeg | score=0.761 | stage=0.233 | 
-5. page_299_img_0_0.jpeg | score=0.716 | stage=0.234 | 
-6. page_139_img_0_0.jpeg | score=0.715 | stage=0.350 | 
-7. page_292_img_0_0.jpeg | score=0.639 | stage=0.231 | 
-8. page_386_img_1_0.jpeg | score=0.625 | stage=0.297 | 
-9. page_298_img_2_0.jpeg | score=0.623 | stage=0.232 | 
-10. page_220_img_0_0.jpeg | score=0.593 | stage=0.293 | </t>
+          <t xml:space="preserve">1. page_154_img_1_0.jpeg | score=1.488 | stage=0.762 | page=1.00; keyword=profinet,slot,ethernet,ip; section=profinet
+2. page_155_img_1_0.jpeg | score=1.364 | stage=0.537 | page=1.00; keyword=slot,slot#1,gpr
+3. page_101_img_0_0.jpeg | score=0.788 | stage=0.000
+4. page_102_img_0_0.jpeg | score=0.653 | stage=0.013 | keyword=ip
+5. page_357_img_0_0.jpeg | score=0.614 | stage=0.000
+6. page_100_img_0_0.jpeg | score=0.538 | stage=0.000
+7. page_220_img_0_0.jpeg | score=0.533 | stage=0.000
+8. page_387_img_0_0.jpeg | score=0.529 | stage=0.000
+9. page_388_img_2_0.jpeg | score=0.487 | stage=0.000
+10. page_292_img_0_0.jpeg | score=0.397 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -3637,16 +3649,16 @@
       </c>
       <c r="P40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_83_img_0_0.jpeg | score=1.328 | stage=0.580 | page=1.00
-2. page_84_img_0_0.jpeg | score=1.153 | stage=0.580 | page=1.00
-3. page_104_img_0_0.jpeg | score=1.077 | stage=0.580 | page=1.00
-4. page_85_img_0_0.jpeg | score=0.944 | stage=0.580 | page=1.00
-5. page_98_img_0_0.jpeg | score=0.934 | stage=0.580 | page=1.00
-6. page_96_img_0_0.jpeg | score=0.915 | stage=0.580 | page=1.00
-7. page_86_img_0_0.jpeg | score=0.872 | stage=0.580 | page=1.00
-8. page_103_img_0_0.jpeg | score=0.851 | stage=0.580 | page=1.00
-9. page_105_img_1_0.jpeg | score=0.835 | stage=0.580 | page=1.00
-10. page_105_img_0_0.jpeg | score=0.833 | stage=0.580 | page=1.00</t>
+          <t xml:space="preserve">1. page_83_img_0_0.jpeg | score=1.387 | stage=0.500 | page=1.00
+2. page_104_img_0_0.jpeg | score=1.196 | stage=0.500 | page=1.00
+3. page_84_img_0_0.jpeg | score=1.134 | stage=0.500 | page=1.00
+4. page_105_img_0_0.jpeg | score=1.118 | stage=0.500 | page=1.00
+5. page_103_img_0_0.jpeg | score=1.037 | stage=0.500 | page=1.00
+6. page_98_img_0_0.jpeg | score=1.010 | stage=0.500 | page=1.00
+7. page_98_img_1_0.jpeg | score=1.003 | stage=0.500 | page=1.00
+8. page_105_img_1_0.jpeg | score=0.954 | stage=0.500 | page=1.00
+9. page_101_img_0_0.jpeg | score=0.856 | stage=0.500 | page=1.00
+10. page_98_img_2_0.jpeg | score=0.844 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3730,7 @@
       </c>
       <c r="N41" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O41" s="0" t="inlineStr">
@@ -3728,16 +3740,16 @@
       </c>
       <c r="P41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_83_img_0_0.jpeg | score=1.344 | stage=0.580 | page=1.00
-2. page_119_img_1_0.jpeg | score=1.267 | stage=0.580 | page=1.00
-3. page_84_img_0_0.jpeg | score=1.262 | stage=0.580 | page=1.00
-4. page_120_img_0_0.jpeg | score=1.239 | stage=0.580 | page=1.00
-5. page_121_img_0_0.jpeg | score=1.219 | stage=0.580 | page=1.00
-6. page_116_img_0_0.jpeg | score=1.213 | stage=0.580 | page=1.00
-7. page_123_img_0_0.jpeg | score=1.206 | stage=0.580 | page=1.00
-8. page_115_img_0_0.jpeg | score=1.171 | stage=0.580 | page=1.00
-9. page_125_img_0_0.jpeg | score=1.074 | stage=0.580 | page=1.00
-10. page_86_img_0_0.jpeg | score=1.056 | stage=0.580 | page=1.00</t>
+          <t xml:space="preserve">1. page_83_img_0_0.jpeg | score=1.396 | stage=0.500 | page=1.00
+2. page_119_img_0_0.jpeg | score=1.329 | stage=0.500 | page=1.00
+3. page_119_img_1_0.jpeg | score=1.312 | stage=0.500 | page=1.00
+4. page_84_img_0_0.jpeg | score=1.265 | stage=0.500 | page=1.00
+5. page_118_img_0_0.jpeg | score=1.242 | stage=0.500 | page=1.00
+6. page_120_img_0_0.jpeg | score=1.231 | stage=0.500 | page=1.00
+7. page_116_img_0_0.jpeg | score=1.051 | stage=0.225 | page=0.45
+8. page_88_img_1_0.jpeg | score=1.034 | stage=0.225 | page=0.45
+9. page_86_img_0_0.jpeg | score=0.889 | stage=0.500 | page=1.00
+10. page_401_img_1_0.jpeg | score=0.881 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3802,7 @@
       </c>
       <c r="K42" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L42" s="0" t="inlineStr">
@@ -3805,7 +3817,7 @@
       </c>
       <c r="N42" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O42" s="0" t="inlineStr">
@@ -3815,16 +3827,16 @@
       </c>
       <c r="P42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_120_img_0_0.jpeg | score=0.861 | stage=0.000 | 
-2. page_86_img_0_0.jpeg | score=0.833 | stage=0.000 | 
-3. page_121_img_0_0.jpeg | score=0.822 | stage=0.000 | 
-4. page_119_img_1_0.jpeg | score=0.789 | stage=0.000 | 
-5. page_163_img_0_0.jpeg | score=0.740 | stage=0.000 | 
-6. page_133_img_0_0.jpeg | score=0.712 | stage=0.000 | 
-7. page_397_img_0_0.jpeg | score=0.681 | stage=0.000 | 
-8. page_398_img_0_0.jpeg | score=0.660 | stage=0.000 | 
-9. page_145_img_0_0.jpeg | score=0.658 | stage=0.000 | 
-10. page_147_img_0_0.jpeg | score=0.649 | stage=0.000 | </t>
+          <t xml:space="preserve">1. page_121_img_0_0.jpeg | score=0.885 | stage=0.000
+2. page_403_img_0_0.jpeg | score=0.868 | stage=0.000
+3. page_120_img_0_0.jpeg | score=0.830 | stage=0.000
+4. page_86_img_0_0.jpeg | score=0.809 | stage=0.000
+5. page_400_img_0_0.jpeg | score=0.745 | stage=0.000
+6. page_399_img_0_0.jpeg | score=0.743 | stage=0.000
+7. page_119_img_0_0.jpeg | score=0.741 | stage=0.000
+8. page_119_img_1_0.jpeg | score=0.733 | stage=0.000
+9. page_163_img_0_0.jpeg | score=0.697 | stage=0.000
+10. page_118_img_0_0.jpeg | score=0.676 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3908,7 @@
       </c>
       <c r="N43" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O43" s="0" t="inlineStr">
@@ -3906,16 +3918,16 @@
       </c>
       <c r="P43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_88_img_1_0.jpeg | score=1.293 | stage=0.580 | page=1.00
-2. page_88_img_0_0.jpeg | score=1.277 | stage=0.580 | page=1.00
-3. page_86_img_0_0.jpeg | score=1.160 | stage=0.580 | page=1.00
-4. page_89_img_1_0.jpeg | score=0.904 | stage=0.580 | page=1.00
-5. page_93_img_0_0.jpeg | score=0.903 | stage=0.406 | page=0.70
-6. page_120_img_0_0.jpeg | score=0.900 | stage=0.319 | 
-7. page_89_img_0_0.jpeg | score=0.895 | stage=0.580 | page=1.00
-8. page_85_img_0_0.jpeg | score=0.862 | stage=0.580 | page=1.00
-9. page_116_img_0_0.jpeg | score=0.849 | stage=0.302 | 
-10. page_113_img_0_0.jpeg | score=0.845 | stage=0.332 | </t>
+          <t xml:space="preserve">1. page_88_img_0_0.jpeg | score=1.290 | stage=0.500 | page=1.00
+2. page_88_img_1_0.jpeg | score=1.286 | stage=0.500 | page=1.00
+3. page_86_img_0_0.jpeg | score=1.212 | stage=0.500 | page=1.00
+4. page_400_img_0_0.jpeg | score=0.849 | stage=0.000
+5. page_121_img_0_0.jpeg | score=0.802 | stage=0.000
+6. page_399_img_0_0.jpeg | score=0.800 | stage=0.000
+7. page_85_img_0_0.jpeg | score=0.782 | stage=0.350 | page=0.70
+8. page_240_img_0_0.jpeg | score=0.771 | stage=0.000
+9. page_401_img_1_0.jpeg | score=0.761 | stage=0.000
+10. page_118_img_0_0.jpeg | score=0.746 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -3993,16 +4005,16 @@
       </c>
       <c r="P44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_89_img_1_0.jpeg | score=0.913 | stage=0.000 | 
-2. page_89_img_0_0.jpeg | score=0.858 | stage=0.000 | 
-3. page_24_img_0_0.jpeg | score=0.757 | stage=0.000 | 
-4. page_296_img_0_0.jpeg | score=0.700 | stage=0.000 | 
-5. page_88_img_1_0.jpeg | score=0.635 | stage=0.000 | 
-6. page_88_img_0_0.jpeg | score=0.625 | stage=0.000 | 
-7. page_352_img_3_0.jpeg | score=0.623 | stage=0.000 | 
-8. page_96_img_0_0.jpeg | score=0.589 | stage=0.000 | 
-9. page_48_img_0_0.jpeg | score=0.579 | stage=0.000 | 
-10. page_220_img_0_0.jpeg | score=0.574 | stage=0.000 | </t>
+          <t xml:space="preserve">1. page_89_img_1_0.jpeg | score=0.911 | stage=0.000
+2. page_89_img_0_0.jpeg | score=0.890 | stage=0.000
+3. page_24_img_0_0.jpeg | score=0.823 | stage=0.000
+4. page_220_img_0_0.jpeg | score=0.823 | stage=0.000
+5. page_103_img_0_0.jpeg | score=0.760 | stage=0.000
+6. page_293_img_1_0.jpeg | score=0.677 | stage=0.000
+7. page_88_img_1_0.jpeg | score=0.642 | stage=0.000
+8. page_352_img_3_0.jpeg | score=0.600 | stage=0.000
+9. page_88_img_0_0.jpeg | score=0.598 | stage=0.000
+10. page_104_img_0_0.jpeg | score=0.563 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -4084,16 +4096,16 @@
       </c>
       <c r="P45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_94_img_0_0.jpeg | score=1.302 | stage=0.580 | page=1.00
-2. page_95_img_0_0.jpeg | score=1.214 | stage=0.580 | page=1.00
-3. page_96_img_0_0.jpeg | score=1.138 | stage=0.580 | page=1.00
-4. page_163_img_0_0.jpeg | score=0.982 | stage=0.346 | 
-5. page_89_img_1_0.jpeg | score=0.947 | stage=0.337 | 
-6. page_163_img_1_0.jpeg | score=0.929 | stage=0.341 | 
-7. page_89_img_0_0.jpeg | score=0.886 | stage=0.332 | 
-8. page_125_img_0_0.jpeg | score=0.844 | stage=0.328 | 
-9. page_88_img_1_0.jpeg | score=0.833 | stage=0.311 | 
-10. page_88_img_0_0.jpeg | score=0.817 | stage=0.306 | </t>
+          <t xml:space="preserve">1. page_94_img_0_0.jpeg | score=1.388 | stage=0.500 | page=1.00
+2. page_95_img_0_0.jpeg | score=1.326 | stage=0.500 | page=1.00
+3. page_96_img_0_0.jpeg | score=1.210 | stage=0.500 | page=1.00
+4. page_93_img_0_0.jpeg | score=1.071 | stage=0.500 | page=1.00
+5. page_163_img_0_0.jpeg | score=0.855 | stage=0.000
+6. page_89_img_1_0.jpeg | score=0.844 | stage=0.000
+7. page_163_img_1_0.jpeg | score=0.825 | stage=0.000
+8. page_89_img_0_0.jpeg | score=0.821 | stage=0.000
+9. page_125_img_0_0.jpeg | score=0.777 | stage=0.000
+10. page_88_img_1_0.jpeg | score=0.729 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4143,7 @@
       </c>
       <c r="H46" s="0" t="inlineStr">
         <is>
-          <t>0.0027</t>
+          <t>0.0028</t>
         </is>
       </c>
       <c r="I46" s="0" t="inlineStr">
@@ -4161,7 +4173,7 @@
       </c>
       <c r="N46" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O46" s="0" t="inlineStr">
@@ -4171,16 +4183,16 @@
       </c>
       <c r="P46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_113_img_0_0.jpeg | score=0.825 | stage=0.000 | 
-2. page_114_img_0_0.jpeg | score=0.822 | stage=0.000 | 
-3. page_123_img_0_0.jpeg | score=0.810 | stage=0.000 | 
-4. page_84_img_0_0.jpeg | score=0.809 | stage=0.000 | 
-5. page_98_img_1_0.jpeg | score=0.765 | stage=0.000 | 
-6. page_115_img_0_0.jpeg | score=0.750 | stage=0.000 | 
-7. page_93_img_0_0.jpeg | score=0.736 | stage=0.000 | 
-8. page_192_img_0_0.jpeg | score=0.641 | stage=0.000 | 
-9. page_88_img_0_0.jpeg | score=0.603 | stage=0.000 | 
-10. page_88_img_1_0.jpeg | score=0.603 | stage=0.000 | </t>
+          <t xml:space="preserve">1. page_113_img_0_0.jpeg | score=0.832 | stage=0.000
+2. page_98_img_0_0.jpeg | score=0.809 | stage=0.000
+3. page_98_img_1_0.jpeg | score=0.805 | stage=0.000
+4. page_123_img_0_0.jpeg | score=0.789 | stage=0.000
+5. page_114_img_0_0.jpeg | score=0.758 | stage=0.000
+6. page_84_img_0_0.jpeg | score=0.723 | stage=0.000
+7. page_115_img_0_0.jpeg | score=0.657 | stage=0.000
+8. page_98_img_2_0.jpeg | score=0.634 | stage=0.000
+9. page_93_img_0_0.jpeg | score=0.613 | stage=0.000
+10. page_188_img_0_0.jpeg | score=0.583 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -4237,24 +4249,24 @@
       </c>
       <c r="K47" s="0" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L47" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M47" s="0" t="inlineStr">
+        <is>
+          <t>page_119_img_1_0.jpeg</t>
+        </is>
+      </c>
+      <c r="N47" s="0" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L47" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M47" s="0" t="inlineStr">
-        <is>
-          <t>page_119_img_1_0.jpeg</t>
-        </is>
-      </c>
-      <c r="N47" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="O47" s="0" t="inlineStr">
         <is>
           <t>O</t>
@@ -4262,16 +4274,16 @@
       </c>
       <c r="P47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_120_img_0_0.jpeg | score=1.293 | stage=0.580 | page=1.00
-2. page_121_img_0_0.jpeg | score=1.254 | stage=0.580 | page=1.00
-3. page_119_img_1_0.jpeg | score=1.247 | stage=0.580 | page=1.00
-4. page_116_img_0_0.jpeg | score=1.191 | stage=0.580 | page=1.00
-5. page_115_img_0_0.jpeg | score=1.176 | stage=0.580 | page=1.00
-6. page_123_img_0_0.jpeg | score=1.094 | stage=0.580 | page=1.00
-7. page_119_img_0_0.jpeg | score=0.993 | stage=0.580 | page=1.00
-8. page_118_img_0_0.jpeg | score=0.970 | stage=0.580 | page=1.00
-9. page_114_img_0_0.jpeg | score=0.928 | stage=0.580 | page=1.00
-10. page_124_img_0_0.jpeg | score=0.903 | stage=0.580 | page=1.00</t>
+          <t xml:space="preserve">1. page_120_img_0_0.jpeg | score=1.348 | stage=0.500 | page=1.00
+2. page_119_img_1_0.jpeg | score=1.299 | stage=0.500 | page=1.00
+3. page_119_img_0_0.jpeg | score=1.295 | stage=0.500 | page=1.00
+4. page_118_img_0_0.jpeg | score=1.281 | stage=0.500 | page=1.00
+5. page_116_img_0_0.jpeg | score=1.241 | stage=0.500 | page=1.00
+6. page_115_img_0_0.jpeg | score=1.151 | stage=0.500 | page=1.00
+7. page_121_img_0_0.jpeg | score=1.093 | stage=0.350 | page=0.70
+8. page_402_img_0_0.jpeg | score=0.868 | stage=0.000
+9. page_400_img_0_0.jpeg | score=0.840 | stage=0.000
+10. page_403_img_0_0.jpeg | score=0.780 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4355,7 @@
       </c>
       <c r="N48" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O48" s="0" t="inlineStr">
@@ -4353,16 +4365,16 @@
       </c>
       <c r="P48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_120_img_0_0.jpeg | score=1.327 | stage=0.580 | page=1.00
-2. page_121_img_0_0.jpeg | score=1.311 | stage=0.580 | page=1.00
-3. page_119_img_1_0.jpeg | score=1.307 | stage=0.580 | page=1.00
-4. page_116_img_0_0.jpeg | score=1.140 | stage=0.580 | page=1.00
-5. page_123_img_0_0.jpeg | score=1.103 | stage=0.580 | page=1.00
-6. page_115_img_0_0.jpeg | score=1.052 | stage=0.580 | page=1.00
-7. page_118_img_0_0.jpeg | score=1.042 | stage=0.580 | page=1.00
-8. page_119_img_0_0.jpeg | score=1.036 | stage=0.580 | page=1.00
-9. page_83_img_0_0.jpeg | score=0.935 | stage=0.306 | 
-10. page_124_img_0_0.jpeg | score=0.932 | stage=0.580 | page=1.00</t>
+          <t xml:space="preserve">1. page_118_img_0_0.jpeg | score=1.398 | stage=0.500 | page=1.00
+2. page_119_img_1_0.jpeg | score=1.362 | stage=0.500 | page=1.00
+3. page_119_img_0_0.jpeg | score=1.343 | stage=0.500 | page=1.00
+4. page_120_img_0_0.jpeg | score=1.232 | stage=0.500 | page=1.00
+5. page_121_img_0_0.jpeg | score=1.083 | stage=0.500 | page=1.00
+6. page_400_img_0_0.jpeg | score=0.887 | stage=0.000
+7. page_116_img_0_0.jpeg | score=0.869 | stage=0.225 | page=0.45
+8. page_402_img_0_0.jpeg | score=0.805 | stage=0.000
+9. page_401_img_1_0.jpeg | score=0.799 | stage=0.000
+10. page_403_img_0_0.jpeg | score=0.773 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4446,7 @@
       </c>
       <c r="N49" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O49" s="0" t="inlineStr">
@@ -4444,16 +4456,16 @@
       </c>
       <c r="P49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_93_img_0_0.jpeg | score=1.355 | stage=0.647 | page=1.00; keyword=m6,9 nm
-2. page_123_img_0_0.jpeg | score=1.318 | stage=0.580 | page=1.00
-3. page_94_img_0_0.jpeg | score=1.190 | stage=0.580 | page=1.00
-4. page_121_img_0_0.jpeg | score=1.143 | stage=0.580 | page=1.00
-5. page_95_img_0_0.jpeg | score=1.135 | stage=0.580 | page=1.00
-6. page_96_img_0_0.jpeg | score=1.088 | stage=0.580 | page=1.00
-7. page_124_img_0_0.jpeg | score=1.051 | stage=0.647 | page=1.00; keyword=m6,9 nm
-8. page_125_img_0_0.jpeg | score=0.983 | stage=0.580 | page=1.00
-9. page_84_img_0_0.jpeg | score=0.944 | stage=0.332 | 
-10. page_119_img_1_0.jpeg | score=0.933 | stage=0.580 | page=1.00</t>
+          <t xml:space="preserve">1. page_123_img_0_0.jpeg | score=1.412 | stage=0.525 | page=1.00; keyword=m6,9 nm
+2. page_93_img_0_0.jpeg | score=1.382 | stage=0.525 | page=1.00; keyword=m6,9 nm
+3. page_94_img_0_0.jpeg | score=1.293 | stage=0.500 | page=1.00
+4. page_95_img_0_0.jpeg | score=1.193 | stage=0.500 | page=1.00
+5. page_124_img_0_0.jpeg | score=1.108 | stage=0.525 | page=1.00; keyword=m6,9 nm
+6. page_121_img_0_0.jpeg | score=1.063 | stage=0.350 | page=0.70
+7. page_92_img_1_0.jpeg | score=0.894 | stage=0.500 | page=1.00
+8. page_84_img_0_0.jpeg | score=0.827 | stage=0.000
+9. page_96_img_0_0.jpeg | score=0.814 | stage=0.350 | page=0.70
+10. page_205_img_1_0.jpeg | score=0.775 | stage=0.013 | keyword=tool</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4533,7 @@
       </c>
       <c r="N50" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O50" s="0" t="inlineStr">
@@ -4531,16 +4543,16 @@
       </c>
       <c r="P50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_88_img_1_0.jpeg | score=0.853 | stage=0.000 | 
-2. page_125_img_0_0.jpeg | score=0.838 | stage=0.000 | 
-3. page_88_img_0_0.jpeg | score=0.834 | stage=0.000 | 
-4. page_163_img_0_0.jpeg | score=0.808 | stage=0.000 | 
-5. page_121_img_0_0.jpeg | score=0.779 | stage=0.000 | 
-6. page_163_img_1_0.jpeg | score=0.761 | stage=0.000 | 
-7. page_144_img_0_0.jpeg | score=0.750 | stage=0.000 | 
-8. page_397_img_0_0.jpeg | score=0.737 | stage=0.000 | 
-9. page_144_img_1_0.jpeg | score=0.735 | stage=0.000 | 
-10. page_86_img_0_0.jpeg | score=0.722 | stage=0.000 | </t>
+          <t xml:space="preserve">1. page_125_img_0_0.jpeg | score=0.892 | stage=0.000
+2. page_88_img_1_0.jpeg | score=0.871 | stage=0.000
+3. page_121_img_0_0.jpeg | score=0.810 | stage=0.000
+4. page_163_img_0_0.jpeg | score=0.782 | stage=0.000
+5. page_89_img_1_0.jpeg | score=0.765 | stage=0.000
+6. page_144_img_0_0.jpeg | score=0.757 | stage=0.000
+7. page_144_img_1_0.jpeg | score=0.754 | stage=0.000
+8. page_163_img_1_0.jpeg | score=0.753 | stage=0.000
+9. page_86_img_0_0.jpeg | score=0.729 | stage=0.000
+10. page_120_img_0_0.jpeg | score=0.717 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -4622,16 +4634,16 @@
       </c>
       <c r="P51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_130_img_0_0.jpeg | score=1.344 | stage=0.681 | page=1.00; keyword=pnp,photo coupler,+24v
-2. page_132_img_0_0.png | score=1.069 | stage=0.580 | page=1.00
-3. page_133_img_0_0.jpeg | score=0.907 | stage=0.580 | page=1.00
-4. page_347_img_0_0.jpeg | score=0.798 | stage=0.328 | 
-5. page_346_img_0_0.jpeg | score=0.798 | stage=0.332 | 
-6. page_136_img_0_0.png | score=0.760 | stage=0.284 | page=0.45
-7. page_348_img_0_0.jpeg | score=0.758 | stage=0.341 | 
-8. page_136_img_1_0.jpeg | score=0.750 | stage=0.311 | page=0.45
-9. page_139_img_0_0.jpeg | score=0.740 | stage=0.218 | 
-10. page_344_img_0_0.jpeg | score=0.705 | stage=0.337 | </t>
+          <t xml:space="preserve">1. page_130_img_0_0.jpeg | score=1.408 | stage=0.550 | page=1.00; keyword=pnp,photo coupler,+24v,open
+2. page_132_img_0_0.png | score=1.264 | stage=0.500 | page=1.00
+3. page_336_img_0_0.jpeg | score=0.845 | stage=0.000
+4. page_335_img_1_0.jpeg | score=0.800 | stage=0.000
+5. page_335_img_2_0.jpeg | score=0.724 | stage=0.000
+6. page_133_img_0_0.jpeg | score=0.697 | stage=0.500 | page=1.00
+7. page_140_img_0_0.jpeg | score=0.685 | stage=0.000
+8. page_334_img_0_0.jpeg | score=0.644 | stage=0.000
+9. page_135_img_0_0.jpeg | score=0.642 | stage=0.225 | page=0.45
+10. page_335_img_0_0.jpeg | score=0.635 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -4713,16 +4725,16 @@
       </c>
       <c r="P52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_132_img_0_0.png | score=1.288 | stage=0.580 | page=1.00
-2. page_137_img_0_0.jpeg | score=1.253 | stage=0.580 | page=1.00
-3. page_136_img_1_0.jpeg | score=1.216 | stage=0.580 | page=1.00
-4. page_130_img_0_0.jpeg | score=1.172 | stage=0.580 | page=1.00
-5. page_136_img_0_0.png | score=1.126 | stage=0.580 | page=1.00
-6. page_135_img_0_0.jpeg | score=1.016 | stage=0.580 | page=1.00
-7. page_133_img_0_0.jpeg | score=1.009 | stage=0.580 | page=1.00
-8. page_138_img_0_0.jpeg | score=0.997 | stage=0.580 | page=1.00
-9. page_138_img_1_0.jpeg | score=0.965 | stage=0.580 | page=1.00
-10. page_128_img_0_0.jpeg | score=0.856 | stage=0.406 | page=0.70</t>
+          <t xml:space="preserve">1. page_132_img_0_0.png | score=1.332 | stage=0.500 | page=1.00
+2. page_135_img_0_0.jpeg | score=1.242 | stage=0.500 | page=1.00
+3. page_130_img_0_0.jpeg | score=1.219 | stage=0.500 | page=1.00
+4. page_133_img_0_0.jpeg | score=1.054 | stage=0.500 | page=1.00
+5. page_336_img_0_0.jpeg | score=0.871 | stage=0.000
+6. page_338_img_0_0.jpeg | score=0.768 | stage=0.000
+7. page_333_img_0_0.jpeg | score=0.709 | stage=0.000
+8. page_136_img_1_0.jpeg | score=0.704 | stage=0.350 | page=0.70
+9. page_335_img_1_0.jpeg | score=0.697 | stage=0.000
+10. page_136_img_0_0.png | score=0.681 | stage=0.350 | page=0.70</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4772,7 @@
       </c>
       <c r="H53" s="0" t="inlineStr">
         <is>
-          <t>0.0092</t>
+          <t>0.0093</t>
         </is>
       </c>
       <c r="I53" s="0" t="inlineStr">
@@ -4790,7 +4802,7 @@
       </c>
       <c r="N53" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O53" s="0" t="inlineStr">
@@ -4800,16 +4812,16 @@
       </c>
       <c r="P53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_147_img_0_0.jpeg | score=0.864 | stage=0.000 | 
-2. page_145_img_0_0.jpeg | score=0.844 | stage=0.000 | 
-3. page_133_img_0_0.jpeg | score=0.842 | stage=0.000 | 
-4. page_139_img_0_0.jpeg | score=0.826 | stage=0.000 | 
-5. page_144_img_0_0.jpeg | score=0.799 | stage=0.000 | 
-6. page_142_img_0_0.jpeg | score=0.797 | stage=0.000 | 
-7. page_144_img_1_0.jpeg | score=0.784 | stage=0.000 | 
-8. page_142_img_1_0.jpeg | score=0.772 | stage=0.000 | 
-9. page_242_img_0_0.jpeg | score=0.751 | stage=0.000 | 
-10. page_137_img_0_0.jpeg | score=0.672 | stage=0.000 | </t>
+          <t xml:space="preserve">1. page_133_img_0_0.jpeg | score=0.874 | stage=0.000
+2. page_145_img_0_0.jpeg | score=0.865 | stage=0.000
+3. page_143_img_1_0.jpeg | score=0.797 | stage=0.000
+4. page_143_img_0_0.jpeg | score=0.795 | stage=0.000
+5. page_102_img_0_0.jpeg | score=0.794 | stage=0.000
+6. page_144_img_0_0.jpeg | score=0.742 | stage=0.000
+7. page_144_img_1_0.jpeg | score=0.738 | stage=0.000
+8. page_397_img_0_0.jpeg | score=0.728 | stage=0.000
+9. page_139_img_0_0.jpeg | score=0.727 | stage=0.000
+10. page_216_img_0_0.jpeg | score=0.702 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -4891,16 +4903,16 @@
       </c>
       <c r="P54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_137_img_0_0.jpeg | score=1.304 | stage=0.580 | page=1.00
-2. page_136_img_1_0.jpeg | score=1.242 | stage=0.580 | page=1.00
-3. page_136_img_0_0.png | score=1.236 | stage=0.580 | page=1.00
-4. page_145_img_0_0.jpeg | score=1.199 | stage=0.580 | page=1.00
-5. page_139_img_0_0.jpeg | score=1.155 | stage=0.580 | page=1.00
-6. page_142_img_0_0.jpeg | score=1.130 | stage=0.580 | page=1.00
-7. page_138_img_0_0.jpeg | score=1.124 | stage=0.580 | page=1.00
-8. page_142_img_1_0.jpeg | score=1.109 | stage=0.580 | page=1.00
-9. page_141_img_1_0.jpeg | score=1.105 | stage=0.580 | page=1.00
-10. page_144_img_0_0.jpeg | score=1.078 | stage=0.580 | page=1.00</t>
+          <t xml:space="preserve">1. page_137_img_0_0.jpeg | score=1.491 | stage=0.712 | page=1.00; keyword=tben; section=tben
+2. page_138_img_0_0.jpeg | score=1.384 | stage=0.712 | page=1.00; keyword=tben; section=tben
+3. page_136_img_0_0.png | score=1.364 | stage=0.500 | page=1.00
+4. page_138_img_1_0.jpeg | score=1.329 | stage=0.712 | page=1.00; keyword=tben; section=tben
+5. page_136_img_1_0.jpeg | score=1.317 | stage=0.500 | page=1.00
+6. page_135_img_0_0.jpeg | score=1.299 | stage=0.500 | page=1.00
+7. page_140_img_0_0.jpeg | score=1.161 | stage=0.500 | page=1.00
+8. page_139_img_0_0.jpeg | score=1.007 | stage=0.500 | page=1.00
+9. page_133_img_0_0.jpeg | score=0.985 | stage=0.225 | page=0.45
+10. page_141_img_1_0.jpeg | score=0.963 | stage=0.350 | page=0.70</t>
         </is>
       </c>
     </row>
@@ -4982,16 +4994,16 @@
       </c>
       <c r="P55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_139_img_0_0.jpeg | score=1.382 | stage=0.722 | page=1.00; keyword=o,16; section=o
-2. page_144_img_0_0.jpeg | score=1.372 | stage=0.722 | page=1.00; keyword=o,controller; section=o
-3. page_144_img_1_0.jpeg | score=1.357 | stage=0.722 | page=1.00; keyword=o,controller; section=o
-4. page_145_img_0_0.jpeg | score=1.304 | stage=0.689 | page=1.00; keyword=o; section=o
-5. page_137_img_0_0.jpeg | score=1.261 | stage=0.689 | page=1.00; keyword=o; section=o
-6. page_142_img_1_0.jpeg | score=1.233 | stage=0.689 | page=1.00; keyword=o; section=o
-7. page_141_img_1_0.jpeg | score=1.190 | stage=0.689 | page=1.00; keyword=o; section=o
-8. page_142_img_0_0.jpeg | score=1.184 | stage=0.689 | page=1.00; keyword=o; section=o
-9. page_147_img_0_0.jpeg | score=1.131 | stage=0.722 | page=1.00; keyword=o,controller; section=o
-10. page_136_img_1_0.jpeg | score=1.096 | stage=0.515 | page=0.70; keyword=o; section=o</t>
+          <t xml:space="preserve">1. page_139_img_0_0.jpeg | score=1.524 | stage=0.725 | page=1.00; keyword=o,16; section=o
+2. page_140_img_0_0.jpeg | score=1.491 | stage=0.725 | page=1.00; keyword=o,16; section=o
+3. page_144_img_0_0.jpeg | score=1.452 | stage=0.725 | page=1.00; keyword=o,controller; section=o
+4. page_144_img_1_0.jpeg | score=1.445 | stage=0.725 | page=1.00; keyword=o,controller; section=o
+5. page_141_img_1_0.jpeg | score=1.373 | stage=0.712 | page=1.00; keyword=o; section=o
+6. page_145_img_0_0.jpeg | score=1.286 | stage=0.725 | page=1.00; keyword=o,controller; section=o
+7. page_138_img_0_0.jpeg | score=1.264 | stage=0.712 | page=1.00; keyword=o; section=o
+8. page_143_img_1_0.jpeg | score=1.262 | stage=0.725 | page=1.00; keyword=o,16; section=o
+9. page_143_img_0_0.jpeg | score=1.257 | stage=0.725 | page=1.00; keyword=o,16; section=o
+10. page_138_img_1_0.jpeg | score=1.135 | stage=0.712 | page=1.00; keyword=o; section=o</t>
         </is>
       </c>
     </row>
@@ -5073,16 +5085,16 @@
       </c>
       <c r="P56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_141_img_1_0.jpeg | score=1.343 | stage=0.681 | page=1.00; keyword=tbco,oxx,gio
-2. page_142_img_0_0.jpeg | score=1.262 | stage=0.614 | page=1.00; keyword=tbco
-3. page_142_img_1_0.jpeg | score=1.244 | stage=0.614 | page=1.00; keyword=tbco
-4. page_145_img_0_0.jpeg | score=1.157 | stage=0.580 | page=1.00
-5. page_144_img_0_0.jpeg | score=1.115 | stage=0.614 | page=1.00; keyword=gio
-6. page_144_img_1_0.jpeg | score=1.095 | stage=0.614 | page=1.00; keyword=gio
-7. page_143_img_1_0.jpeg | score=0.996 | stage=0.614 | page=1.00; keyword=tbco
-8. page_143_img_0_0.jpeg | score=0.993 | stage=0.614 | page=1.00; keyword=tbco
-9. page_137_img_0_0.jpeg | score=0.962 | stage=0.406 | page=0.70
-10. page_133_img_0_0.jpeg | score=0.873 | stage=0.319 | </t>
+          <t xml:space="preserve">1. page_141_img_1_0.jpeg | score=1.420 | stage=0.537 | page=1.00; keyword=tbco,oxx,gio
+2. page_142_img_1_0.jpeg | score=1.381 | stage=0.537 | page=1.00; keyword=tbco,oxx,gio
+3. page_142_img_0_0.jpeg | score=1.368 | stage=0.537 | page=1.00; keyword=tbco,oxx,gio
+4. page_143_img_1_0.jpeg | score=1.272 | stage=0.500 | page=1.00
+5. page_143_img_0_0.jpeg | score=1.268 | stage=0.500 | page=1.00
+6. page_140_img_0_0.jpeg | score=1.206 | stage=0.500 | page=1.00
+7. page_141_img_0_0.jpeg | score=1.201 | stage=0.537 | page=1.00; keyword=tbco,oxx,gio
+8. page_144_img_0_0.jpeg | score=1.139 | stage=0.512 | page=1.00; keyword=gio
+9. page_145_img_0_0.jpeg | score=1.135 | stage=0.362 | page=0.70; keyword=gio
+10. page_144_img_1_0.jpeg | score=1.133 | stage=0.512 | page=1.00; keyword=gio</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5166,7 @@
       </c>
       <c r="N57" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O57" s="0" t="inlineStr">
@@ -5164,16 +5176,16 @@
       </c>
       <c r="P57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_142_img_0_0.jpeg | score=1.367 | stage=0.781 | page=1.00; keyword=sink type,negative common,tbco; section=o,sink type
-2. page_142_img_1_0.jpeg | score=1.338 | stage=0.781 | page=1.00; keyword=sink type,negative common,tbco; section=o,sink type
-3. page_144_img_0_0.jpeg | score=1.279 | stage=0.664 | page=1.00; keyword=gio; section=o
-4. page_141_img_1_0.jpeg | score=1.268 | stage=0.731 | page=1.00; keyword=oxx,gio,tbco; section=o
-5. page_144_img_1_0.jpeg | score=1.262 | stage=0.664 | page=1.00; keyword=gio; section=o
-6. page_139_img_0_0.jpeg | score=1.216 | stage=0.630 | page=1.00; section=o
-7. page_145_img_0_0.jpeg | score=1.190 | stage=0.630 | page=1.00; section=o
-8. page_143_img_1_0.jpeg | score=1.096 | stage=0.781 | page=1.00; keyword=sink type,negative common,tbco; section=o,sink type
-9. page_143_img_0_0.jpeg | score=1.093 | stage=0.781 | page=1.00; keyword=sink type,negative common,tbco; section=o,sink type
-10. page_137_img_0_0.jpeg | score=1.001 | stage=0.456 | page=0.70; section=o</t>
+          <t xml:space="preserve">1. page_142_img_1_0.jpeg | score=1.563 | stage=0.829 | page=1.00; keyword=sink type,negative common,oxx,gio; section=o,sink type
+2. page_142_img_0_0.jpeg | score=1.554 | stage=0.829 | page=1.00; keyword=sink type,negative common,oxx,gio; section=o,sink type
+3. page_143_img_1_0.jpeg | score=1.429 | stage=0.792 | page=1.00; keyword=sink type,negative common; section=o,sink type
+4. page_143_img_0_0.jpeg | score=1.424 | stage=0.792 | page=1.00; keyword=sink type,negative common; section=o,sink type
+5. page_140_img_0_0.jpeg | score=1.399 | stage=0.633 | page=1.00; section=o
+6. page_144_img_0_0.jpeg | score=1.395 | stage=0.646 | page=1.00; keyword=gio; section=o
+7. page_144_img_1_0.jpeg | score=1.389 | stage=0.646 | page=1.00; keyword=gio; section=o
+8. page_141_img_1_0.jpeg | score=1.355 | stage=0.671 | page=1.00; keyword=oxx,gio,tbco; section=o
+9. page_139_img_0_0.jpeg | score=1.241 | stage=0.633 | page=1.00; section=o
+10. page_145_img_0_0.jpeg | score=1.235 | stage=0.646 | page=1.00; keyword=gio; section=o</t>
         </is>
       </c>
     </row>
@@ -5215,7 +5227,7 @@
       </c>
       <c r="H58" s="0" t="inlineStr">
         <is>
-          <t>0.1485</t>
+          <t>0.1484</t>
         </is>
       </c>
       <c r="I58" s="0" t="inlineStr">
@@ -5255,16 +5267,16 @@
       </c>
       <c r="P58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_147_img_0_0.jpeg | score=1.441 | stage=0.799 | page=1.00; keyword=safety controller,si1,si2,si3; section=o
-2. page_145_img_0_0.jpeg | score=1.288 | stage=0.680 | page=1.00; section=safety i,o
-3. page_142_img_0_0.jpeg | score=1.224 | stage=0.630 | page=1.00; section=o
-4. page_142_img_1_0.jpeg | score=1.195 | stage=0.630 | page=1.00; section=o
-5. page_139_img_0_0.jpeg | score=1.173 | stage=0.630 | page=1.00; section=o
-6. page_144_img_0_0.jpeg | score=1.162 | stage=0.664 | page=1.00; keyword=safety controller; section=o
-7. page_144_img_1_0.jpeg | score=1.145 | stage=0.664 | page=1.00; keyword=safety controller; section=o
-8. page_143_img_0_0.jpeg | score=0.986 | stage=0.630 | page=1.00; section=o
-9. page_143_img_1_0.jpeg | score=0.983 | stage=0.630 | page=1.00; section=o
-10. page_148_img_0_0.jpeg | score=0.945 | stage=0.630 | page=1.00; section=o</t>
+          <t xml:space="preserve">1. page_147_img_0_0.jpeg | score=1.511 | stage=0.696 | page=1.00; keyword=safety controller,si1,si2,si3; section=o
+2. page_145_img_0_0.jpeg | score=1.494 | stage=0.779 | page=1.00; keyword=safety controller; section=safety i,o
+3. page_143_img_1_0.jpeg | score=1.421 | stage=0.767 | page=1.00; section=safety i,o
+4. page_143_img_0_0.jpeg | score=1.416 | stage=0.767 | page=1.00; section=safety i,o
+5. page_148_img_0_0.jpeg | score=1.330 | stage=0.646 | page=1.00; keyword=safety controller; section=o
+6. page_144_img_0_0.jpeg | score=1.328 | stage=0.779 | page=1.00; keyword=safety controller; section=safety i,o
+7. page_144_img_1_0.jpeg | score=1.321 | stage=0.779 | page=1.00; keyword=safety controller; section=safety i,o
+8. page_142_img_1_0.jpeg | score=0.920 | stage=0.483 | page=0.70; section=o
+9. page_142_img_0_0.jpeg | score=0.918 | stage=0.483 | page=0.70; section=o
+10. page_133_img_0_0.jpeg | score=0.811 | stage=0.133 | section=o</t>
         </is>
       </c>
     </row>
@@ -5346,16 +5358,16 @@
       </c>
       <c r="P59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_148_img_0_0.jpeg | score=1.333 | stage=0.715 | page=1.00; keyword=wan,tcp,ip,modbus
-2. page_355_img_1_0.jpeg | score=1.218 | stage=0.681 | page=1.00; keyword=ip,ethernet,profinet
-3. page_355_img_0_0.jpeg | score=1.186 | stage=0.647 | page=1.00; keyword=network,controller
-4. page_145_img_0_0.jpeg | score=1.098 | stage=0.580 | page=1.00
-5. page_354_img_0_0.jpeg | score=1.087 | stage=0.647 | page=1.00; keyword=network,controller
-6. page_154_img_1_0.jpeg | score=0.996 | stage=0.647 | page=1.00; keyword=ip,ethernet
-7. page_152_img_3_0.jpeg | score=0.960 | stage=0.580 | page=1.00
-8. page_151_img_2_0.jpeg | score=0.947 | stage=0.580 | page=1.00
-9. page_144_img_0_0.jpeg | score=0.944 | stage=0.295 | page=0.45; keyword=controller
-10. page_144_img_1_0.jpeg | score=0.927 | stage=0.295 | page=0.45; keyword=controller</t>
+          <t xml:space="preserve">1. page_148_img_0_0.jpeg | score=1.405 | stage=0.575 | page=1.00; keyword=wan,lan,tcp,ip
+2. page_355_img_1_0.jpeg | score=1.204 | stage=0.562 | page=1.00; keyword=ip,ethernet,profinet,network
+3. page_355_img_0_0.jpeg | score=1.197 | stage=0.562 | page=1.00; keyword=ip,ethernet,profinet,network
+4. page_354_img_0_0.jpeg | score=1.056 | stage=0.537 | page=1.00; keyword=ip,network,controller
+5. page_151_img_3_0.jpeg | score=1.005 | stage=0.512 | page=1.00; keyword=lan
+6. page_151_img_2_0.jpeg | score=1.002 | stage=0.512 | page=1.00; keyword=lan
+7. page_144_img_0_0.jpeg | score=0.984 | stage=0.238 | page=0.45; keyword=controller
+8. page_145_img_0_0.jpeg | score=0.983 | stage=0.362 | page=0.70; keyword=controller
+9. page_144_img_1_0.jpeg | score=0.979 | stage=0.238 | page=0.45; keyword=controller
+10. page_147_img_0_0.jpeg | score=0.880 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5439,7 @@
       </c>
       <c r="N60" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O60" s="0" t="inlineStr">
@@ -5437,16 +5449,16 @@
       </c>
       <c r="P60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_176_img_3_0.jpeg | score=1.286 | stage=0.681 | page=1.00; keyword=x,y,z
-2. page_177_img_1_0.jpeg | score=1.279 | stage=0.647 | page=1.00; keyword=x,y
-3. page_176_img_2_0.jpeg | score=1.266 | stage=0.647 | page=1.00; keyword=x,y
-4. page_176_img_1_0.png | score=1.030 | stage=0.647 | page=1.00; keyword=x,y
-5. page_176_img_0_0.png | score=1.026 | stage=0.647 | page=1.00; keyword=x,y
-6. page_175_img_1_0.jpeg | score=0.984 | stage=0.681 | page=1.00; keyword=x,y,z
-7. page_175_img_4_0.jpeg | score=0.981 | stage=0.681 | page=1.00; keyword=x,y,z
-8. page_175_img_3_0.jpeg | score=0.976 | stage=0.681 | page=1.00; keyword=x,y,z
-9. page_175_img_2_0.jpeg | score=0.970 | stage=0.681 | page=1.00; keyword=x,y,z
-10. page_378_img_2_0.jpeg | score=0.876 | stage=0.212 | keyword=x,y</t>
+          <t xml:space="preserve">1. page_176_img_0_0.png | score=1.388 | stage=0.537 | page=1.00; keyword=x,y,z
+2. page_175_img_1_0.jpeg | score=1.325 | stage=0.537 | page=1.00; keyword=x,y,z
+3. page_175_img_3_0.jpeg | score=1.318 | stage=0.537 | page=1.00; keyword=x,y,z
+4. page_177_img_1_0.jpeg | score=1.250 | stage=0.500 | page=1.00
+5. page_176_img_1_0.png | score=1.196 | stage=0.537 | page=1.00; keyword=x,y,z
+6. page_176_img_3_0.jpeg | score=1.193 | stage=0.537 | page=1.00; keyword=x,y,z
+7. page_176_img_2_0.jpeg | score=1.190 | stage=0.537 | page=1.00; keyword=x,y,z
+8. page_175_img_4_0.jpeg | score=1.123 | stage=0.537 | page=1.00; keyword=x,y,z
+9. page_175_img_2_0.jpeg | score=1.112 | stage=0.537 | page=1.00; keyword=x,y,z
+10. page_174_img_1_0.jpeg | score=1.042 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -5528,16 +5540,16 @@
       </c>
       <c r="P61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_181_img_0_0.jpeg | score=1.308 | stage=0.689 | page=1.00; keyword=recovery; section=recovery
-2. page_184_img_0_0.jpeg | score=1.217 | stage=0.580 | page=1.00
-3. page_182_img_0_0.jpeg | score=0.975 | stage=0.580 | page=1.00
-4. page_192_img_0_0.jpeg | score=0.861 | stage=0.284 | page=0.45
-5. page_191_img_0_0.jpeg | score=0.681 | stage=0.289 | page=0.45
-6. page_196_img_0_0.jpeg | score=0.671 | stage=0.261 | page=0.45
-7. page_189_img_0_0.jpeg | score=0.669 | stage=0.261 | page=0.45
-8. page_379_img_2_0.jpeg | score=0.637 | stage=0.245 | 
-9. page_92_img_1_0.jpeg | score=0.635 | stage=0.332 | 
-10. page_84_img_0_0.jpeg | score=0.625 | stage=0.319 | </t>
+          <t xml:space="preserve">1. page_181_img_0_0.jpeg | score=1.461 | stage=0.712 | page=1.00; keyword=recovery; section=recovery
+2. page_182_img_0_0.jpeg | score=1.414 | stage=0.712 | page=1.00; keyword=recovery; section=recovery
+3. page_184_img_0_0.jpeg | score=1.188 | stage=0.525 | page=1.00; keyword=joint,task
+4. page_186_img_0_0.jpeg | score=1.016 | stage=0.712 | page=1.00; keyword=recovery; section=recovery
+5. page_178_img_0_0.jpeg | score=0.908 | stage=0.450 | page=0.45; keyword=recovery,joint; section=recovery
+6. page_188_img_0_0.jpeg | score=0.750 | stage=0.225 | page=0.45
+7. page_179_img_1_0.jpeg | score=0.734 | stage=0.350 | page=0.70
+8. page_48_img_0_0.jpeg | score=0.704 | stage=0.000
+9. page_92_img_1_0.jpeg | score=0.638 | stage=0.213 | keyword=recovery; section=recovery
+10. page_177_img_1_0.jpeg | score=0.627 | stage=0.225 | page=0.45</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5587,7 @@
       </c>
       <c r="H62" s="0" t="inlineStr">
         <is>
-          <t>0.0254</t>
+          <t>0.0255</t>
         </is>
       </c>
       <c r="I62" s="0" t="inlineStr">
@@ -5590,7 +5602,7 @@
       </c>
       <c r="K62" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L62" s="0" t="inlineStr">
@@ -5605,7 +5617,7 @@
       </c>
       <c r="N62" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O62" s="0" t="inlineStr">
@@ -5615,16 +5627,16 @@
       </c>
       <c r="P62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_168_img_0_0.jpeg | score=0.858 | stage=0.000 | 
-2. page_361_img_0_0.jpeg | score=0.821 | stage=0.000 | 
-3. page_248_img_0_0.jpeg | score=0.806 | stage=0.000 | 
-4. page_360_img_0_0.jpeg | score=0.802 | stage=0.000 | 
-5. page_186_img_0_0.jpeg | score=0.796 | stage=0.000 | 
-6. page_376_img_0_0.jpeg | score=0.754 | stage=0.000 | 
-7. page_375_img_0_0.jpeg | score=0.732 | stage=0.000 | 
-8. page_184_img_0_0.jpeg | score=0.719 | stage=0.000 | 
-9. page_309_img_1_0.jpeg | score=0.696 | stage=0.000 | 
-10. page_323_img_0_0.jpeg | score=0.694 | stage=0.000 | </t>
+          <t xml:space="preserve">1. page_168_img_0_0.jpeg | score=0.867 | stage=0.000
+2. page_196_img_0_0.jpeg | score=0.841 | stage=0.000
+3. page_186_img_0_0.jpeg | score=0.824 | stage=0.000
+4. page_246_img_0_0.jpeg | score=0.791 | stage=0.000
+5. page_187_img_1_0.jpeg | score=0.745 | stage=0.000
+6. page_197_img_0_0.jpeg | score=0.744 | stage=0.000
+7. page_376_img_0_0.jpeg | score=0.742 | stage=0.000
+8. page_247_img_0_0.jpeg | score=0.709 | stage=0.000
+9. page_361_img_0_0.jpeg | score=0.702 | stage=0.000
+10. page_361_img_1_0.jpeg | score=0.702 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -5706,16 +5718,16 @@
       </c>
       <c r="P63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_196_img_0_0.jpeg | score=1.059 | stage=0.614 | page=1.00; keyword=setting
-2. page_195_img_2_0.jpeg | score=0.956 | stage=0.614 | page=1.00; keyword=setting
-3. page_192_img_0_0.jpeg | score=0.934 | stage=0.614 | page=1.00; keyword=setting
-4. page_190_img_1_0.jpeg | score=0.900 | stage=0.614 | page=1.00; keyword=setting
-5. page_190_img_0_0.jpeg | score=0.872 | stage=0.614 | page=1.00; keyword=setting
-6. page_220_img_0_0.jpeg | score=0.796 | stage=0.226 | keyword=setting
-7. page_224_img_0_0.jpeg | score=0.771 | stage=0.227 | keyword=setting
-8. page_195_img_0_0.jpeg | score=0.746 | stage=0.614 | page=1.00; keyword=setting
-9. page_376_img_0_0.jpeg | score=0.742 | stage=0.245 | 
-10. page_235_img_1_0.jpeg | score=0.741 | stage=0.225 | keyword=setting</t>
+          <t xml:space="preserve">1. page_196_img_0_0.jpeg | score=1.396 | stage=0.525 | page=1.00; keyword=1+2,setting
+2. page_197_img_0_0.jpeg | score=1.279 | stage=0.512 | page=1.00; keyword=setting
+3. page_195_img_0_0.jpeg | score=1.234 | stage=0.512 | page=1.00; keyword=setting
+4. page_195_img_2_0.jpeg | score=1.208 | stage=0.512 | page=1.00; keyword=setting
+5. page_192_img_0_0.jpeg | score=0.983 | stage=0.238 | page=0.45; keyword=setting
+6. page_101_img_0_0.jpeg | score=0.834 | stage=0.013 | keyword=cockpit
+7. page_191_img_0_0.jpeg | score=0.802 | stage=0.013 | keyword=setting
+8. page_189_img_0_0.jpeg | score=0.779 | stage=0.013 | keyword=setting
+9. page_220_img_0_0.jpeg | score=0.727 | stage=0.025 | keyword=setting,reset
+10. page_190_img_1_0.jpeg | score=0.710 | stage=0.013 | keyword=setting</t>
         </is>
       </c>
     </row>
@@ -5797,16 +5809,16 @@
       </c>
       <c r="P64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_205_img_1_0.jpeg | score=1.379 | stage=0.831 | page=1.00; keyword=tool weight,weight,tool settings; section=tool settings,tool weight
-2. page_192_img_0_0.jpeg | score=1.094 | stage=0.406 | page=0.70
-3. page_206_img_0_0.jpeg | score=1.052 | stage=0.689 | page=1.00; keyword=tool settings; section=tool settings
-4. page_196_img_0_0.jpeg | score=0.960 | stage=0.406 | page=0.70
-5. page_208_img_0_0.jpeg | score=0.944 | stage=0.689 | page=1.00; keyword=tool settings; section=tool settings
-6. page_210_img_0_0.jpeg | score=0.930 | stage=0.689 | page=1.00; keyword=tool settings; section=tool settings
-7. page_195_img_2_0.jpeg | score=0.924 | stage=0.406 | page=0.70
-8. page_195_img_0_0.jpeg | score=0.918 | stage=0.406 | page=0.70
-9. page_191_img_0_0.jpeg | score=0.846 | stage=0.406 | page=0.70
-10. page_189_img_0_0.jpeg | score=0.843 | stage=0.406 | page=0.70</t>
+          <t xml:space="preserve">1. page_205_img_1_0.jpeg | score=1.612 | stage=0.938 | page=1.00; keyword=tool weight,weight,tool settings; section=tool settings,tool weight
+2. page_206_img_0_0.jpeg | score=1.503 | stage=0.938 | page=1.00; keyword=tool weight,weight,tool settings; section=tool settings,tool weight
+3. page_208_img_0_0.jpeg | score=1.218 | stage=0.712 | page=1.00; keyword=tool settings; section=tool settings
+4. page_204_img_0_0.jpeg | score=0.989 | stage=0.712 | page=1.00; keyword=tool settings; section=tool settings
+5. page_204_img_1_0.jpeg | score=0.982 | stage=0.712 | page=1.00; keyword=tool settings; section=tool settings
+6. page_279_img_0_0.jpeg | score=0.831 | stage=0.225 | keyword=tool weight,weight; section=tool weight
+7. page_188_img_0_0.jpeg | score=0.805 | stage=0.013 | keyword=robot parameters
+8. page_189_img_0_0.jpeg | score=0.744 | stage=0.000
+9. page_289_img_0_0.jpeg | score=0.668 | stage=0.000
+10. page_280_img_0_0.jpeg | score=0.666 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5890,7 @@
       </c>
       <c r="N65" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O65" s="0" t="inlineStr">
@@ -5888,16 +5900,16 @@
       </c>
       <c r="P65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_208_img_0_0.jpeg | score=1.278 | stage=0.655 | page=1.00; section=tool settings
-2. page_209_img_0_0.jpeg | score=1.249 | stage=0.655 | page=1.00; section=tool settings
-3. page_210_img_0_0.jpeg | score=1.205 | stage=0.655 | page=1.00; section=tool settings
-4. page_206_img_0_0.jpeg | score=1.169 | stage=0.655 | page=1.00; section=tool settings
-5. page_224_img_0_0.jpeg | score=1.162 | stage=0.580 | page=1.00
-6. page_205_img_1_0.jpeg | score=1.115 | stage=0.655 | page=1.00; section=tool settings
-7. page_245_img_0_0.jpeg | score=1.108 | stage=0.580 | page=1.00
-8. page_235_img_1_0.jpeg | score=1.066 | stage=0.580 | page=1.00
-9. page_233_img_2_0.jpeg | score=1.031 | stage=0.580 | page=1.00
-10. page_226_img_2_0.jpeg | score=1.019 | stage=0.580 | page=1.00</t>
+          <t xml:space="preserve">1. page_209_img_0_0.jpeg | score=1.598 | stage=0.925 | page=1.00; keyword=tool shape,shape; section=tool settings,tool shape
+2. page_208_img_0_0.jpeg | score=1.555 | stage=0.938 | page=1.00; keyword=tool shape,simulation,shape; section=tool settings,tool shape
+3. page_210_img_0_0.jpeg | score=1.508 | stage=0.925 | page=1.00; keyword=tool shape,shape; section=tool settings,tool shape
+4. page_210_img_2_0.jpeg | score=1.504 | stage=0.925 | page=1.00; keyword=tool shape,shape; section=tool settings,tool shape
+5. page_206_img_0_0.jpeg | score=1.369 | stage=0.700 | page=1.00; section=tool settings
+6. page_210_img_1_0.jpeg | score=1.263 | stage=0.925 | page=1.00; keyword=tool shape,shape; section=tool settings,tool shape
+7. page_205_img_1_0.jpeg | score=1.066 | stage=0.550 | page=0.70; section=tool settings
+8. page_259_img_1_0.jpeg | score=0.706 | stage=0.000
+9. page_226_img_2_0.jpeg | score=0.706 | stage=0.013 | keyword=shape
+10. page_236_img_0_0.jpeg | score=0.691 | stage=0.013 | keyword=shape</t>
         </is>
       </c>
     </row>
@@ -5954,12 +5966,12 @@
       </c>
       <c r="K66" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L66" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
       <c r="M66" s="0" t="inlineStr">
@@ -5967,24 +5979,28 @@
           <t>page_226_img_0_0.jpeg</t>
         </is>
       </c>
-      <c r="N66" s="0"/>
+      <c r="N66" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O66" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_224_img_0_0.jpeg | score=1.300 | stage=0.698 | page=1.00; keyword=x,y; section=safety settings
-2. page_240_img_0_0.jpeg | score=1.287 | stage=0.698 | page=1.00; keyword=x,y; section=safety settings
-3. page_241_img_0_0.jpeg | score=1.264 | stage=0.698 | page=1.00; keyword=x,y; section=safety settings
-4. page_242_img_0_0.jpeg | score=1.217 | stage=0.698 | page=1.00; keyword=x,y; section=safety settings
-5. page_236_img_0_0.jpeg | score=1.155 | stage=0.698 | page=1.00; keyword=x,y; section=safety settings
-6. page_244_img_0_0.jpeg | score=1.145 | stage=0.698 | page=1.00; keyword=x,y; section=safety settings
-7. page_243_img_0_0.jpeg | score=1.102 | stage=0.698 | page=1.00; keyword=x,y; section=safety settings
-8. page_226_img_2_0.jpeg | score=1.084 | stage=0.698 | page=1.00; keyword=x,y; section=safety settings
-9. page_232_img_0_0.jpeg | score=1.062 | stage=0.698 | page=1.00; keyword=x,y; section=safety settings
-10. page_243_img_1_0.jpeg | score=1.046 | stage=0.698 | page=1.00; keyword=x,y; section=safety settings</t>
+          <t xml:space="preserve">1. page_224_img_0_0.jpeg | score=1.398 | stage=0.671 | page=1.00; keyword=zone,y,z; section=safety settings
+2. page_225_img_0_0.jpeg | score=1.312 | stage=0.696 | page=1.00; keyword=zone,x,y,z; section=safety settings
+3. page_226_img_0_0.jpeg | score=1.159 | stage=0.671 | page=1.00; keyword=y,z,radius; section=safety settings
+4. page_223_img_0_0.jpeg | score=1.080 | stage=0.646 | page=1.00; keyword=y; section=safety settings
+5. page_226_img_2_0.jpeg | score=0.996 | stage=0.671 | page=1.00; keyword=y,z,radius; section=safety settings
+6. page_239_img_0_0.jpeg | score=0.927 | stage=0.171 | keyword=zone,y,z; section=safety settings
+7. page_240_img_0_0.jpeg | score=0.923 | stage=0.146 | keyword=y; section=safety settings
+8. page_241_img_0_0.jpeg | score=0.872 | stage=0.183 | keyword=zone,y,z,robot parameter; section=safety settings
+9. page_228_img_0_0.jpeg | score=0.861 | stage=0.817 | page=1.00; keyword=center position,x,y,z; section=safety settings,center position
+10. page_228_img_2_0.jpeg | score=0.855 | stage=0.817 | page=1.00; keyword=center position,x,y,z; section=safety settings,center position</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6068,7 @@
       </c>
       <c r="N67" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O67" s="0" t="inlineStr">
@@ -6062,16 +6078,16 @@
       </c>
       <c r="P67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_240_img_0_0.jpeg | score=0.820 | stage=0.000 | 
-2. page_236_img_0_0.jpeg | score=0.798 | stage=0.000 | 
-3. page_241_img_0_0.jpeg | score=0.797 | stage=0.000 | 
-4. page_230_img_0_0.jpeg | score=0.745 | stage=0.000 | 
-5. page_232_img_0_0.jpeg | score=0.736 | stage=0.000 | 
-6. page_244_img_0_0.jpeg | score=0.712 | stage=0.000 | 
-7. page_235_img_1_0.jpeg | score=0.701 | stage=0.000 | 
-8. page_242_img_0_0.jpeg | score=0.700 | stage=0.000 | 
-9. page_230_img_1_0.jpeg | score=0.688 | stage=0.000 | 
-10. page_233_img_1_0.jpeg | score=0.679 | stage=0.000 | </t>
+          <t xml:space="preserve">1. page_239_img_0_0.jpeg | score=0.885 | stage=0.000
+2. page_237_img_0_0.jpeg | score=0.861 | stage=0.000
+3. page_240_img_0_0.jpeg | score=0.835 | stage=0.000
+4. page_238_img_0_0.jpeg | score=0.816 | stage=0.000
+5. page_230_img_0_0.jpeg | score=0.809 | stage=0.000
+6. page_230_img_1_0.jpeg | score=0.758 | stage=0.000
+7. page_232_img_0_0.jpeg | score=0.741 | stage=0.000
+8. page_236_img_0_0.jpeg | score=0.736 | stage=0.000
+9. page_241_img_0_0.jpeg | score=0.735 | stage=0.000
+10. page_231_img_1_0.jpeg | score=0.719 | stage=0.000</t>
         </is>
       </c>
     </row>
@@ -6153,16 +6169,16 @@
       </c>
       <c r="P68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_243_img_0_0.jpeg | score=1.314 | stage=0.655 | page=1.00; section=safety settings
-2. page_242_img_0_0.jpeg | score=1.278 | stage=0.655 | page=1.00; section=safety settings
-3. page_244_img_0_0.jpeg | score=1.123 | stage=0.655 | page=1.00; section=safety settings
-4. page_240_img_0_0.jpeg | score=1.071 | stage=0.655 | page=1.00; section=safety settings
-5. page_243_img_1_0.jpeg | score=1.035 | stage=0.655 | page=1.00; section=safety settings
-6. page_241_img_0_0.jpeg | score=0.898 | stage=0.655 | page=1.00; section=safety settings
-7. page_245_img_0_0.jpeg | score=0.863 | stage=0.655 | page=1.00; section=safety settings
-8. page_224_img_0_0.jpeg | score=0.814 | stage=0.655 | page=1.00; section=safety settings
-9. page_24_img_0_0.jpeg | score=0.742 | stage=0.306 | 
-10. page_225_img_0_0.jpeg | score=0.732 | stage=0.655 | page=1.00; section=safety settings</t>
+          <t xml:space="preserve">1. page_243_img_0_0.jpeg | score=1.607 | stage=0.938 | page=1.00; keyword=collision sensitivity,reduction zone,sensitivity; section=safety settings,collision sensitivity reduction zone
+2. page_242_img_0_0.jpeg | score=1.464 | stage=0.712 | page=1.00; keyword=robot parameter; section=safety settings
+3. page_243_img_1_0.jpeg | score=1.405 | stage=0.938 | page=1.00; keyword=collision sensitivity,reduction zone,sensitivity; section=safety settings,collision sensitivity reduction zone
+4. page_244_img_0_0.jpeg | score=1.384 | stage=0.700 | page=1.00; section=safety settings
+5. page_241_img_0_0.jpeg | score=1.322 | stage=0.712 | page=1.00; keyword=robot parameter; section=safety settings
+6. page_240_img_0_0.jpeg | score=1.154 | stage=0.700 | page=1.00; section=safety settings
+7. page_239_img_0_0.jpeg | score=0.947 | stage=0.700 | page=1.00; section=safety settings
+8. page_245_img_0_0.jpeg | score=0.935 | stage=0.712 | page=1.00; keyword=robot parameter; section=safety settings
+9. page_295_img_0_0.jpeg | score=0.732 | stage=0.038 | keyword=collision sensitivity,sensitivity,robot parameter
+10. page_284_img_0_0.jpeg | score=0.731 | stage=0.038 | keyword=collision sensitivity,sensitivity,robot parameter</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6250,7 @@
       </c>
       <c r="N69" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O69" s="0" t="inlineStr">
@@ -6244,16 +6260,16 @@
       </c>
       <c r="P69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_248_img_0_0.jpeg | score=1.413 | stage=0.831 | page=1.00; keyword=safety setting review,robot parameter,review; section=safety setting review
-2. page_240_img_0_0.jpeg | score=1.242 | stage=0.614 | page=1.00; keyword=safety settings
-3. page_249_img_0_0.jpeg | score=1.221 | stage=0.580 | page=1.00
-4. page_220_img_0_0.jpeg | score=1.211 | stage=0.614 | page=1.00; keyword=safety settings
-5. page_245_img_0_0.jpeg | score=1.182 | stage=0.614 | page=1.00; keyword=safety settings
-6. page_224_img_0_0.jpeg | score=1.161 | stage=0.614 | page=1.00; keyword=safety settings
-7. page_246_img_0_0.jpeg | score=1.132 | stage=0.831 | page=1.00; keyword=safety setting review,robot parameter,review; section=safety setting review
-8. page_247_img_0_0.jpeg | score=1.124 | stage=0.831 | page=1.00; keyword=safety setting review,robot parameter,review; section=safety setting review
-9. page_247_img_1_0.jpeg | score=1.064 | stage=0.797 | page=1.00; keyword=safety setting review,review; section=safety setting review
-10. page_252_img_2_0.jpeg | score=1.054 | stage=0.614 | page=1.00; keyword=robot parameter</t>
+          <t xml:space="preserve">1. page_246_img_0_0.jpeg | score=1.601 | stage=0.950 | page=1.00; keyword=safety setting review,robot parameter,safety settings,review; section=safety setting review
+2. page_247_img_0_0.jpeg | score=1.578 | stage=0.938 | page=1.00; keyword=safety setting review,robot parameter,review; section=safety setting review
+3. page_247_img_1_0.jpeg | score=1.572 | stage=0.938 | page=1.00; keyword=safety setting review,robot parameter,review; section=safety setting review
+4. page_248_img_0_0.jpeg | score=1.244 | stage=0.925 | page=1.00; keyword=safety setting review,review; section=safety setting review
+5. page_245_img_0_0.jpeg | score=1.224 | stage=0.525 | page=1.00; keyword=robot parameter,safety settings
+6. page_244_img_0_0.jpeg | score=0.924 | stage=0.512 | page=1.00; keyword=safety settings
+7. page_223_img_0_0.jpeg | score=0.863 | stage=0.025 | keyword=safety settings,save
+8. page_208_img_0_0.jpeg | score=0.797 | stage=0.000
+9. page_224_img_0_0.jpeg | score=0.774 | stage=0.025 | keyword=safety settings,save
+10. page_251_img_2_0.jpeg | score=0.768 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6311,7 @@
       </c>
       <c r="H70" s="0" t="inlineStr">
         <is>
-          <t>0.1788</t>
+          <t>0.1789</t>
         </is>
       </c>
       <c r="I70" s="0" t="inlineStr">
@@ -6325,7 +6341,7 @@
       </c>
       <c r="N70" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O70" s="0" t="inlineStr">
@@ -6335,16 +6351,16 @@
       </c>
       <c r="P70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_251_img_2_0.jpeg | score=1.368 | stage=0.689 | page=1.00; keyword=remote control; section=remote control
-2. page_252_img_0_0.jpeg | score=1.325 | stage=0.689 | page=1.00; keyword=remote control; section=remote control
-3. page_251_img_1_0.jpeg | score=1.312 | stage=0.689 | page=1.00; keyword=remote control; section=remote control
-4. page_249_img_0_0.jpeg | score=1.296 | stage=0.689 | page=1.00; keyword=remote control; section=remote control
-5. page_256_img_0_0.jpeg | score=1.269 | stage=0.580 | page=1.00
-6. page_249_img_2_0.jpeg | score=1.235 | stage=0.689 | page=1.00; keyword=remote control; section=remote control
-7. page_257_img_0_0.jpeg | score=1.226 | stage=0.689 | page=1.00; keyword=remote control; section=remote control
-8. page_258_img_0_0.jpeg | score=1.164 | stage=0.580 | page=1.00
-9. page_259_img_1_0.jpeg | score=1.153 | stage=0.580 | page=1.00
-10. page_252_img_2_0.jpeg | score=1.134 | stage=0.580 | page=1.00</t>
+          <t xml:space="preserve">1. page_254_img_0_0.jpeg | score=1.440 | stage=0.712 | page=1.00; keyword=remote control; section=remote control
+2. page_249_img_0_0.jpeg | score=1.407 | stage=0.712 | page=1.00; keyword=remote control; section=remote control
+3. page_251_img_2_0.jpeg | score=1.392 | stage=0.712 | page=1.00; keyword=remote control; section=remote control
+4. page_251_img_1_0.jpeg | score=1.376 | stage=0.712 | page=1.00; keyword=remote control; section=remote control
+5. page_257_img_0_0.jpeg | score=1.336 | stage=0.738 | page=1.00; keyword=remote control,task,servo on; section=remote control
+6. page_249_img_2_0.jpeg | score=1.249 | stage=0.712 | page=1.00; keyword=remote control; section=remote control
+7. page_256_img_0_0.jpeg | score=1.248 | stage=0.500 | page=1.00
+8. page_249_img_3_0.png | score=1.226 | stage=0.712 | page=1.00; keyword=remote control; section=remote control
+9. page_258_img_0_0.jpeg | score=1.209 | stage=0.712 | page=1.00; keyword=remote control; section=remote control
+10. page_248_img_0_0.jpeg | score=1.114 | stage=0.712 | page=1.00; keyword=remote control; section=remote control</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6432,7 @@
       </c>
       <c r="N71" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O71" s="0" t="inlineStr">
@@ -6426,16 +6442,16 @@
       </c>
       <c r="P71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_336_img_0_0.jpeg | score=1.306 | stage=0.747 | page=1.00; keyword=i,o overview; section=i,o overview
-2. page_333_img_0_0.jpeg | score=1.287 | stage=0.747 | page=1.00; keyword=i,o overview; section=i,o overview
-3. page_335_img_1_0.jpeg | score=1.114 | stage=0.747 | page=1.00; keyword=i,o overview; section=i,o overview
-4. page_335_img_2_0.jpeg | score=1.096 | stage=0.747 | page=1.00; keyword=i,o overview; section=i,o overview
-5. page_334_img_0_0.jpeg | score=1.052 | stage=0.747 | page=1.00; keyword=i,o overview; section=i,o overview
-6. page_335_img_0_0.jpeg | score=1.047 | stage=0.747 | page=1.00; keyword=i,o overview; section=i,o overview
-7. page_332_img_0_0.jpeg | score=1.032 | stage=0.747 | page=1.00; keyword=i,o overview; section=i,o overview
-8. page_338_img_0_0.jpeg | score=0.939 | stage=0.664 | page=1.00; keyword=i; section=i
-9. page_142_img_0_0.jpeg | score=0.867 | stage=0.337 | keyword=i; section=i
-10. page_139_img_0_0.jpeg | score=0.866 | stage=0.302 | keyword=i; section=i</t>
+          <t xml:space="preserve">1. page_334_img_0_0.jpeg | score=1.544 | stage=0.817 | page=1.00; keyword=i,o overview,high,low; section=i,o overview
+2. page_336_img_0_0.jpeg | score=1.482 | stage=0.792 | page=1.00; keyword=i,o overview; section=i,o overview
+3. page_335_img_1_0.jpeg | score=1.434 | stage=0.792 | page=1.00; keyword=i,o overview; section=i,o overview
+4. page_335_img_2_0.jpeg | score=1.430 | stage=0.792 | page=1.00; keyword=i,o overview; section=i,o overview
+5. page_333_img_0_0.jpeg | score=1.392 | stage=0.792 | page=1.00; keyword=i,o overview; section=i,o overview
+6. page_335_img_0_0.jpeg | score=1.238 | stage=0.792 | page=1.00; keyword=i,o overview; section=i,o overview
+7. page_332_img_0_0.jpeg | score=1.150 | stage=0.792 | page=1.00; keyword=i,o overview; section=i,o overview
+8. page_328_img_1_0.jpeg | score=0.855 | stage=0.496 | page=0.70; keyword=i; section=i
+9. page_328_img_2_0.jpeg | score=0.835 | stage=0.496 | page=0.70; keyword=i; section=i
+10. page_139_img_0_0.jpeg | score=0.743 | stage=0.146 | keyword=i; section=i</t>
         </is>
       </c>
     </row>

--- a/SCIE용/excel/30_g4_auto_retrieval_results.xlsx
+++ b/SCIE용/excel/30_g4_auto_retrieval_results.xlsx
@@ -231,28 +231,24 @@
           <t>page_403_img_0_0.jpeg</t>
         </is>
       </c>
-      <c r="N2" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="N2" s="0"/>
       <c r="O2" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_403_img_0_0.jpeg | score=0.732 | stage=0.000
-2. page_48_img_0_0.jpeg | score=0.696 | stage=0.000
-3. page_116_img_0_0.jpeg | score=0.628 | stage=0.000
-4. page_104_img_0_0.jpeg | score=0.593 | stage=0.000
-5. page_98_img_0_0.jpeg | score=0.591 | stage=0.000
-6. page_98_img_1_0.jpeg | score=0.590 | stage=0.000
-7. page_174_img_1_0.jpeg | score=0.515 | stage=0.000
-8. page_105_img_0_0.jpeg | score=0.514 | stage=0.000
-9. page_402_img_0_0.jpeg | score=0.500 | stage=0.000
-10. page_402_img_1_0.jpeg | score=0.500 | stage=0.000</t>
+          <t xml:space="preserve">1. page_104_img_0_0.jpeg | score=0.755 | stage=0.000 | 
+2. page_116_img_0_0.jpeg | score=0.641 | stage=0.000 | 
+3. page_84_img_0_0.jpeg | score=0.557 | stage=0.000 | 
+4. page_105_img_0_0.jpeg | score=0.551 | stage=0.000 | 
+5. page_98_img_0_0.jpeg | score=0.522 | stage=0.000 | 
+6. page_98_img_1_0.jpeg | score=0.521 | stage=0.000 | 
+7. page_103_img_0_0.jpeg | score=0.513 | stage=0.000 | 
+8. page_115_img_0_0.jpeg | score=0.513 | stage=0.000 | 
+9. page_118_img_0_0.jpeg | score=0.507 | stage=0.000 | 
+10. page_98_img_2_0.jpeg | score=0.505 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -294,7 +290,7 @@
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>0.0502</t>
+          <t>0.0501</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
@@ -335,15 +331,15 @@
       <c r="P3" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">1. page_403_img_0_0.jpeg | score=1.391 | stage=0.633 | page=1.00; section=cs-12p
-2. page_86_img_0_0.jpeg | score=1.359 | stage=0.500 | page=1.00
-3. page_121_img_0_0.jpeg | score=1.346 | stage=0.500 | page=1.00
-4. page_120_img_0_0.jpeg | score=1.091 | stage=0.500 | page=1.00
-5. page_124_img_0_0.jpeg | score=0.958 | stage=0.500 | page=1.00
-6. page_402_img_0_0.jpeg | score=0.940 | stage=0.633 | page=1.00; section=cs-12p
-7. page_125_img_0_0.jpeg | score=0.939 | stage=0.225 | page=0.45
-8. page_402_img_1_0.jpeg | score=0.937 | stage=0.633 | page=1.00; section=cs-12p
-9. page_88_img_1_0.jpeg | score=0.930 | stage=0.500 | page=1.00
-10. page_85_img_0_0.jpeg | score=0.901 | stage=0.500 | page=1.00</t>
+2. page_86_img_0_0.jpeg | score=1.361 | stage=0.500 | page=1.00
+3. page_125_img_0_0.jpeg | score=1.211 | stage=0.500 | page=1.00
+4. page_88_img_1_0.jpeg | score=1.186 | stage=0.500 | page=1.00
+5. page_121_img_0_0.jpeg | score=1.159 | stage=0.500 | page=1.00
+6. page_88_img_0_0.jpeg | score=1.117 | stage=0.500 | page=1.00
+7. page_402_img_0_0.jpeg | score=1.091 | stage=0.633 | page=1.00; section=cs-12p
+8. page_402_img_1_0.jpeg | score=1.088 | stage=0.633 | page=1.00; section=cs-12p
+9. page_120_img_0_0.jpeg | score=1.049 | stage=0.500 | page=1.00
+10. page_89_img_1_0.jpeg | score=0.940 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -425,16 +421,16 @@
       </c>
       <c r="P4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_115_img_0_0.jpeg | score=1.383 | stage=0.525 | page=1.00; keyword=m8,20nm
-2. page_84_img_0_0.jpeg | score=1.317 | stage=0.500 | page=1.00
-3. page_116_img_0_0.jpeg | score=1.284 | stage=0.500 | page=1.00
-4. page_85_img_0_0.jpeg | score=1.236 | stage=0.525 | page=1.00; keyword=robot base,base
-5. page_114_img_0_0.jpeg | score=1.183 | stage=0.500 | page=1.00
-6. page_86_img_0_0.jpeg | score=1.164 | stage=0.500 | page=1.00
-7. page_121_img_0_0.jpeg | score=1.042 | stage=0.350 | page=0.70
-8. page_83_img_0_0.jpeg | score=0.908 | stage=0.500 | page=1.00
-9. page_113_img_0_0.jpeg | score=0.905 | stage=0.350 | page=0.70
-10. page_93_img_0_0.jpeg | score=0.858 | stage=0.000</t>
+          <t xml:space="preserve">1. page_115_img_0_0.jpeg | score=1.379 | stage=0.525 | page=1.00; keyword=m8,20nm
+2. page_116_img_0_0.jpeg | score=1.336 | stage=0.500 | page=1.00
+3. page_123_img_0_0.jpeg | score=1.324 | stage=0.500 | page=1.00
+4. page_84_img_0_0.jpeg | score=1.315 | stage=0.500 | page=1.00
+5. page_88_img_0_0.jpeg | score=1.235 | stage=0.500 | page=1.00
+6. page_88_img_1_0.jpeg | score=1.226 | stage=0.500 | page=1.00
+7. page_118_img_0_0.jpeg | score=1.173 | stage=0.500 | page=1.00
+8. page_114_img_0_0.jpeg | score=1.171 | stage=0.500 | page=1.00
+9. page_124_img_0_0.jpeg | score=1.140 | stage=0.500 | page=1.00
+10. page_86_img_0_0.jpeg | score=1.127 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -506,7 +502,7 @@
       </c>
       <c r="N5" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O5" s="0" t="inlineStr">
@@ -516,16 +512,16 @@
       </c>
       <c r="P5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_143_img_1_0.jpeg | score=1.502 | stage=0.838 | page=1.00; keyword=safety i,o,tbsft; section=safety i,o,tbsft
-2. page_145_img_0_0.jpeg | score=1.495 | stage=0.738 | page=1.00; keyword=safety i,o,em; section=safety i,o
-3. page_143_img_0_0.jpeg | score=1.493 | stage=0.838 | page=1.00; keyword=safety i,o,tbsft; section=safety i,o,tbsft
-4. page_147_img_0_0.jpeg | score=1.360 | stage=0.738 | page=1.00; keyword=o,em,emergency stop; section=o,emergency stop
-5. page_144_img_0_0.jpeg | score=1.319 | stage=0.725 | page=1.00; keyword=safety i,o; section=safety i,o
-6. page_144_img_1_0.jpeg | score=1.312 | stage=0.725 | page=1.00; keyword=safety i,o; section=safety i,o
-7. page_148_img_0_0.jpeg | score=1.171 | stage=0.612 | page=1.00; keyword=o; section=o
-8. page_142_img_1_0.jpeg | score=1.161 | stage=0.612 | page=1.00; keyword=o; section=o
-9. page_142_img_0_0.jpeg | score=1.153 | stage=0.612 | page=1.00; keyword=o; section=o
-10. page_133_img_0_0.jpeg | score=0.891 | stage=0.113 | keyword=o; section=o</t>
+          <t xml:space="preserve">1. page_145_img_0_0.jpeg | score=1.484 | stage=0.725 | page=1.00; keyword=safety i,o; section=safety i,o
+2. page_147_img_0_0.jpeg | score=1.406 | stage=0.612 | page=1.00; keyword=o; section=o
+3. page_142_img_0_0.jpeg | score=1.366 | stage=0.612 | page=1.00; keyword=o; section=o
+4. page_142_img_1_0.jpeg | score=1.363 | stage=0.612 | page=1.00; keyword=o; section=o
+5. page_148_img_0_0.jpeg | score=1.272 | stage=0.612 | page=1.00; keyword=o; section=o
+6. page_144_img_0_0.jpeg | score=1.234 | stage=0.612 | page=1.00; keyword=o; section=o
+7. page_144_img_1_0.jpeg | score=1.227 | stage=0.612 | page=1.00; keyword=o; section=o
+8. page_143_img_0_0.jpeg | score=1.175 | stage=0.612 | page=1.00; keyword=o; section=o
+9. page_143_img_1_0.jpeg | score=1.172 | stage=0.612 | page=1.00; keyword=o; section=o
+10. page_141_img_1_0.jpeg | score=1.106 | stage=0.612 | page=1.00; keyword=o; section=o</t>
         </is>
       </c>
     </row>
@@ -599,16 +595,16 @@
       </c>
       <c r="P6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_94_img_0_0.jpeg | score=0.865 | stage=0.000
-2. page_127_img_0_0.jpeg | score=0.851 | stage=0.000
-3. page_336_img_0_0.jpeg | score=0.808 | stage=0.000
-4. page_95_img_0_0.jpeg | score=0.775 | stage=0.000
-5. page_130_img_0_0.jpeg | score=0.753 | stage=0.000
-6. page_132_img_0_0.png | score=0.736 | stage=0.000
-7. page_101_img_0_0.jpeg | score=0.711 | stage=0.000
-8. page_93_img_0_0.jpeg | score=0.706 | stage=0.000
-9. page_137_img_0_0.jpeg | score=0.670 | stage=0.000
-10. page_136_img_0_0.png | score=0.653 | stage=0.000</t>
+          <t xml:space="preserve">1. page_94_img_0_0.jpeg | score=0.865 | stage=0.000 | 
+2. page_127_img_0_0.jpeg | score=0.843 | stage=0.000 | 
+3. page_132_img_0_0.png | score=0.821 | stage=0.000 | 
+4. page_95_img_0_0.jpeg | score=0.773 | stage=0.000 | 
+5. page_130_img_0_0.jpeg | score=0.771 | stage=0.000 | 
+6. page_137_img_0_0.jpeg | score=0.714 | stage=0.000 | 
+7. page_104_img_0_0.jpeg | score=0.711 | stage=0.000 | 
+8. page_93_img_0_0.jpeg | score=0.709 | stage=0.000 | 
+9. page_103_img_0_0.jpeg | score=0.686 | stage=0.000 | 
+10. page_98_img_0_0.jpeg | score=0.676 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -690,16 +686,16 @@
       </c>
       <c r="P7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_89_img_1_0.jpeg | score=1.329 | stage=0.500 | page=1.00
-2. page_89_img_0_0.jpeg | score=1.304 | stage=0.500 | page=1.00
-3. page_88_img_1_0.jpeg | score=1.165 | stage=0.500 | page=1.00
-4. page_103_img_0_0.jpeg | score=1.149 | stage=0.500 | page=1.00
-5. page_104_img_0_0.jpeg | score=1.096 | stage=0.500 | page=1.00
-6. page_88_img_0_0.jpeg | score=1.017 | stage=0.500 | page=1.00
-7. page_24_img_0_0.jpeg | score=0.881 | stage=0.000
-8. page_220_img_0_0.jpeg | score=0.807 | stage=0.000
-9. page_102_img_0_0.jpeg | score=0.777 | stage=0.500 | page=1.00
-10. page_163_img_0_0.jpeg | score=0.737 | stage=0.000</t>
+          <t xml:space="preserve">1. page_89_img_1_0.jpeg | score=1.330 | stage=0.500 | page=1.00
+2. page_89_img_0_0.jpeg | score=1.302 | stage=0.500 | page=1.00
+3. page_88_img_1_0.jpeg | score=1.173 | stage=0.500 | page=1.00
+4. page_103_img_0_0.jpeg | score=1.121 | stage=0.500 | page=1.00
+5. page_104_img_0_0.jpeg | score=1.051 | stage=0.500 | page=1.00
+6. page_88_img_0_0.jpeg | score=1.001 | stage=0.500 | page=1.00
+7. page_24_img_0_0.jpeg | score=0.902 | stage=0.013 | keyword=emergency stop
+8. page_102_img_0_0.jpeg | score=0.848 | stage=0.500 | page=1.00
+9. page_224_img_0_0.jpeg | score=0.738 | stage=0.000 | 
+10. page_163_img_0_0.jpeg | score=0.738 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -771,7 +767,7 @@
       </c>
       <c r="N8" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O8" s="0" t="inlineStr">
@@ -781,16 +777,16 @@
       </c>
       <c r="P8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_195_img_0_0.jpeg | score=1.304 | stage=0.500 | page=1.00
-2. page_195_img_2_0.jpeg | score=1.274 | stage=0.500 | page=1.00
-3. page_196_img_0_0.jpeg | score=1.181 | stage=0.500 | page=1.00
-4. page_325_img_0_0.jpeg | score=0.944 | stage=0.213 | keyword=cockpit; section=cockpit
-5. page_101_img_0_0.jpeg | score=0.892 | stage=0.225 | keyword=cockpit,tool flange; section=cockpit
-6. page_324_img_0_0.jpeg | score=0.778 | stage=0.000
-7. page_123_img_0_0.jpeg | score=0.732 | stage=0.000
-8. page_88_img_1_0.jpeg | score=0.678 | stage=0.000
-9. page_103_img_0_0.jpeg | score=0.633 | stage=0.000
-10. page_281_img_1_0.jpeg | score=0.581 | stage=0.000</t>
+          <t xml:space="preserve">1. page_195_img_2_0.jpeg | score=1.273 | stage=0.500 | page=1.00
+2. page_195_img_0_0.jpeg | score=1.165 | stage=0.500 | page=1.00
+3. page_196_img_0_0.jpeg | score=1.056 | stage=0.500 | page=1.00
+4. page_323_img_0_0.jpeg | score=0.822 | stage=0.000 | 
+5. page_325_img_0_0.jpeg | score=0.810 | stage=0.000 | 
+6. page_323_img_1_0.jpeg | score=0.791 | stage=0.000 | 
+7. page_324_img_0_0.jpeg | score=0.785 | stage=0.000 | 
+8. page_123_img_0_0.jpeg | score=0.711 | stage=0.000 | 
+9. page_88_img_1_0.jpeg | score=0.658 | stage=0.000 | 
+10. page_89_img_1_0.jpeg | score=0.657 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -862,7 +858,7 @@
       </c>
       <c r="N9" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O9" s="0" t="inlineStr">
@@ -872,16 +868,16 @@
       </c>
       <c r="P9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_140_img_0_0.jpeg | score=1.413 | stage=0.646 | page=1.00; keyword=o; section=o
-2. page_138_img_1_0.jpeg | score=1.395 | stage=0.671 | page=1.00; keyword=o,npn,pnp; section=o
-3. page_138_img_0_0.jpeg | score=1.392 | stage=0.671 | page=1.00; keyword=o,npn,pnp; section=o
-4. page_141_img_1_0.jpeg | score=1.347 | stage=0.683 | page=1.00; keyword=o,vio,gio,tbco; section=o
-5. page_142_img_1_0.jpeg | score=1.308 | stage=0.671 | page=1.00; keyword=o,gio,tbco; section=o
-6. page_142_img_0_0.jpeg | score=1.300 | stage=0.671 | page=1.00; keyword=o,gio,tbco; section=o
-7. page_137_img_0_0.jpeg | score=1.262 | stage=0.525 | page=1.00; keyword=npn,pnp
-8. page_132_img_0_0.png | score=1.241 | stage=0.646 | page=1.00; keyword=o; section=o
-9. page_130_img_0_0.jpeg | score=1.198 | stage=0.508 | page=0.70; keyword=o,pnp; section=o
-10. page_139_img_0_0.jpeg | score=1.196 | stage=0.671 | page=1.00; keyword=o,npn,pnp; section=o</t>
+          <t xml:space="preserve">1. page_138_img_0_0.jpeg | score=1.442 | stage=0.646 | page=1.00; keyword=o; section=o
+2. page_138_img_1_0.jpeg | score=1.438 | stage=0.646 | page=1.00; keyword=o; section=o
+3. page_139_img_0_0.jpeg | score=1.423 | stage=0.646 | page=1.00; keyword=o; section=o
+4. page_142_img_1_0.jpeg | score=1.410 | stage=0.658 | page=1.00; keyword=o,tbco; section=o
+5. page_142_img_0_0.jpeg | score=1.406 | stage=0.658 | page=1.00; keyword=o,tbco; section=o
+6. page_140_img_0_0.jpeg | score=1.392 | stage=0.646 | page=1.00; keyword=o; section=o
+7. page_144_img_0_0.jpeg | score=1.341 | stage=0.696 | page=1.00; keyword=o,vcc,vio,gnd; section=o
+8. page_137_img_0_0.jpeg | score=1.335 | stage=0.646 | page=1.00; keyword=o; section=o
+9. page_144_img_1_0.jpeg | score=1.334 | stage=0.696 | page=1.00; keyword=o,vcc,vio,gnd; section=o
+10. page_132_img_0_0.png | score=1.323 | stage=0.646 | page=1.00; keyword=o; section=o</t>
         </is>
       </c>
     </row>
@@ -949,7 +945,7 @@
       </c>
       <c r="N10" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O10" s="0" t="inlineStr">
@@ -959,16 +955,16 @@
       </c>
       <c r="P10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_145_img_0_0.jpeg | score=0.881 | stage=0.000
-2. page_147_img_0_0.jpeg | score=0.843 | stage=0.000
-3. page_133_img_0_0.jpeg | score=0.838 | stage=0.000
-4. page_143_img_1_0.jpeg | score=0.816 | stage=0.000
-5. page_143_img_0_0.jpeg | score=0.814 | stage=0.000
-6. page_144_img_0_0.jpeg | score=0.754 | stage=0.000
-7. page_144_img_1_0.jpeg | score=0.751 | stage=0.000
-8. page_255_img_0_0.jpeg | score=0.748 | stage=0.000
-9. page_334_img_0_0.jpeg | score=0.733 | stage=0.000
-10. page_148_img_0_0.jpeg | score=0.727 | stage=0.000</t>
+          <t xml:space="preserve">1. page_147_img_0_0.jpeg | score=0.887 | stage=0.000 | 
+2. page_145_img_0_0.jpeg | score=0.879 | stage=0.000 | 
+3. page_133_img_0_0.jpeg | score=0.840 | stage=0.000 | 
+4. page_142_img_0_0.jpeg | score=0.800 | stage=0.000 | 
+5. page_142_img_1_0.jpeg | score=0.800 | stage=0.000 | 
+6. page_148_img_0_0.jpeg | score=0.767 | stage=0.000 | 
+7. page_144_img_0_0.jpeg | score=0.763 | stage=0.000 | 
+8. page_144_img_1_0.jpeg | score=0.759 | stage=0.000 | 
+9. page_242_img_0_0.jpeg | score=0.706 | stage=0.000 | 
+10. page_241_img_0_0.jpeg | score=0.702 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -1025,7 +1021,7 @@
       </c>
       <c r="K11" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L11" s="0" t="inlineStr">
@@ -1046,16 +1042,16 @@
       </c>
       <c r="P11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_188_img_0_0.jpeg | score=0.928 | stage=0.146 | keyword=i; section=i
-2. page_195_img_0_0.jpeg | score=0.923 | stage=0.146 | keyword=i; section=i
-3. page_388_img_2_0.jpeg | score=0.878 | stage=0.146 | keyword=i; section=i
+          <t xml:space="preserve">1. page_196_img_0_0.jpeg | score=0.934 | stage=0.146 | keyword=i; section=i
+2. page_192_img_0_0.jpeg | score=0.930 | stage=0.146 | keyword=i; section=i
+3. page_387_img_0_0.jpeg | score=0.882 | stage=0.146 | keyword=i; section=i
 4. page_104_img_0_0.jpeg | score=0.870 | stage=0.146 | keyword=i; section=i
-5. page_189_img_0_0.jpeg | score=0.861 | stage=0.146 | keyword=i; section=i
-6. page_195_img_2_0.jpeg | score=0.834 | stage=0.146 | keyword=i; section=i
-7. page_196_img_0_0.jpeg | score=0.828 | stage=0.146 | keyword=i; section=i
-8. page_389_img_0_0.jpeg | score=0.792 | stage=0.146 | keyword=i; section=i
-9. page_165_img_0_0.jpeg | score=0.791 | stage=0.146 | keyword=i; section=i
-10. page_105_img_0_0.jpeg | score=0.777 | stage=0.146 | keyword=i; section=i</t>
+5. page_384_img_0_0.jpeg | score=0.861 | stage=0.146 | keyword=i; section=i
+6. page_195_img_2_0.jpeg | score=0.854 | stage=0.146 | keyword=i; section=i
+7. page_195_img_0_0.jpeg | score=0.813 | stage=0.146 | keyword=i; section=i
+8. page_376_img_0_0.jpeg | score=0.784 | stage=0.146 | keyword=i; section=i
+9. page_105_img_0_0.jpeg | score=0.771 | stage=0.146 | keyword=i; section=i
+10. page_96_img_0_0.jpeg | score=0.765 | stage=0.146 | keyword=i; section=i</t>
         </is>
       </c>
     </row>
@@ -1125,28 +1121,24 @@
           <t>page_188_img_0_0.jpeg</t>
         </is>
       </c>
-      <c r="N12" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="N12" s="0"/>
       <c r="O12" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_188_img_0_0.jpeg | score=1.578 | stage=0.925 | page=1.00; keyword=mount,robot settings; section=robot settings,mount
-2. page_189_img_0_0.jpeg | score=1.505 | stage=0.938 | page=1.00; keyword=mount,robot settings,y; section=robot settings,mount
-3. page_187_img_0_0.jpeg | score=1.261 | stage=0.925 | page=1.00; keyword=mount,robot settings; section=robot settings,mount
-4. page_187_img_1_0.jpeg | score=1.248 | stage=0.925 | page=1.00; keyword=mount,robot settings; section=robot settings,mount
-5. page_181_img_0_0.jpeg | score=0.813 | stage=0.013 | keyword=y
-6. page_289_img_0_0.jpeg | score=0.808 | stage=0.013 | keyword=y
-7. page_378_img_2_0.jpeg | score=0.806 | stage=0.025 | keyword=y,z
-8. page_182_img_0_0.jpeg | score=0.780 | stage=0.013 | keyword=y
-9. page_184_img_0_0.jpeg | score=0.745 | stage=0.225 | page=0.45
-10. page_195_img_0_0.jpeg | score=0.734 | stage=0.725 | page=1.00; keyword=robot settings,z; section=robot settings</t>
+          <t xml:space="preserve">1. page_192_img_0_0.jpeg | score=1.510 | stage=0.725 | page=1.00; keyword=robot settings,y; section=robot settings
+2. page_195_img_2_0.jpeg | score=1.395 | stage=0.938 | page=1.00; keyword=mount,robot settings,y; section=robot settings,mount
+3. page_196_img_0_0.jpeg | score=1.333 | stage=0.725 | page=1.00; keyword=robot settings,y; section=robot settings
+4. page_191_img_0_0.jpeg | score=1.280 | stage=0.725 | page=1.00; keyword=robot settings,y; section=robot settings
+5. page_189_img_0_0.jpeg | score=1.275 | stage=0.725 | page=1.00; keyword=robot settings,y; section=robot settings
+6. page_190_img_0_0.jpeg | score=1.246 | stage=0.725 | page=1.00; keyword=robot settings,y; section=robot settings
+7. page_195_img_0_0.jpeg | score=1.132 | stage=0.712 | page=1.00; keyword=robot settings; section=robot settings
+8. page_190_img_1_0.jpeg | score=1.073 | stage=0.712 | page=1.00; keyword=robot settings; section=robot settings
+9. page_184_img_0_0.jpeg | score=1.070 | stage=0.500 | page=1.00
+10. page_199_img_0_0.jpeg | score=1.069 | stage=0.712 | page=1.00; keyword=robot settings; section=robot settings</t>
         </is>
       </c>
     </row>
@@ -1228,16 +1220,16 @@
       </c>
       <c r="P13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_179_img_1_0.jpeg | score=1.408 | stage=0.646 | page=1.00; keyword=backdrive; section=backdrive
-2. page_178_img_0_0.jpeg | score=1.394 | stage=0.671 | page=1.00; keyword=backdrive,joint,recovery; section=backdrive
-3. page_177_img_1_0.jpeg | score=1.044 | stage=0.512 | page=1.00; keyword=servo off
-4. page_125_img_0_0.jpeg | score=0.789 | stage=0.000
-5. page_89_img_1_0.jpeg | score=0.778 | stage=0.000
-6. page_89_img_0_0.jpeg | score=0.752 | stage=0.000
-7. page_195_img_0_0.jpeg | score=0.658 | stage=0.000
-8. page_220_img_0_0.jpeg | score=0.654 | stage=0.000
-9. page_195_img_2_0.jpeg | score=0.632 | stage=0.000
-10. page_403_img_0_0.jpeg | score=0.599 | stage=0.000</t>
+          <t xml:space="preserve">1. page_179_img_1_0.jpeg | score=1.411 | stage=0.658 | page=1.00; keyword=backdrive,recovery; section=backdrive
+2. page_178_img_0_0.jpeg | score=1.389 | stage=0.658 | page=1.00; keyword=backdrive,recovery; section=backdrive
+3. page_181_img_0_0.jpeg | score=1.148 | stage=0.512 | page=1.00; keyword=recovery
+4. page_177_img_1_0.jpeg | score=1.036 | stage=0.500 | page=1.00
+5. page_125_img_0_0.jpeg | score=0.791 | stage=0.000 | 
+6. page_89_img_1_0.jpeg | score=0.776 | stage=0.000 | 
+7. page_182_img_0_0.jpeg | score=0.766 | stage=0.350 | page=0.70
+8. page_89_img_0_0.jpeg | score=0.750 | stage=0.000 | 
+9. page_24_img_0_0.jpeg | score=0.614 | stage=0.013 | keyword=emergency
+10. page_225_img_0_0.jpeg | score=0.606 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -1279,7 +1271,7 @@
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t>0.0620</t>
+          <t>0.0619</t>
         </is>
       </c>
       <c r="I14" s="0" t="inlineStr">
@@ -1309,7 +1301,7 @@
       </c>
       <c r="N14" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O14" s="0" t="inlineStr">
@@ -1319,16 +1311,16 @@
       </c>
       <c r="P14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_94_img_0_0.jpeg | score=1.371 | stage=0.500 | page=1.00
-2. page_95_img_0_0.jpeg | score=1.329 | stage=0.500 | page=1.00
-3. page_96_img_0_0.jpeg | score=1.217 | stage=0.500 | page=1.00
-4. page_103_img_0_0.jpeg | score=1.150 | stage=0.500 | page=1.00
-5. page_104_img_0_0.jpeg | score=1.099 | stage=0.500 | page=1.00
-6. page_93_img_0_0.jpeg | score=1.057 | stage=0.500 | page=1.00
-7. page_163_img_0_0.jpeg | score=0.879 | stage=0.000
-8. page_163_img_1_0.jpeg | score=0.861 | stage=0.000
-9. page_24_img_0_0.jpeg | score=0.823 | stage=0.000
-10. page_220_img_0_0.jpeg | score=0.776 | stage=0.000</t>
+          <t xml:space="preserve">1. page_94_img_0_0.jpeg | score=1.372 | stage=0.500 | page=1.00
+2. page_95_img_0_0.jpeg | score=1.317 | stage=0.500 | page=1.00
+3. page_96_img_0_0.jpeg | score=1.300 | stage=0.500 | page=1.00
+4. page_103_img_0_0.jpeg | score=1.159 | stage=0.500 | page=1.00
+5. page_104_img_0_0.jpeg | score=1.106 | stage=0.500 | page=1.00
+6. page_102_img_0_0.jpeg | score=0.880 | stage=0.500 | page=1.00
+7. page_163_img_0_0.jpeg | score=0.876 | stage=0.000 | 
+8. page_163_img_1_0.jpeg | score=0.858 | stage=0.000 | 
+9. page_93_img_0_0.jpeg | score=0.836 | stage=0.500 | page=1.00
+10. page_24_img_0_0.jpeg | score=0.818 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -1410,16 +1402,16 @@
       </c>
       <c r="P15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_173_img_1_0.jpeg | score=1.501 | stage=0.712 | page=1.00; keyword=singularity; section=singularity
-2. page_174_img_1_0.jpeg | score=1.370 | stage=0.512 | page=1.00; keyword=wrist
-3. page_175_img_1_0.jpeg | score=1.240 | stage=0.500 | page=1.00
-4. page_175_img_4_0.jpeg | score=1.057 | stage=0.500 | page=1.00
-5. page_175_img_3_0.jpeg | score=1.048 | stage=0.500 | page=1.00
-6. page_175_img_2_0.jpeg | score=1.042 | stage=0.500 | page=1.00
-7. page_277_img_0_0.jpeg | score=0.797 | stage=0.000
-8. page_242_img_0_0.jpeg | score=0.718 | stage=0.000
-9. page_278_img_1_0.jpeg | score=0.608 | stage=0.000
-10. page_276_img_0_0.jpeg | score=0.608 | stage=0.000</t>
+          <t xml:space="preserve">1. page_173_img_1_0.jpeg | score=1.494 | stage=0.712 | page=1.00; keyword=singularity; section=singularity
+2. page_174_img_1_0.jpeg | score=1.378 | stage=0.500 | page=1.00
+3. page_175_img_2_0.jpeg | score=1.327 | stage=0.500 | page=1.00
+4. page_175_img_1_0.jpeg | score=1.156 | stage=0.500 | page=1.00
+5. page_175_img_4_0.jpeg | score=1.153 | stage=0.500 | page=1.00
+6. page_175_img_3_0.jpeg | score=1.147 | stage=0.500 | page=1.00
+7. page_176_img_1_0.png | score=1.053 | stage=0.500 | page=1.00
+8. page_176_img_3_0.jpeg | score=1.049 | stage=0.500 | page=1.00
+9. page_176_img_2_0.jpeg | score=1.046 | stage=0.500 | page=1.00
+10. page_176_img_0_0.png | score=1.043 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -1485,28 +1477,24 @@
           <t>page_340_img_0_0.jpeg</t>
         </is>
       </c>
-      <c r="N16" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="N16" s="0"/>
       <c r="O16" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_363_img_0_0.jpeg | score=0.808 | stage=0.000
-2. page_182_img_0_0.jpeg | score=0.765 | stage=0.000
-3. page_340_img_0_0.jpeg | score=0.734 | stage=0.000
-4. page_368_img_0_0.jpeg | score=0.726 | stage=0.000
-5. page_364_img_1_0.jpeg | score=0.724 | stage=0.000
-6. page_169_img_2_0.jpeg | score=0.702 | stage=0.000
-7. page_342_img_2_0.jpeg | score=0.690 | stage=0.000
-8. page_349_img_0_0.jpeg | score=0.688 | stage=0.000
-9. page_369_img_0_0.jpeg | score=0.641 | stage=0.000
-10. page_361_img_0_0.jpeg | score=0.639 | stage=0.000</t>
+          <t xml:space="preserve">1. page_366_img_0_0.jpeg | score=0.812 | stage=0.000 | 
+2. page_368_img_0_0.jpeg | score=0.799 | stage=0.000 | 
+3. page_367_img_0_0.jpeg | score=0.799 | stage=0.000 | 
+4. page_369_img_0_0.jpeg | score=0.795 | stage=0.000 | 
+5. page_182_img_0_0.jpeg | score=0.791 | stage=0.000 | 
+6. page_363_img_0_0.jpeg | score=0.782 | stage=0.000 | 
+7. page_342_img_2_0.jpeg | score=0.769 | stage=0.000 | 
+8. page_370_img_0_0.jpeg | score=0.767 | stage=0.000 | 
+9. page_258_img_0_0.jpeg | score=0.698 | stage=0.000 | 
+10. page_361_img_0_0.jpeg | score=0.685 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -1588,16 +1576,16 @@
       </c>
       <c r="P17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_116_img_0_0.jpeg | score=1.371 | stage=0.500 | page=1.00
-2. page_119_img_0_0.jpeg | score=1.277 | stage=0.500 | page=1.00
-3. page_120_img_0_0.jpeg | score=1.192 | stage=0.500 | page=1.00
-4. page_119_img_1_0.jpeg | score=1.094 | stage=0.500 | page=1.00
-5. page_115_img_0_0.jpeg | score=1.040 | stage=0.500 | page=1.00
-6. page_118_img_0_0.jpeg | score=0.992 | stage=0.500 | page=1.00
-7. page_402_img_0_0.jpeg | score=0.861 | stage=0.000
-8. page_121_img_0_0.jpeg | score=0.849 | stage=0.350 | page=0.70
-9. page_401_img_0_0.jpeg | score=0.779 | stage=0.000
-10. page_401_img_1_0.jpeg | score=0.775 | stage=0.000</t>
+          <t xml:space="preserve">1. page_116_img_0_0.jpeg | score=1.366 | stage=0.500 | page=1.00
+2. page_119_img_1_0.jpeg | score=1.325 | stage=0.500 | page=1.00
+3. page_121_img_0_0.jpeg | score=1.283 | stage=0.500 | page=1.00
+4. page_123_img_0_0.jpeg | score=1.161 | stage=0.500 | page=1.00
+5. page_119_img_0_0.jpeg | score=1.123 | stage=0.500 | page=1.00
+6. page_115_img_0_0.jpeg | score=1.056 | stage=0.500 | page=1.00
+7. page_120_img_0_0.jpeg | score=1.044 | stage=0.350 | page=0.70
+8. page_124_img_0_0.jpeg | score=1.022 | stage=0.500 | page=1.00
+9. page_118_img_0_0.jpeg | score=1.004 | stage=0.500 | page=1.00
+10. page_88_img_0_0.jpeg | score=0.822 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -1679,16 +1667,16 @@
       </c>
       <c r="P18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_128_img_0_0.jpeg | score=1.424 | stage=0.612 | page=1.00; keyword=x1; section=o
-2. page_127_img_0_0.jpeg | score=1.311 | stage=0.600 | page=1.00; section=o
-3. page_132_img_0_0.png | score=1.195 | stage=0.600 | page=1.00; section=o
-4. page_130_img_0_0.jpeg | score=1.154 | stage=0.600 | page=1.00; section=o
-5. page_201_img_1_0.jpeg | score=0.777 | stage=0.100 | section=o
-6. page_336_img_0_0.jpeg | score=0.762 | stage=0.100 | section=o
-7. page_124_img_0_0.jpeg | score=0.754 | stage=0.350 | page=0.70
-8. page_94_img_0_0.jpeg | score=0.697 | stage=0.100 | section=o
-9. page_95_img_0_0.jpeg | score=0.680 | stage=0.200 | section=flange i,o
-10. page_199_img_0_0.jpeg | score=0.637 | stage=0.113 | keyword=x1; section=o</t>
+          <t xml:space="preserve">1. page_128_img_0_0.jpeg | score=1.407 | stage=0.600 | page=1.00; section=o
+2. page_130_img_0_0.jpeg | score=1.355 | stage=0.600 | page=1.00; section=o
+3. page_127_img_0_0.jpeg | score=1.346 | stage=0.600 | page=1.00; section=o
+4. page_132_img_0_0.png | score=1.314 | stage=0.600 | page=1.00; section=o
+5. page_133_img_0_0.jpeg | score=1.081 | stage=0.600 | page=1.00; section=o
+6. page_123_img_0_0.jpeg | score=1.070 | stage=0.450 | page=0.70; section=o
+7. page_124_img_0_0.jpeg | score=0.916 | stage=0.450 | page=0.70; section=o
+8. page_125_img_0_0.jpeg | score=0.912 | stage=0.450 | page=0.70; section=o
+9. page_201_img_1_0.jpeg | score=0.793 | stage=0.100 | section=o
+10. page_95_img_0_0.jpeg | score=0.695 | stage=0.100 | section=o</t>
         </is>
       </c>
     </row>
@@ -1770,16 +1758,16 @@
       </c>
       <c r="P19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_242_img_0_0.jpeg | score=1.475 | stage=0.700 | page=1.00; section=safety settings
-2. page_241_img_0_0.jpeg | score=1.350 | stage=0.700 | page=1.00; section=safety settings
-3. page_243_img_0_0.jpeg | score=1.276 | stage=0.700 | page=1.00; section=safety settings
-4. page_243_img_1_0.jpeg | score=1.181 | stage=0.700 | page=1.00; section=safety settings
-5. page_244_img_0_0.jpeg | score=1.149 | stage=0.700 | page=1.00; section=safety settings
-6. page_240_img_0_0.jpeg | score=1.103 | stage=0.700 | page=1.00; section=safety settings
-7. page_245_img_0_0.jpeg | score=1.097 | stage=0.700 | page=1.00; section=safety settings
-8. page_224_img_0_0.jpeg | score=0.806 | stage=0.213 | keyword=safety zone; section=safety settings
-9. page_238_img_0_0.jpeg | score=0.716 | stage=0.700 | page=1.00; section=safety settings
-10. page_225_img_0_0.jpeg | score=0.712 | stage=0.200 | section=safety settings</t>
+          <t xml:space="preserve">1. page_242_img_0_0.jpeg | score=1.455 | stage=0.700 | page=1.00; section=safety settings
+2. page_243_img_0_0.jpeg | score=1.369 | stage=0.700 | page=1.00; section=safety settings
+3. page_241_img_0_0.jpeg | score=1.246 | stage=0.700 | page=1.00; section=safety settings
+4. page_243_img_1_0.jpeg | score=1.166 | stage=0.700 | page=1.00; section=safety settings
+5. page_224_img_0_0.jpeg | score=1.058 | stage=0.700 | page=1.00; section=safety settings
+6. page_225_img_0_0.jpeg | score=1.042 | stage=0.700 | page=1.00; section=safety settings
+7. page_245_img_0_0.jpeg | score=1.009 | stage=0.700 | page=1.00; section=safety settings
+8. page_240_img_0_0.jpeg | score=0.978 | stage=0.700 | page=1.00; section=safety settings
+9. page_244_img_0_0.jpeg | score=0.968 | stage=0.700 | page=1.00; section=safety settings
+10. page_227_img_0_0.jpeg | score=0.946 | stage=0.712 | page=1.00; keyword=safety zone; section=safety settings</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1809,7 @@
       </c>
       <c r="H20" s="0" t="inlineStr">
         <is>
-          <t>0.1312</t>
+          <t>0.1313</t>
         </is>
       </c>
       <c r="I20" s="0" t="inlineStr">
@@ -1851,26 +1839,26 @@
       </c>
       <c r="N20" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O20" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
       <c r="P20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_375_img_0_0.jpeg | score=1.364 | stage=0.646 | page=1.00; keyword=jog; section=jog
-2. page_374_img_1_0.jpeg | score=1.286 | stage=0.500 | page=1.00
-3. page_374_img_0_0.jpeg | score=1.284 | stage=0.500 | page=1.00
-4. page_376_img_0_0.jpeg | score=1.199 | stage=0.646 | page=1.00; keyword=jog; section=jog
-5. page_373_img_0_0.jpeg | score=1.165 | stage=0.500 | page=1.00
-6. page_379_img_2_0.jpeg | score=1.014 | stage=0.500 | page=1.00
-7. page_379_img_1_0.jpeg | score=0.975 | stage=0.500 | page=1.00
-8. page_378_img_2_0.jpeg | score=0.898 | stage=0.500 | page=1.00
-9. page_379_img_0_0.jpeg | score=0.895 | stage=0.500 | page=1.00
-10. page_381_img_0_0.jpeg | score=0.886 | stage=0.500 | page=1.00</t>
+          <t xml:space="preserve">1. page_374_img_1_0.jpeg | score=1.459 | stage=0.658 | page=1.00; keyword=jog,manual; section=jog
+2. page_375_img_0_0.jpeg | score=1.409 | stage=0.658 | page=1.00; keyword=jog,manual; section=jog
+3. page_374_img_0_0.jpeg | score=1.374 | stage=0.512 | page=1.00; keyword=manual
+4. page_384_img_0_0.jpeg | score=1.137 | stage=0.512 | page=1.00; keyword=manual
+5. page_376_img_0_0.jpeg | score=1.137 | stage=0.500 | page=1.00
+6. page_379_img_2_0.jpeg | score=1.051 | stage=0.512 | page=1.00; keyword=manual
+7. page_373_img_0_0.jpeg | score=1.024 | stage=0.500 | page=1.00
+8. page_379_img_1_0.jpeg | score=1.010 | stage=0.512 | page=1.00; keyword=manual
+9. page_378_img_2_0.jpeg | score=0.947 | stage=0.512 | page=1.00; keyword=manual
+10. page_379_img_0_0.jpeg | score=0.903 | stage=0.512 | page=1.00; keyword=manual</t>
         </is>
       </c>
     </row>
@@ -1952,16 +1940,16 @@
       </c>
       <c r="P21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_202_img_1_0.jpeg | score=1.548 | stage=0.875 | page=1.00; keyword=tool settings,tcp,tool center point,x; section=tool settings,tool center point,tcp
-2. page_201_img_1_0.jpeg | score=1.524 | stage=0.875 | page=1.00; keyword=tool settings,tcp,tool center point,x; section=tool settings,tool center point,tcp
-3. page_203_img_0_0.jpeg | score=1.400 | stage=0.762 | page=1.00; keyword=tool settings,tcp,x,y; section=tool settings,tcp
-4. page_202_img_0_0.jpeg | score=1.331 | stage=0.875 | page=1.00; keyword=tool settings,tcp,tool center point,x; section=tool settings,tool center point,tcp
-5. page_201_img_0_0.jpeg | score=1.309 | stage=0.875 | page=1.00; keyword=tool settings,tcp,tool center point,x; section=tool settings,tool center point,tcp
-6. page_208_img_0_0.jpeg | score=1.154 | stage=0.637 | page=1.00; keyword=tool settings,y,simulation; section=tool settings
-7. page_204_img_0_0.jpeg | score=1.082 | stage=0.762 | page=1.00; keyword=tool settings,tcp,x,y; section=tool settings,tcp
-8. page_204_img_1_0.jpeg | score=1.011 | stage=0.762 | page=1.00; keyword=tool settings,tcp,x,y; section=tool settings,tcp
-9. page_244_img_0_0.jpeg | score=0.945 | stage=0.138 | keyword=tcp,y,z; section=tcp
-10. page_206_img_0_0.jpeg | score=0.913 | stage=0.625 | page=1.00; keyword=tool settings,y; section=tool settings</t>
+          <t xml:space="preserve">1. page_202_img_1_0.jpeg | score=1.528 | stage=0.863 | page=1.00; keyword=tool settings,tcp,tool center point,x; section=tool settings,tool center point,tcp
+2. page_201_img_1_0.jpeg | score=1.489 | stage=0.863 | page=1.00; keyword=tool settings,tcp,tool center point,x; section=tool settings,tool center point,tcp
+3. page_203_img_0_0.jpeg | score=1.431 | stage=0.650 | page=1.00; keyword=tool settings,x,y,z; section=tool settings
+4. page_204_img_1_0.jpeg | score=1.414 | stage=0.750 | page=1.00; keyword=tool settings,tcp,x,y; section=tool settings,tcp
+5. page_209_img_0_0.jpeg | score=1.408 | stage=0.650 | page=1.00; keyword=tool settings,x,y,z; section=tool settings
+6. page_208_img_0_0.jpeg | score=1.382 | stage=0.650 | page=1.00; keyword=tool settings,x,y,z; section=tool settings
+7. page_201_img_0_0.jpeg | score=1.268 | stage=0.863 | page=1.00; keyword=tool settings,tcp,tool center point,x; section=tool settings,tool center point,tcp
+8. page_210_img_2_0.jpeg | score=1.236 | stage=0.612 | page=1.00; keyword=tool settings; section=tool settings
+9. page_244_img_0_0.jpeg | score=1.226 | stage=0.375 | page=0.70; keyword=x,y
+10. page_202_img_0_0.jpeg | score=1.208 | stage=0.650 | page=1.00; keyword=tool settings,x,y,z; section=tool settings</t>
         </is>
       </c>
     </row>
@@ -2014,24 +2002,24 @@
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M22" s="0" t="inlineStr">
+        <is>
+          <t>page_241_img_0_0.jpeg</t>
+        </is>
+      </c>
+      <c r="N22" s="0" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="L22" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M22" s="0" t="inlineStr">
-        <is>
-          <t>page_241_img_0_0.jpeg</t>
-        </is>
-      </c>
-      <c r="N22" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="O22" s="0" t="inlineStr">
         <is>
           <t>O</t>
@@ -2039,16 +2027,16 @@
       </c>
       <c r="P22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_225_img_0_0.jpeg | score=0.888 | stage=0.000
-2. page_224_img_0_0.jpeg | score=0.869 | stage=0.000
-3. page_241_img_0_0.jpeg | score=0.835 | stage=0.000
-4. page_240_img_0_0.jpeg | score=0.814 | stage=0.000
-5. page_242_img_0_0.jpeg | score=0.797 | stage=0.000
-6. page_226_img_0_0.jpeg | score=0.797 | stage=0.000
-7. page_239_img_0_0.jpeg | score=0.707 | stage=0.000
-8. page_220_img_0_0.jpeg | score=0.664 | stage=0.000
-9. page_237_img_0_0.jpeg | score=0.621 | stage=0.000
-10. page_226_img_2_0.jpeg | score=0.603 | stage=0.000</t>
+          <t xml:space="preserve">1. page_224_img_0_0.jpeg | score=0.875 | stage=0.000 | 
+2. page_225_img_0_0.jpeg | score=0.862 | stage=0.000 | 
+3. page_240_img_0_0.jpeg | score=0.814 | stage=0.000 | 
+4. page_241_img_0_0.jpeg | score=0.814 | stage=0.000 | 
+5. page_243_img_0_0.jpeg | score=0.811 | stage=0.000 | 
+6. page_242_img_0_0.jpeg | score=0.801 | stage=0.000 | 
+7. page_236_img_0_0.jpeg | score=0.761 | stage=0.000 | 
+8. page_227_img_0_0.jpeg | score=0.728 | stage=0.000 | 
+9. page_226_img_2_0.jpeg | score=0.719 | stage=0.000 | 
+10. page_235_img_1_0.jpeg | score=0.714 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -2105,7 +2093,7 @@
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L23" s="0" t="inlineStr">
@@ -2126,16 +2114,16 @@
       </c>
       <c r="P23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_271_img_1_0.jpeg | score=1.072 | stage=0.512 | page=1.00; keyword=radius
-2. page_271_img_0_0.jpeg | score=1.056 | stage=0.512 | page=1.00; keyword=radius
-3. page_277_img_0_0.jpeg | score=1.013 | stage=0.500 | page=1.00
-4. page_316_img_0_0.jpeg | score=0.833 | stage=0.000
-5. page_278_img_1_0.jpeg | score=0.821 | stage=0.500 | page=1.00
-6. page_276_img_0_0.jpeg | score=0.814 | stage=0.500 | page=1.00
-7. page_312_img_0_0.jpeg | score=0.743 | stage=0.013 | keyword=tcp
-8. page_313_img_0_0.jpeg | score=0.692 | stage=0.000
-9. page_104_img_0_0.jpeg | score=0.588 | stage=0.000
-10. page_398_img_0_0.jpeg | score=0.528 | stage=0.000</t>
+          <t xml:space="preserve">1. page_275_img_0_0.jpeg | score=1.323 | stage=0.792 | page=1.00; keyword=movej,movel; section=movej,movel
+2. page_278_img_1_0.jpeg | score=1.251 | stage=0.500 | page=1.00
+3. page_277_img_0_0.jpeg | score=1.120 | stage=0.500 | page=1.00
+4. page_271_img_1_0.jpeg | score=1.065 | stage=0.512 | page=1.00; keyword=radius
+5. page_276_img_0_0.jpeg | score=1.030 | stage=0.500 | page=1.00
+6. page_281_img_1_0.jpeg | score=0.953 | stage=0.500 | page=1.00
+7. page_279_img_0_0.jpeg | score=0.950 | stage=0.500 | page=1.00
+8. page_280_img_0_0.jpeg | score=0.945 | stage=0.500 | page=1.00
+9. page_271_img_0_0.jpeg | score=0.894 | stage=0.500 | page=1.00
+10. page_316_img_0_0.jpeg | score=0.834 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -2177,7 +2165,7 @@
       </c>
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t>0.0381</t>
+          <t>0.0380</t>
         </is>
       </c>
       <c r="I24" s="0" t="inlineStr">
@@ -2192,7 +2180,7 @@
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
@@ -2207,26 +2195,26 @@
       </c>
       <c r="N24" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O24" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_165_img_0_0.jpeg | score=1.435 | stage=0.646 | page=1.00; keyword=header; section=header
-2. page_166_img_1_0.jpeg | score=1.338 | stage=0.646 | page=1.00; keyword=header; section=header
-3. page_168_img_0_0.jpeg | score=1.316 | stage=0.500 | page=1.00
-4. page_168_img_1_0.png | score=1.111 | stage=0.500 | page=1.00
-5. page_164_img_1_0.jpeg | score=1.078 | stage=0.500 | page=1.00
-6. page_169_img_2_0.jpeg | score=1.034 | stage=0.500 | page=1.00
-7. page_167_img_3_0.jpeg | score=1.030 | stage=0.500 | page=1.00
-8. page_169_img_1_0.png | score=1.003 | stage=0.500 | page=1.00
-9. page_167_img_2_0.jpeg | score=0.872 | stage=0.500 | page=1.00
-10. page_357_img_0_0.jpeg | score=0.813 | stage=0.000</t>
+          <t xml:space="preserve">1. page_168_img_0_0.jpeg | score=1.045 | stage=0.512 | page=1.00; keyword=dart-platform
+2. page_165_img_0_0.jpeg | score=0.991 | stage=0.500 | page=1.00
+3. page_167_img_2_0.jpeg | score=0.885 | stage=0.512 | page=1.00; keyword=dart-platform
+4. page_167_img_3_0.jpeg | score=0.879 | stage=0.512 | page=1.00; keyword=dart-platform
+5. page_168_img_1_0.png | score=0.855 | stage=0.512 | page=1.00; keyword=dart-platform
+6. page_169_img_1_0.png | score=0.852 | stage=0.512 | page=1.00; keyword=dart-platform
+7. page_166_img_1_0.jpeg | score=0.815 | stage=0.500 | page=1.00
+8. page_357_img_0_0.jpeg | score=0.771 | stage=0.000 | 
+9. page_259_img_1_0.jpeg | score=0.733 | stage=0.000 | 
+10. page_258_img_0_0.jpeg | score=0.725 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -2268,7 +2256,7 @@
       </c>
       <c r="H25" s="0" t="inlineStr">
         <is>
-          <t>0.0563</t>
+          <t>0.0562</t>
         </is>
       </c>
       <c r="I25" s="0" t="inlineStr">
@@ -2298,7 +2286,7 @@
       </c>
       <c r="N25" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O25" s="0" t="inlineStr">
@@ -2308,16 +2296,16 @@
       </c>
       <c r="P25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_276_img_0_0.jpeg | score=1.459 | stage=0.804 | page=1.00; keyword=movej,movel,tcp; section=movej,movel
-2. page_275_img_0_0.jpeg | score=1.348 | stage=0.829 | page=1.00; keyword=movej,movel,motion,linear; section=movej,movel
-3. page_277_img_0_0.jpeg | score=1.210 | stage=0.512 | page=1.00; keyword=tcp
-4. page_269_img_0_0.jpeg | score=0.994 | stage=0.512 | page=1.00; keyword=tcp
-5. page_267_img_1_0.jpeg | score=0.981 | stage=0.792 | page=1.00; keyword=movej,movel; section=movej,movel
-6. page_195_img_0_0.jpeg | score=0.817 | stage=0.000
-7. page_195_img_2_0.jpeg | score=0.791 | stage=0.000
-8. page_271_img_1_0.jpeg | score=0.769 | stage=0.512 | page=1.00; keyword=radius
-9. page_271_img_0_0.jpeg | score=0.754 | stage=0.512 | page=1.00; keyword=radius
-10. page_196_img_0_0.jpeg | score=0.715 | stage=0.000</t>
+          <t xml:space="preserve">1. page_275_img_0_0.jpeg | score=1.337 | stage=0.792 | page=1.00; keyword=movej,movel; section=movej,movel
+2. page_276_img_0_0.jpeg | score=1.308 | stage=0.500 | page=1.00
+3. page_277_img_0_0.jpeg | score=1.293 | stage=0.500 | page=1.00
+4. page_278_img_1_0.jpeg | score=1.132 | stage=0.500 | page=1.00
+5. page_281_img_1_0.jpeg | score=1.119 | stage=0.500 | page=1.00
+6. page_280_img_0_0.jpeg | score=1.106 | stage=0.500 | page=1.00
+7. page_279_img_0_0.jpeg | score=1.100 | stage=0.500 | page=1.00
+8. page_267_img_1_0.jpeg | score=0.927 | stage=0.792 | page=1.00; keyword=movej,movel; section=movej,movel
+9. page_271_img_1_0.jpeg | score=0.842 | stage=0.512 | page=1.00; keyword=radius
+10. page_271_img_0_0.jpeg | score=0.796 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2358,7 @@
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L26" s="0" t="inlineStr">
@@ -2395,16 +2383,16 @@
       </c>
       <c r="P26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_378_img_2_0.jpeg | score=0.883 | stage=0.000
-2. page_374_img_1_0.jpeg | score=0.818 | stage=0.000
-3. page_374_img_0_0.jpeg | score=0.817 | stage=0.000
-4. page_379_img_2_0.jpeg | score=0.763 | stage=0.000
-5. page_375_img_0_0.jpeg | score=0.705 | stage=0.000
-6. page_275_img_0_0.jpeg | score=0.705 | stage=0.000
-7. page_378_img_0_0.jpeg | score=0.670 | stage=0.000
-8. page_373_img_0_0.jpeg | score=0.650 | stage=0.000
-9. page_379_img_1_0.jpeg | score=0.634 | stage=0.000
-10. page_269_img_0_0.jpeg | score=0.628 | stage=0.000</t>
+          <t xml:space="preserve">1. page_378_img_2_0.jpeg | score=0.870 | stage=0.000 | 
+2. page_379_img_2_0.jpeg | score=0.866 | stage=0.000 | 
+3. page_374_img_1_0.jpeg | score=0.832 | stage=0.000 | 
+4. page_374_img_0_0.jpeg | score=0.830 | stage=0.000 | 
+5. page_384_img_0_0.jpeg | score=0.812 | stage=0.000 | 
+6. page_275_img_0_0.jpeg | score=0.766 | stage=0.000 | 
+7. page_375_img_0_0.jpeg | score=0.725 | stage=0.000 | 
+8. page_379_img_1_0.jpeg | score=0.722 | stage=0.000 | 
+9. page_379_img_0_0.jpeg | score=0.682 | stage=0.000 | 
+10. page_267_img_1_0.jpeg | score=0.673 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -2446,7 +2434,7 @@
       </c>
       <c r="H27" s="0" t="inlineStr">
         <is>
-          <t>0.1249</t>
+          <t>0.1250</t>
         </is>
       </c>
       <c r="I27" s="0" t="inlineStr">
@@ -2476,26 +2464,26 @@
       </c>
       <c r="N27" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O27" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_167_img_3_0.jpeg | score=1.326 | stage=0.500 | page=1.00
-2. page_361_img_0_0.jpeg | score=1.321 | stage=0.712 | page=1.00; keyword=robot update; section=robot update
-3. page_361_img_1_0.jpeg | score=1.318 | stage=0.712 | page=1.00; keyword=robot update; section=robot update
-4. page_366_img_0_0.jpeg | score=1.287 | stage=0.500 | page=1.00
-5. page_168_img_0_0.jpeg | score=1.240 | stage=0.500 | page=1.00
-6. page_360_img_0_0.jpeg | score=1.203 | stage=0.712 | page=1.00; keyword=robot update; section=robot update
-7. page_367_img_0_0.jpeg | score=1.188 | stage=0.500 | page=1.00
-8. page_167_img_2_0.jpeg | score=1.138 | stage=0.500 | page=1.00
-9. page_361_img_2_0.png | score=1.081 | stage=0.712 | page=1.00; keyword=robot update; section=robot update
-10. page_166_img_1_0.jpeg | score=1.073 | stage=0.500 | page=1.00</t>
+          <t xml:space="preserve">1. page_361_img_0_0.jpeg | score=1.440 | stage=0.712 | page=1.00; keyword=robot update; section=robot update
+2. page_361_img_1_0.jpeg | score=1.436 | stage=0.712 | page=1.00; keyword=robot update; section=robot update
+3. page_167_img_2_0.jpeg | score=1.301 | stage=0.500 | page=1.00
+4. page_366_img_0_0.jpeg | score=1.290 | stage=0.500 | page=1.00
+5. page_360_img_0_0.jpeg | score=1.233 | stage=0.712 | page=1.00; keyword=robot update; section=robot update
+6. page_363_img_0_0.jpeg | score=1.228 | stage=0.712 | page=1.00; keyword=robot update; section=robot update
+7. page_364_img_1_0.jpeg | score=1.217 | stage=0.712 | page=1.00; keyword=robot update; section=robot update
+8. page_168_img_0_0.jpeg | score=1.208 | stage=0.500 | page=1.00
+9. page_361_img_2_0.png | score=1.204 | stage=0.712 | page=1.00; keyword=robot update; section=robot update
+10. page_367_img_0_0.jpeg | score=1.185 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2525,7 @@
       </c>
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t>0.2173</t>
+          <t>0.2172</t>
         </is>
       </c>
       <c r="I28" s="0" t="inlineStr">
@@ -2577,16 +2565,16 @@
       </c>
       <c r="P28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_370_img_0_0.jpeg | score=1.480 | stage=0.725 | page=1.00; keyword=factory reset,reset; section=factory reset
-2. page_369_img_0_0.jpeg | score=1.261 | stage=0.500 | page=1.00
-3. page_368_img_0_0.jpeg | score=1.098 | stage=0.500 | page=1.00
-4. page_364_img_1_0.jpeg | score=0.942 | stage=0.350 | page=0.70
-5. page_363_img_0_0.jpeg | score=0.908 | stage=0.225 | page=0.45
-6. page_367_img_0_0.jpeg | score=0.855 | stage=0.500 | page=1.00
-7. page_213_img_0_0.jpeg | score=0.734 | stage=0.013 | keyword=reset
-8. page_214_img_0_0.jpeg | score=0.713 | stage=0.013 | keyword=reset
-9. page_182_img_0_0.jpeg | score=0.694 | stage=0.000
-10. page_197_img_0_0.jpeg | score=0.656 | stage=0.000</t>
+          <t xml:space="preserve">1. page_370_img_0_0.jpeg | score=1.323 | stage=0.500 | page=1.00
+2. page_369_img_0_0.jpeg | score=1.216 | stage=0.500 | page=1.00
+3. page_363_img_0_0.jpeg | score=1.188 | stage=0.500 | page=1.00
+4. page_361_img_0_0.jpeg | score=1.067 | stage=0.500 | page=1.00
+5. page_361_img_1_0.jpeg | score=1.064 | stage=0.500 | page=1.00
+6. page_368_img_0_0.jpeg | score=1.046 | stage=0.500 | page=1.00
+7. page_361_img_2_0.png | score=0.964 | stage=0.500 | page=1.00
+8. page_364_img_1_0.jpeg | score=0.924 | stage=0.500 | page=1.00
+9. page_360_img_0_0.jpeg | score=0.791 | stage=0.500 | page=1.00
+10. page_228_img_0_0.jpeg | score=0.745 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -2643,7 +2631,7 @@
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
@@ -2656,28 +2644,24 @@
           <t>page_405_img_0_0.jpeg</t>
         </is>
       </c>
-      <c r="N29" s="0" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="N29" s="0"/>
       <c r="O29" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_405_img_5_0.jpeg | score=1.294 | stage=0.646 | page=1.00; keyword=grommet; section=grommet
-2. page_405_img_3_0.jpeg | score=1.290 | stage=0.646 | page=1.00; keyword=grommet; section=grommet
-3. page_403_img_0_0.jpeg | score=1.224 | stage=0.350 | page=0.70
-4. page_405_img_4_0.jpeg | score=1.125 | stage=0.646 | page=1.00; keyword=grommet; section=grommet
-5. page_405_img_2_0.jpeg | score=1.123 | stage=0.646 | page=1.00; keyword=grommet; section=grommet
-6. page_405_img_1_0.jpeg | score=1.120 | stage=0.646 | page=1.00; keyword=grommet; section=grommet
-7. page_405_img_0_0.jpeg | score=1.106 | stage=0.646 | page=1.00; keyword=grommet; section=grommet
-8. page_401_img_1_0.jpeg | score=0.920 | stage=0.225 | page=0.45
-9. page_402_img_0_0.jpeg | score=0.911 | stage=0.350 | page=0.70
-10. page_402_img_1_0.jpeg | score=0.910 | stage=0.350 | page=0.70</t>
+          <t xml:space="preserve">1. page_398_img_0_0.jpeg | score=1.339 | stage=0.500 | page=1.00
+2. page_397_img_0_0.jpeg | score=1.335 | stage=0.500 | page=1.00
+3. page_405_img_3_0.jpeg | score=1.322 | stage=0.646 | page=1.00; keyword=grommet; section=grommet
+4. page_405_img_5_0.jpeg | score=1.319 | stage=0.646 | page=1.00; keyword=grommet; section=grommet
+5. page_403_img_0_0.jpeg | score=1.190 | stage=0.500 | page=1.00
+6. page_402_img_0_0.jpeg | score=1.138 | stage=0.500 | page=1.00
+7. page_402_img_1_0.jpeg | score=1.136 | stage=0.500 | page=1.00
+8. page_401_img_1_0.jpeg | score=1.133 | stage=0.500 | page=1.00
+9. page_400_img_0_0.jpeg | score=1.130 | stage=0.500 | page=1.00
+10. page_405_img_1_0.jpeg | score=1.128 | stage=0.646 | page=1.00; keyword=grommet; section=grommet</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2699,7 @@
       </c>
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t>0.0170</t>
+          <t>0.0169</t>
         </is>
       </c>
       <c r="I30" s="0" t="inlineStr">
@@ -2751,16 +2735,16 @@
       </c>
       <c r="P30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_201_img_1_0.jpeg | score=0.881 | stage=0.000
-2. page_202_img_1_0.jpeg | score=0.876 | stage=0.000
-3. page_110_img_0_0.jpeg | score=0.794 | stage=0.000
-4. page_175_img_1_0.jpeg | score=0.768 | stage=0.000
-5. page_175_img_3_0.jpeg | score=0.763 | stage=0.000
-6. page_203_img_0_0.jpeg | score=0.759 | stage=0.000
-7. page_244_img_0_0.jpeg | score=0.753 | stage=0.000
-8. page_378_img_2_0.jpeg | score=0.726 | stage=0.000
-9. page_389_img_0_0.jpeg | score=0.726 | stage=0.000
-10. page_201_img_0_0.jpeg | score=0.685 | stage=0.000</t>
+          <t xml:space="preserve">1. page_201_img_1_0.jpeg | score=0.885 | stage=0.000 | 
+2. page_202_img_1_0.jpeg | score=0.876 | stage=0.000 | 
+3. page_203_img_0_0.jpeg | score=0.876 | stage=0.000 | 
+4. page_110_img_0_0.jpeg | score=0.791 | stage=0.000 | 
+5. page_176_img_3_0.jpeg | score=0.783 | stage=0.000 | 
+6. page_176_img_0_0.png | score=0.782 | stage=0.000 | 
+7. page_204_img_1_0.jpeg | score=0.775 | stage=0.000 | 
+8. page_378_img_2_0.jpeg | score=0.769 | stage=0.000 | 
+9. page_204_img_0_0.jpeg | score=0.757 | stage=0.000 | 
+10. page_381_img_0_0.jpeg | score=0.751 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -2832,7 +2816,7 @@
       </c>
       <c r="N31" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O31" s="0" t="inlineStr">
@@ -2842,16 +2826,16 @@
       </c>
       <c r="P31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_403_img_0_0.jpeg | score=1.446 | stage=0.633 | page=1.00; section=cs-12p
-2. page_399_img_0_0.jpeg | score=1.345 | stage=0.633 | page=1.00; section=cs-12p
-3. page_400_img_0_0.jpeg | score=1.289 | stage=0.633 | page=1.00; section=cs-12p
-4. page_402_img_0_0.jpeg | score=1.205 | stage=0.633 | page=1.00; section=cs-12p
-5. page_402_img_1_0.jpeg | score=1.125 | stage=0.633 | page=1.00; section=cs-12p
-6. page_398_img_0_0.jpeg | score=1.061 | stage=0.633 | page=1.00; section=cs-12p
-7. page_401_img_1_0.jpeg | score=0.905 | stage=0.633 | page=1.00; section=cs-12p
-8. page_401_img_0_0.jpeg | score=0.881 | stage=0.633 | page=1.00; section=cs-12p
-9. page_121_img_0_0.jpeg | score=0.853 | stage=0.000
-10. page_120_img_0_0.jpeg | score=0.711 | stage=0.000</t>
+          <t xml:space="preserve">1. page_398_img_0_0.jpeg | score=1.101 | stage=0.633 | page=1.00; section=cs-12p
+2. page_397_img_0_0.jpeg | score=1.096 | stage=0.633 | page=1.00; section=cs-12p
+3. page_403_img_0_0.jpeg | score=1.082 | stage=0.633 | page=1.00; section=cs-12p
+4. page_402_img_1_0.jpeg | score=0.952 | stage=0.633 | page=1.00; section=cs-12p
+5. page_402_img_0_0.jpeg | score=0.949 | stage=0.633 | page=1.00; section=cs-12p
+6. page_400_img_0_0.jpeg | score=0.935 | stage=0.633 | page=1.00; section=cs-12p
+7. page_401_img_1_0.jpeg | score=0.932 | stage=0.633 | page=1.00; section=cs-12p
+8. page_399_img_0_0.jpeg | score=0.923 | stage=0.633 | page=1.00; section=cs-12p
+9. page_401_img_0_0.jpeg | score=0.921 | stage=0.633 | page=1.00; section=cs-12p
+10. page_121_img_0_0.jpeg | score=0.863 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -2893,7 +2877,7 @@
       </c>
       <c r="H32" s="0" t="inlineStr">
         <is>
-          <t>0.0947</t>
+          <t>0.0946</t>
         </is>
       </c>
       <c r="I32" s="0" t="inlineStr">
@@ -2933,16 +2917,16 @@
       </c>
       <c r="P32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_102_img_0_0.jpeg | score=1.423 | stage=0.712 | page=1.00; keyword=usb; section=usb
-2. page_104_img_0_0.jpeg | score=1.231 | stage=0.500 | page=1.00
-3. page_103_img_0_0.jpeg | score=1.187 | stage=0.500 | page=1.00
-4. page_105_img_0_0.jpeg | score=1.129 | stage=0.500 | page=1.00
-5. page_105_img_1_0.jpeg | score=0.957 | stage=0.500 | page=1.00
-6. page_101_img_0_0.jpeg | score=0.939 | stage=0.500 | page=1.00
-7. page_100_img_0_0.jpeg | score=0.894 | stage=0.500 | page=1.00
-8. page_401_img_0_0.jpeg | score=0.861 | stage=0.000
-9. page_401_img_1_0.jpeg | score=0.857 | stage=0.000
-10. page_119_img_0_0.jpeg | score=0.807 | stage=0.000</t>
+          <t xml:space="preserve">1. page_102_img_0_0.jpeg | score=1.346 | stage=0.500 | page=1.00
+2. page_104_img_0_0.jpeg | score=1.229 | stage=0.500 | page=1.00
+3. page_103_img_0_0.jpeg | score=1.202 | stage=0.500 | page=1.00
+4. page_105_img_0_0.jpeg | score=1.117 | stage=0.500 | page=1.00
+5. page_101_img_0_0.jpeg | score=1.039 | stage=0.500 | page=1.00
+6. page_105_img_1_0.jpeg | score=0.935 | stage=0.500 | page=1.00
+7. page_119_img_1_0.jpeg | score=0.831 | stage=0.000 | 
+8. page_95_img_0_0.jpeg | score=0.824 | stage=0.000 | 
+9. page_96_img_0_0.jpeg | score=0.793 | stage=0.000 | 
+10. page_163_img_0_0.jpeg | score=0.790 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -2995,12 +2979,12 @@
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
       <c r="M33" s="0" t="inlineStr">
@@ -3008,24 +2992,28 @@
           <t>page_192_img_0_0.jpeg</t>
         </is>
       </c>
-      <c r="N33" s="0"/>
+      <c r="N33" s="0" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="O33" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>△</t>
         </is>
       </c>
       <c r="P33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_181_img_0_0.jpeg | score=0.827 | stage=0.000
-2. page_182_img_0_0.jpeg | score=0.792 | stage=0.000
-3. page_195_img_0_0.jpeg | score=0.737 | stage=0.000
-4. page_195_img_2_0.jpeg | score=0.713 | stage=0.000
-5. page_178_img_0_0.jpeg | score=0.675 | stage=0.000
-6. page_188_img_0_0.jpeg | score=0.617 | stage=0.000
-7. page_189_img_0_0.jpeg | score=0.587 | stage=0.000
-8. page_184_img_0_0.jpeg | score=0.559 | stage=0.000
-9. page_298_img_2_0.jpeg | score=0.558 | stage=0.000
-10. page_293_img_1_0.jpeg | score=0.553 | stage=0.000</t>
+          <t xml:space="preserve">1. page_181_img_0_0.jpeg | score=0.736 | stage=0.000 | 
+2. page_84_img_0_0.jpeg | score=0.712 | stage=0.000 | 
+3. page_323_img_0_0.jpeg | score=0.692 | stage=0.000 | 
+4. page_92_img_1_0.jpeg | score=0.670 | stage=0.000 | 
+5. page_83_img_0_0.jpeg | score=0.664 | stage=0.000 | 
+6. page_325_img_0_0.jpeg | score=0.660 | stage=0.000 | 
+7. page_323_img_1_0.jpeg | score=0.660 | stage=0.000 | 
+8. page_192_img_0_0.jpeg | score=0.644 | stage=0.000 | 
+9. page_324_img_0_0.jpeg | score=0.634 | stage=0.000 | 
+10. page_184_img_0_0.jpeg | score=0.588 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -3107,16 +3095,16 @@
       </c>
       <c r="P34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_353_img_1_0.jpeg | score=1.516 | stage=0.762 | page=1.00; keyword=supervisor,password,admin,safety password; section=supervisor password,safety password
-2. page_352_img_3_0.jpeg | score=1.431 | stage=0.662 | page=1.00; keyword=password,admin,safety password,lock; section=safety password
-3. page_353_img_0_0.png | score=1.320 | stage=0.762 | page=1.00; keyword=supervisor,password,admin,safety password; section=supervisor password,safety password
-4. page_352_img_1_0.png | score=1.242 | stage=0.662 | page=1.00; keyword=password,admin,safety password,lock; section=safety password
-5. page_354_img_0_0.jpeg | score=1.126 | stage=0.625 | page=1.00; keyword=supervisor,password; section=supervisor password
-6. page_350_img_0_0.jpeg | score=1.014 | stage=0.512 | page=1.00; keyword=setting
-7. page_285_img_0_0.jpeg | score=0.862 | stage=0.150 | keyword=password,admin,safety password,setting; section=safety password
-8. page_296_img_0_0.jpeg | score=0.756 | stage=0.013 | keyword=setting
-9. page_169_img_2_0.jpeg | score=0.742 | stage=0.000
-10. page_214_img_0_0.jpeg | score=0.726 | stage=0.150 | keyword=password,safety password,lock,setting; section=safety password</t>
+          <t xml:space="preserve">1. page_353_img_1_0.jpeg | score=1.443 | stage=0.625 | page=1.00; keyword=supervisor,password; section=supervisor password
+2. page_352_img_3_0.jpeg | score=1.325 | stage=0.512 | page=1.00; keyword=password
+3. page_353_img_0_0.png | score=1.239 | stage=0.625 | page=1.00; keyword=supervisor,password; section=supervisor password
+4. page_354_img_0_0.jpeg | score=1.200 | stage=0.500 | page=1.00
+5. page_352_img_1_0.png | score=1.136 | stage=0.500 | page=1.00
+6. page_355_img_1_0.jpeg | score=0.871 | stage=0.500 | page=1.00
+7. page_355_img_0_0.jpeg | score=0.858 | stage=0.500 | page=1.00
+8. page_350_img_0_0.jpeg | score=0.838 | stage=0.500 | page=1.00
+9. page_169_img_2_0.jpeg | score=0.725 | stage=0.000 | 
+10. page_330_img_0_0.jpeg | score=0.710 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -3188,7 +3176,7 @@
       </c>
       <c r="N35" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O35" s="0" t="inlineStr">
@@ -3198,16 +3186,16 @@
       </c>
       <c r="P35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_181_img_0_0.jpeg | score=1.452 | stage=0.712 | page=1.00; keyword=recovery; section=recovery
-2. page_182_img_0_0.jpeg | score=1.413 | stage=0.712 | page=1.00; keyword=recovery; section=recovery
-3. page_184_img_0_0.jpeg | score=1.185 | stage=0.525 | page=1.00; keyword=joint,task
-4. page_186_img_0_0.jpeg | score=1.144 | stage=0.712 | page=1.00; keyword=recovery; section=recovery
-5. page_178_img_0_0.jpeg | score=0.972 | stage=0.450 | page=0.45; keyword=recovery,joint; section=recovery
-6. page_179_img_1_0.jpeg | score=0.785 | stage=0.350 | page=0.70
-7. page_177_img_1_0.jpeg | score=0.672 | stage=0.225 | page=0.45
-8. page_92_img_1_0.jpeg | score=0.619 | stage=0.213 | keyword=recovery; section=recovery
-9. page_48_img_0_0.jpeg | score=0.539 | stage=0.000
-10. page_24_img_0_0.jpeg | score=0.536 | stage=0.000</t>
+          <t xml:space="preserve">1. page_181_img_0_0.jpeg | score=1.445 | stage=0.712 | page=1.00; keyword=recovery; section=recovery
+2. page_184_img_0_0.jpeg | score=1.262 | stage=0.500 | page=1.00
+3. page_178_img_0_0.jpeg | score=1.209 | stage=0.712 | page=1.00; keyword=recovery; section=recovery
+4. page_182_img_0_0.jpeg | score=1.156 | stage=0.500 | page=1.00
+5. page_179_img_1_0.jpeg | score=1.073 | stage=0.712 | page=1.00; keyword=recovery; section=recovery
+6. page_186_img_0_0.jpeg | score=0.963 | stage=0.500 | page=1.00
+7. page_187_img_0_0.jpeg | score=0.890 | stage=0.500 | page=1.00
+8. page_187_img_1_0.jpeg | score=0.883 | stage=0.500 | page=1.00
+9. page_48_img_0_0.jpeg | score=0.654 | stage=0.000 | 
+10. page_92_img_1_0.jpeg | score=0.639 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -3245,7 +3233,7 @@
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t>0.0130</t>
+          <t>0.0129</t>
         </is>
       </c>
       <c r="I36" s="0" t="inlineStr">
@@ -3285,16 +3273,16 @@
       </c>
       <c r="P36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_144_img_0_0.jpeg | score=0.868 | stage=0.000
-2. page_144_img_1_0.jpeg | score=0.865 | stage=0.000
-3. page_140_img_0_0.jpeg | score=0.845 | stage=0.000
-4. page_141_img_1_0.jpeg | score=0.829 | stage=0.000
-5. page_133_img_0_0.jpeg | score=0.806 | stage=0.000
-6. page_136_img_0_0.png | score=0.789 | stage=0.000
-7. page_95_img_0_0.jpeg | score=0.755 | stage=0.000
-8. page_143_img_1_0.jpeg | score=0.740 | stage=0.000
-9. page_143_img_0_0.jpeg | score=0.739 | stage=0.000
-10. page_145_img_0_0.jpeg | score=0.734 | stage=0.000</t>
+          <t xml:space="preserve">1. page_144_img_0_0.jpeg | score=0.864 | stage=0.000 | 
+2. page_144_img_1_0.jpeg | score=0.860 | stage=0.000 | 
+3. page_133_img_0_0.jpeg | score=0.828 | stage=0.000 | 
+4. page_145_img_0_0.jpeg | score=0.819 | stage=0.000 | 
+5. page_141_img_1_0.jpeg | score=0.810 | stage=0.000 | 
+6. page_142_img_1_0.jpeg | score=0.801 | stage=0.000 | 
+7. page_139_img_0_0.jpeg | score=0.794 | stage=0.000 | 
+8. page_140_img_0_0.jpeg | score=0.788 | stage=0.000 | 
+9. page_142_img_0_0.jpeg | score=0.775 | stage=0.000 | 
+10. page_136_img_0_0.png | score=0.767 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -3336,7 +3324,7 @@
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t>0.0529</t>
+          <t>0.0528</t>
         </is>
       </c>
       <c r="I37" s="0" t="inlineStr">
@@ -3366,7 +3354,7 @@
       </c>
       <c r="N37" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O37" s="0" t="inlineStr">
@@ -3376,16 +3364,16 @@
       </c>
       <c r="P37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_238_img_0_0.jpeg | score=1.553 | stage=0.792 | page=1.00; keyword=space limit,zone; section=safety settings,space limit
-2. page_237_img_0_0.jpeg | score=1.506 | stage=0.792 | page=1.00; keyword=space limit,zone; section=safety settings,space limit
-3. page_239_img_0_0.jpeg | score=1.481 | stage=0.792 | page=1.00; keyword=space limit,zone; section=safety settings,space limit
-4. page_232_img_0_0.jpeg | score=1.427 | stage=0.817 | page=1.00; keyword=point 1,point 2,3 point,point; section=safety settings,point
-5. page_240_img_0_0.jpeg | score=1.388 | stage=0.633 | page=1.00; section=safety settings
-6. page_238_img_1_0.jpeg | score=1.329 | stage=0.792 | page=1.00; keyword=space limit,zone; section=safety settings,space limit
-7. page_233_img_1_0.jpeg | score=1.323 | stage=0.804 | page=1.00; keyword=point 1,point 2,point; section=safety settings,point
-8. page_235_img_1_0.jpeg | score=1.277 | stage=0.792 | page=1.00; keyword=point 1,point; section=safety settings,point
-9. page_235_img_0_0.jpeg | score=1.270 | stage=0.792 | page=1.00; keyword=point 1,point; section=safety settings,point
-10. page_236_img_0_0.jpeg | score=1.235 | stage=0.633 | page=1.00; section=safety settings</t>
+          <t xml:space="preserve">1. page_237_img_0_0.jpeg | score=1.386 | stage=0.633 | page=1.00; section=safety settings
+2. page_232_img_0_0.jpeg | score=1.318 | stage=0.804 | page=1.00; keyword=point 1,point 2,point; section=safety settings,point
+3. page_236_img_0_0.jpeg | score=1.294 | stage=0.633 | page=1.00; section=safety settings
+4. page_240_img_0_0.jpeg | score=1.289 | stage=0.633 | page=1.00; section=safety settings
+5. page_243_img_0_0.jpeg | score=1.277 | stage=0.633 | page=1.00; section=safety settings
+6. page_244_img_0_0.jpeg | score=1.272 | stage=0.633 | page=1.00; section=safety settings
+7. page_241_img_0_0.jpeg | score=1.250 | stage=0.633 | page=1.00; section=safety settings
+8. page_242_img_0_0.jpeg | score=1.232 | stage=0.633 | page=1.00; section=safety settings
+9. page_238_img_1_0.jpeg | score=1.222 | stage=0.658 | page=1.00; keyword=zone,safety zone; section=safety settings
+10. page_231_img_0_0.jpeg | score=1.111 | stage=0.792 | page=1.00; keyword=point 1,point; section=safety settings,point</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3415,7 @@
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t>0.1409</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
@@ -3457,26 +3445,26 @@
       </c>
       <c r="N38" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O38" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
       <c r="P38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_310_img_1_0.jpeg | score=1.401 | stage=0.658 | page=1.00; keyword=custom code,drl; section=custom code
-2. page_305_img_0_0.jpeg | score=1.258 | stage=0.500 | page=1.00
-3. page_304_img_0_0.jpeg | score=1.131 | stage=0.658 | page=1.00; keyword=force control,compliance; section=force control
-4. page_303_img_0_0.jpeg | score=1.127 | stage=0.512 | page=1.00; keyword=compliance
-5. page_306_img_0_0.jpeg | score=1.126 | stage=0.500 | page=1.00
-6. page_311_img_0_0.jpeg | score=1.124 | stage=0.512 | page=1.00; keyword=set_external_force_reset
-7. page_309_img_0_0.jpeg | score=1.122 | stage=0.646 | page=1.00; keyword=custom code; section=custom code
-8. page_309_img_1_0.jpeg | score=1.113 | stage=0.646 | page=1.00; keyword=custom code; section=custom code
-9. page_307_img_1_0.jpeg | score=1.047 | stage=0.500 | page=1.00
-10. page_302_img_1_0.jpeg | score=0.924 | stage=0.512 | page=1.00; keyword=compliance</t>
+          <t xml:space="preserve">1. page_309_img_1_0.jpeg | score=1.343 | stage=0.500 | page=1.00
+2. page_308_img_1_0.jpeg | score=1.338 | stage=0.500 | page=1.00
+3. page_299_img_0_0.jpeg | score=1.175 | stage=0.500 | page=1.00
+4. page_311_img_0_0.jpeg | score=1.157 | stage=0.500 | page=1.00
+5. page_309_img_0_0.jpeg | score=1.150 | stage=0.500 | page=1.00
+6. page_310_img_1_0.jpeg | score=1.144 | stage=0.500 | page=1.00
+7. page_296_img_0_0.jpeg | score=1.067 | stage=0.500 | page=1.00
+8. page_307_img_1_0.jpeg | score=1.061 | stage=0.500 | page=1.00
+9. page_307_img_0_0.jpeg | score=1.054 | stage=0.500 | page=1.00
+10. page_292_img_0_0.jpeg | score=1.033 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3536,7 @@
       </c>
       <c r="N39" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O39" s="0" t="inlineStr">
@@ -3558,16 +3546,16 @@
       </c>
       <c r="P39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_154_img_1_0.jpeg | score=1.488 | stage=0.762 | page=1.00; keyword=profinet,slot,ethernet,ip; section=profinet
-2. page_155_img_1_0.jpeg | score=1.364 | stage=0.537 | page=1.00; keyword=slot,slot#1,gpr
-3. page_101_img_0_0.jpeg | score=0.788 | stage=0.000
-4. page_102_img_0_0.jpeg | score=0.653 | stage=0.013 | keyword=ip
-5. page_357_img_0_0.jpeg | score=0.614 | stage=0.000
-6. page_100_img_0_0.jpeg | score=0.538 | stage=0.000
-7. page_220_img_0_0.jpeg | score=0.533 | stage=0.000
-8. page_387_img_0_0.jpeg | score=0.529 | stage=0.000
-9. page_388_img_2_0.jpeg | score=0.487 | stage=0.000
-10. page_292_img_0_0.jpeg | score=0.397 | stage=0.000</t>
+          <t xml:space="preserve">1. page_155_img_1_0.jpeg | score=1.381 | stage=0.537 | page=1.00; keyword=ethernet,ip,adapter
+2. page_154_img_1_0.jpeg | score=1.375 | stage=0.537 | page=1.00; keyword=ethernet,ip,adapter
+3. page_357_img_0_0.jpeg | score=0.698 | stage=0.000 | 
+4. page_168_img_0_0.jpeg | score=0.687 | stage=0.000 | 
+5. page_291_img_0_0.jpeg | score=0.639 | stage=0.000 | 
+6. page_298_img_2_0.jpeg | score=0.627 | stage=0.000 | 
+7. page_298_img_0_0.jpeg | score=0.625 | stage=0.000 | 
+8. page_292_img_0_0.jpeg | score=0.620 | stage=0.000 | 
+9. page_299_img_0_0.jpeg | score=0.588 | stage=0.000 | 
+10. page_167_img_3_0.jpeg | score=0.542 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -3649,16 +3637,16 @@
       </c>
       <c r="P40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_83_img_0_0.jpeg | score=1.387 | stage=0.500 | page=1.00
-2. page_104_img_0_0.jpeg | score=1.196 | stage=0.500 | page=1.00
-3. page_84_img_0_0.jpeg | score=1.134 | stage=0.500 | page=1.00
-4. page_105_img_0_0.jpeg | score=1.118 | stage=0.500 | page=1.00
-5. page_103_img_0_0.jpeg | score=1.037 | stage=0.500 | page=1.00
-6. page_98_img_0_0.jpeg | score=1.010 | stage=0.500 | page=1.00
-7. page_98_img_1_0.jpeg | score=1.003 | stage=0.500 | page=1.00
-8. page_105_img_1_0.jpeg | score=0.954 | stage=0.500 | page=1.00
-9. page_101_img_0_0.jpeg | score=0.856 | stage=0.500 | page=1.00
-10. page_98_img_2_0.jpeg | score=0.844 | stage=0.500 | page=1.00</t>
+          <t xml:space="preserve">1. page_83_img_0_0.jpeg | score=1.381 | stage=0.500 | page=1.00
+2. page_84_img_0_0.jpeg | score=1.318 | stage=0.500 | page=1.00
+3. page_104_img_0_0.jpeg | score=1.083 | stage=0.500 | page=1.00
+4. page_85_img_0_0.jpeg | score=1.025 | stage=0.500 | page=1.00
+5. page_105_img_0_0.jpeg | score=1.009 | stage=0.500 | page=1.00
+6. page_103_img_0_0.jpeg | score=0.927 | stage=0.500 | page=1.00
+7. page_96_img_0_0.jpeg | score=0.852 | stage=0.500 | page=1.00
+8. page_98_img_0_0.jpeg | score=0.840 | stage=0.500 | page=1.00
+9. page_98_img_1_0.jpeg | score=0.833 | stage=0.500 | page=1.00
+10. page_105_img_1_0.jpeg | score=0.829 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -3730,26 +3718,26 @@
       </c>
       <c r="N41" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O41" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
       <c r="P41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_83_img_0_0.jpeg | score=1.396 | stage=0.500 | page=1.00
-2. page_119_img_0_0.jpeg | score=1.329 | stage=0.500 | page=1.00
-3. page_119_img_1_0.jpeg | score=1.312 | stage=0.500 | page=1.00
-4. page_84_img_0_0.jpeg | score=1.265 | stage=0.500 | page=1.00
-5. page_118_img_0_0.jpeg | score=1.242 | stage=0.500 | page=1.00
-6. page_120_img_0_0.jpeg | score=1.231 | stage=0.500 | page=1.00
-7. page_116_img_0_0.jpeg | score=1.051 | stage=0.225 | page=0.45
-8. page_88_img_1_0.jpeg | score=1.034 | stage=0.225 | page=0.45
-9. page_86_img_0_0.jpeg | score=0.889 | stage=0.500 | page=1.00
-10. page_401_img_1_0.jpeg | score=0.881 | stage=0.000</t>
+          <t xml:space="preserve">1. page_83_img_0_0.jpeg | score=1.395 | stage=0.500 | page=1.00
+2. page_119_img_1_0.jpeg | score=1.327 | stage=0.500 | page=1.00
+3. page_120_img_0_0.jpeg | score=1.319 | stage=0.500 | page=1.00
+4. page_121_img_0_0.jpeg | score=1.308 | stage=0.500 | page=1.00
+5. page_116_img_0_0.jpeg | score=1.297 | stage=0.500 | page=1.00
+6. page_84_img_0_0.jpeg | score=1.270 | stage=0.500 | page=1.00
+7. page_123_img_0_0.jpeg | score=1.260 | stage=0.500 | page=1.00
+8. page_119_img_0_0.jpeg | score=1.111 | stage=0.500 | page=1.00
+9. page_118_img_0_0.jpeg | score=1.092 | stage=0.500 | page=1.00
+10. page_125_img_0_0.jpeg | score=1.088 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3790,7 @@
       </c>
       <c r="K42" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L42" s="0" t="inlineStr">
@@ -3817,7 +3805,7 @@
       </c>
       <c r="N42" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O42" s="0" t="inlineStr">
@@ -3827,16 +3815,16 @@
       </c>
       <c r="P42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_121_img_0_0.jpeg | score=0.885 | stage=0.000
-2. page_403_img_0_0.jpeg | score=0.868 | stage=0.000
-3. page_120_img_0_0.jpeg | score=0.830 | stage=0.000
-4. page_86_img_0_0.jpeg | score=0.809 | stage=0.000
-5. page_400_img_0_0.jpeg | score=0.745 | stage=0.000
-6. page_399_img_0_0.jpeg | score=0.743 | stage=0.000
-7. page_119_img_0_0.jpeg | score=0.741 | stage=0.000
-8. page_119_img_1_0.jpeg | score=0.733 | stage=0.000
-9. page_163_img_0_0.jpeg | score=0.697 | stage=0.000
-10. page_118_img_0_0.jpeg | score=0.676 | stage=0.000</t>
+          <t xml:space="preserve">1. page_120_img_0_0.jpeg | score=0.879 | stage=0.000 | 
+2. page_86_img_0_0.jpeg | score=0.851 | stage=0.000 | 
+3. page_121_img_0_0.jpeg | score=0.841 | stage=0.000 | 
+4. page_119_img_1_0.jpeg | score=0.781 | stage=0.000 | 
+5. page_163_img_0_0.jpeg | score=0.714 | stage=0.000 | 
+6. page_133_img_0_0.jpeg | score=0.689 | stage=0.000 | 
+7. page_403_img_0_0.jpeg | score=0.681 | stage=0.000 | 
+8. page_398_img_0_0.jpeg | score=0.666 | stage=0.000 | 
+9. page_397_img_0_0.jpeg | score=0.664 | stage=0.000 | 
+10. page_88_img_1_0.jpeg | score=0.644 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -3908,7 +3896,7 @@
       </c>
       <c r="N43" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O43" s="0" t="inlineStr">
@@ -3918,16 +3906,16 @@
       </c>
       <c r="P43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_88_img_0_0.jpeg | score=1.290 | stage=0.500 | page=1.00
-2. page_88_img_1_0.jpeg | score=1.286 | stage=0.500 | page=1.00
-3. page_86_img_0_0.jpeg | score=1.212 | stage=0.500 | page=1.00
-4. page_400_img_0_0.jpeg | score=0.849 | stage=0.000
-5. page_121_img_0_0.jpeg | score=0.802 | stage=0.000
-6. page_399_img_0_0.jpeg | score=0.800 | stage=0.000
-7. page_85_img_0_0.jpeg | score=0.782 | stage=0.350 | page=0.70
-8. page_240_img_0_0.jpeg | score=0.771 | stage=0.000
-9. page_401_img_1_0.jpeg | score=0.761 | stage=0.000
-10. page_118_img_0_0.jpeg | score=0.746 | stage=0.000</t>
+          <t xml:space="preserve">1. page_88_img_1_0.jpeg | score=1.382 | stage=0.500 | page=1.00
+2. page_88_img_0_0.jpeg | score=1.378 | stage=0.500 | page=1.00
+3. page_86_img_0_0.jpeg | score=1.226 | stage=0.500 | page=1.00
+4. page_89_img_1_0.jpeg | score=1.115 | stage=0.500 | page=1.00
+5. page_89_img_0_0.jpeg | score=1.021 | stage=0.500 | page=1.00
+6. page_85_img_0_0.jpeg | score=0.930 | stage=0.500 | page=1.00
+7. page_93_img_0_0.jpeg | score=0.833 | stage=0.350 | page=0.70
+8. page_120_img_0_0.jpeg | score=0.818 | stage=0.000 | 
+9. page_116_img_0_0.jpeg | score=0.787 | stage=0.000 | 
+10. page_119_img_1_0.jpeg | score=0.784 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -4005,16 +3993,16 @@
       </c>
       <c r="P44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_89_img_1_0.jpeg | score=0.911 | stage=0.000
-2. page_89_img_0_0.jpeg | score=0.890 | stage=0.000
-3. page_24_img_0_0.jpeg | score=0.823 | stage=0.000
-4. page_220_img_0_0.jpeg | score=0.823 | stage=0.000
-5. page_103_img_0_0.jpeg | score=0.760 | stage=0.000
-6. page_293_img_1_0.jpeg | score=0.677 | stage=0.000
-7. page_88_img_1_0.jpeg | score=0.642 | stage=0.000
-8. page_352_img_3_0.jpeg | score=0.600 | stage=0.000
-9. page_88_img_0_0.jpeg | score=0.598 | stage=0.000
-10. page_104_img_0_0.jpeg | score=0.563 | stage=0.000</t>
+          <t xml:space="preserve">1. page_89_img_1_0.jpeg | score=0.910 | stage=0.000 | 
+2. page_89_img_0_0.jpeg | score=0.885 | stage=0.000 | 
+3. page_24_img_0_0.jpeg | score=0.766 | stage=0.000 | 
+4. page_88_img_1_0.jpeg | score=0.647 | stage=0.000 | 
+5. page_88_img_0_0.jpeg | score=0.645 | stage=0.000 | 
+6. page_296_img_0_0.jpeg | score=0.626 | stage=0.000 | 
+7. page_227_img_0_0.jpeg | score=0.590 | stage=0.000 | 
+8. page_220_img_0_0.jpeg | score=0.590 | stage=0.000 | 
+9. page_245_img_0_0.jpeg | score=0.583 | stage=0.000 | 
+10. page_243_img_0_0.jpeg | score=0.581 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -4096,16 +4084,16 @@
       </c>
       <c r="P45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_94_img_0_0.jpeg | score=1.388 | stage=0.500 | page=1.00
-2. page_95_img_0_0.jpeg | score=1.326 | stage=0.500 | page=1.00
-3. page_96_img_0_0.jpeg | score=1.210 | stage=0.500 | page=1.00
-4. page_93_img_0_0.jpeg | score=1.071 | stage=0.500 | page=1.00
-5. page_163_img_0_0.jpeg | score=0.855 | stage=0.000
-6. page_89_img_1_0.jpeg | score=0.844 | stage=0.000
-7. page_163_img_1_0.jpeg | score=0.825 | stage=0.000
-8. page_89_img_0_0.jpeg | score=0.821 | stage=0.000
-9. page_125_img_0_0.jpeg | score=0.777 | stage=0.000
-10. page_88_img_1_0.jpeg | score=0.729 | stage=0.000</t>
+          <t xml:space="preserve">1. page_94_img_0_0.jpeg | score=1.387 | stage=0.500 | page=1.00
+2. page_95_img_0_0.jpeg | score=1.303 | stage=0.500 | page=1.00
+3. page_96_img_0_0.jpeg | score=1.203 | stage=0.500 | page=1.00
+4. page_93_img_0_0.jpeg | score=0.930 | stage=0.500 | page=1.00
+5. page_163_img_0_0.jpeg | score=0.857 | stage=0.000 | 
+6. page_89_img_1_0.jpeg | score=0.842 | stage=0.000 | 
+7. page_163_img_1_0.jpeg | score=0.828 | stage=0.000 | 
+8. page_89_img_0_0.jpeg | score=0.817 | stage=0.000 | 
+9. page_125_img_0_0.jpeg | score=0.771 | stage=0.000 | 
+10. page_88_img_1_0.jpeg | score=0.726 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -4143,7 +4131,7 @@
       </c>
       <c r="H46" s="0" t="inlineStr">
         <is>
-          <t>0.0028</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="I46" s="0" t="inlineStr">
@@ -4183,16 +4171,16 @@
       </c>
       <c r="P46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_113_img_0_0.jpeg | score=0.832 | stage=0.000
-2. page_98_img_0_0.jpeg | score=0.809 | stage=0.000
-3. page_98_img_1_0.jpeg | score=0.805 | stage=0.000
-4. page_123_img_0_0.jpeg | score=0.789 | stage=0.000
-5. page_114_img_0_0.jpeg | score=0.758 | stage=0.000
-6. page_84_img_0_0.jpeg | score=0.723 | stage=0.000
-7. page_115_img_0_0.jpeg | score=0.657 | stage=0.000
-8. page_98_img_2_0.jpeg | score=0.634 | stage=0.000
-9. page_93_img_0_0.jpeg | score=0.613 | stage=0.000
-10. page_188_img_0_0.jpeg | score=0.583 | stage=0.000</t>
+          <t xml:space="preserve">1. page_113_img_0_0.jpeg | score=0.829 | stage=0.000 | 
+2. page_98_img_0_0.jpeg | score=0.790 | stage=0.000 | 
+3. page_98_img_1_0.jpeg | score=0.788 | stage=0.000 | 
+4. page_123_img_0_0.jpeg | score=0.786 | stage=0.000 | 
+5. page_84_img_0_0.jpeg | score=0.764 | stage=0.000 | 
+6. page_114_img_0_0.jpeg | score=0.757 | stage=0.000 | 
+7. page_93_img_0_0.jpeg | score=0.653 | stage=0.000 | 
+8. page_192_img_0_0.jpeg | score=0.633 | stage=0.000 | 
+9. page_115_img_0_0.jpeg | score=0.630 | stage=0.000 | 
+10. page_124_img_0_0.jpeg | score=0.627 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -4249,7 +4237,7 @@
       </c>
       <c r="K47" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L47" s="0" t="inlineStr">
@@ -4264,7 +4252,7 @@
       </c>
       <c r="N47" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O47" s="0" t="inlineStr">
@@ -4274,16 +4262,16 @@
       </c>
       <c r="P47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_120_img_0_0.jpeg | score=1.348 | stage=0.500 | page=1.00
-2. page_119_img_1_0.jpeg | score=1.299 | stage=0.500 | page=1.00
-3. page_119_img_0_0.jpeg | score=1.295 | stage=0.500 | page=1.00
-4. page_118_img_0_0.jpeg | score=1.281 | stage=0.500 | page=1.00
-5. page_116_img_0_0.jpeg | score=1.241 | stage=0.500 | page=1.00
-6. page_115_img_0_0.jpeg | score=1.151 | stage=0.500 | page=1.00
-7. page_121_img_0_0.jpeg | score=1.093 | stage=0.350 | page=0.70
-8. page_402_img_0_0.jpeg | score=0.868 | stage=0.000
-9. page_400_img_0_0.jpeg | score=0.840 | stage=0.000
-10. page_403_img_0_0.jpeg | score=0.780 | stage=0.000</t>
+          <t xml:space="preserve">1. page_120_img_0_0.jpeg | score=1.377 | stage=0.500 | page=1.00
+2. page_121_img_0_0.jpeg | score=1.338 | stage=0.500 | page=1.00
+3. page_119_img_1_0.jpeg | score=1.318 | stage=0.500 | page=1.00
+4. page_116_img_0_0.jpeg | score=1.284 | stage=0.500 | page=1.00
+5. page_123_img_0_0.jpeg | score=1.186 | stage=0.500 | page=1.00
+6. page_115_img_0_0.jpeg | score=1.181 | stage=0.500 | page=1.00
+7. page_119_img_0_0.jpeg | score=1.124 | stage=0.500 | page=1.00
+8. page_118_img_0_0.jpeg | score=1.103 | stage=0.500 | page=1.00
+9. page_124_img_0_0.jpeg | score=0.981 | stage=0.500 | page=1.00
+10. page_114_img_0_0.jpeg | score=0.902 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4343,7 @@
       </c>
       <c r="N48" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O48" s="0" t="inlineStr">
@@ -4365,16 +4353,16 @@
       </c>
       <c r="P48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_118_img_0_0.jpeg | score=1.398 | stage=0.500 | page=1.00
-2. page_119_img_1_0.jpeg | score=1.362 | stage=0.500 | page=1.00
-3. page_119_img_0_0.jpeg | score=1.343 | stage=0.500 | page=1.00
-4. page_120_img_0_0.jpeg | score=1.232 | stage=0.500 | page=1.00
-5. page_121_img_0_0.jpeg | score=1.083 | stage=0.500 | page=1.00
-6. page_400_img_0_0.jpeg | score=0.887 | stage=0.000
-7. page_116_img_0_0.jpeg | score=0.869 | stage=0.225 | page=0.45
-8. page_402_img_0_0.jpeg | score=0.805 | stage=0.000
-9. page_401_img_1_0.jpeg | score=0.799 | stage=0.000
-10. page_403_img_0_0.jpeg | score=0.773 | stage=0.000</t>
+          <t xml:space="preserve">1. page_120_img_0_0.jpeg | score=1.397 | stage=0.500 | page=1.00
+2. page_121_img_0_0.jpeg | score=1.394 | stage=0.500 | page=1.00
+3. page_119_img_1_0.jpeg | score=1.376 | stage=0.500 | page=1.00
+4. page_116_img_0_0.jpeg | score=1.214 | stage=0.500 | page=1.00
+5. page_123_img_0_0.jpeg | score=1.190 | stage=0.500 | page=1.00
+6. page_118_img_0_0.jpeg | score=1.176 | stage=0.500 | page=1.00
+7. page_119_img_0_0.jpeg | score=1.167 | stage=0.500 | page=1.00
+8. page_115_img_0_0.jpeg | score=1.027 | stage=0.500 | page=1.00
+9. page_124_img_0_0.jpeg | score=1.000 | stage=0.500 | page=1.00
+10. page_125_img_0_0.jpeg | score=0.818 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4434,7 @@
       </c>
       <c r="N49" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O49" s="0" t="inlineStr">
@@ -4456,16 +4444,16 @@
       </c>
       <c r="P49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_123_img_0_0.jpeg | score=1.412 | stage=0.525 | page=1.00; keyword=m6,9 nm
-2. page_93_img_0_0.jpeg | score=1.382 | stage=0.525 | page=1.00; keyword=m6,9 nm
-3. page_94_img_0_0.jpeg | score=1.293 | stage=0.500 | page=1.00
-4. page_95_img_0_0.jpeg | score=1.193 | stage=0.500 | page=1.00
-5. page_124_img_0_0.jpeg | score=1.108 | stage=0.525 | page=1.00; keyword=m6,9 nm
-6. page_121_img_0_0.jpeg | score=1.063 | stage=0.350 | page=0.70
-7. page_92_img_1_0.jpeg | score=0.894 | stage=0.500 | page=1.00
-8. page_84_img_0_0.jpeg | score=0.827 | stage=0.000
-9. page_96_img_0_0.jpeg | score=0.814 | stage=0.350 | page=0.70
-10. page_205_img_1_0.jpeg | score=0.775 | stage=0.013 | keyword=tool</t>
+          <t xml:space="preserve">1. page_93_img_0_0.jpeg | score=1.385 | stage=0.525 | page=1.00; keyword=m6,9 nm
+2. page_123_img_0_0.jpeg | score=1.380 | stage=0.500 | page=1.00
+3. page_94_img_0_0.jpeg | score=1.291 | stage=0.500 | page=1.00
+4. page_121_img_0_0.jpeg | score=1.217 | stage=0.500 | page=1.00
+5. page_124_img_0_0.jpeg | score=1.198 | stage=0.525 | page=1.00; keyword=m6,9 nm
+6. page_95_img_0_0.jpeg | score=1.196 | stage=0.500 | page=1.00
+7. page_125_img_0_0.jpeg | score=1.171 | stage=0.500 | page=1.00
+8. page_96_img_0_0.jpeg | score=1.160 | stage=0.500 | page=1.00
+9. page_119_img_1_0.jpeg | score=0.976 | stage=0.500 | page=1.00
+10. page_119_img_0_0.jpeg | score=0.925 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -4543,16 +4531,16 @@
       </c>
       <c r="P50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_125_img_0_0.jpeg | score=0.892 | stage=0.000
-2. page_88_img_1_0.jpeg | score=0.871 | stage=0.000
-3. page_121_img_0_0.jpeg | score=0.810 | stage=0.000
-4. page_163_img_0_0.jpeg | score=0.782 | stage=0.000
-5. page_89_img_1_0.jpeg | score=0.765 | stage=0.000
-6. page_144_img_0_0.jpeg | score=0.757 | stage=0.000
-7. page_144_img_1_0.jpeg | score=0.754 | stage=0.000
-8. page_163_img_1_0.jpeg | score=0.753 | stage=0.000
-9. page_86_img_0_0.jpeg | score=0.729 | stage=0.000
-10. page_120_img_0_0.jpeg | score=0.717 | stage=0.000</t>
+          <t xml:space="preserve">1. page_125_img_0_0.jpeg | score=0.888 | stage=0.000 | 
+2. page_88_img_1_0.jpeg | score=0.867 | stage=0.000 | 
+3. page_89_img_1_0.jpeg | score=0.856 | stage=0.000 | 
+4. page_121_img_0_0.jpeg | score=0.800 | stage=0.000 | 
+5. page_163_img_0_0.jpeg | score=0.782 | stage=0.000 | 
+6. page_163_img_1_0.jpeg | score=0.753 | stage=0.000 | 
+7. page_398_img_0_0.jpeg | score=0.750 | stage=0.000 | 
+8. page_397_img_0_0.jpeg | score=0.748 | stage=0.000 | 
+9. page_144_img_0_0.jpeg | score=0.737 | stage=0.000 | 
+10. page_144_img_1_0.jpeg | score=0.733 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -4634,16 +4622,16 @@
       </c>
       <c r="P51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_130_img_0_0.jpeg | score=1.408 | stage=0.550 | page=1.00; keyword=pnp,photo coupler,+24v,open
-2. page_132_img_0_0.png | score=1.264 | stage=0.500 | page=1.00
-3. page_336_img_0_0.jpeg | score=0.845 | stage=0.000
-4. page_335_img_1_0.jpeg | score=0.800 | stage=0.000
-5. page_335_img_2_0.jpeg | score=0.724 | stage=0.000
-6. page_133_img_0_0.jpeg | score=0.697 | stage=0.500 | page=1.00
-7. page_140_img_0_0.jpeg | score=0.685 | stage=0.000
-8. page_334_img_0_0.jpeg | score=0.644 | stage=0.000
-9. page_135_img_0_0.jpeg | score=0.642 | stage=0.225 | page=0.45
-10. page_335_img_0_0.jpeg | score=0.635 | stage=0.000</t>
+          <t xml:space="preserve">1. page_130_img_0_0.jpeg | score=1.413 | stage=0.537 | page=1.00; keyword=pnp,photo coupler,+24v
+2. page_132_img_0_0.png | score=1.287 | stage=0.500 | page=1.00
+3. page_133_img_0_0.jpeg | score=0.990 | stage=0.500 | page=1.00
+4. page_336_img_0_0.jpeg | score=0.717 | stage=0.000 | 
+5. page_136_img_0_0.png | score=0.712 | stage=0.225 | page=0.45
+6. page_347_img_0_0.jpeg | score=0.675 | stage=0.000 | 
+7. page_137_img_0_0.jpeg | score=0.661 | stage=0.225 | page=0.45
+8. page_346_img_0_0.jpeg | score=0.655 | stage=0.000 | 
+9. page_334_img_0_0.jpeg | score=0.653 | stage=0.000 | 
+10. page_335_img_2_0.jpeg | score=0.648 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -4725,16 +4713,16 @@
       </c>
       <c r="P52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_132_img_0_0.png | score=1.332 | stage=0.500 | page=1.00
-2. page_135_img_0_0.jpeg | score=1.242 | stage=0.500 | page=1.00
-3. page_130_img_0_0.jpeg | score=1.219 | stage=0.500 | page=1.00
-4. page_133_img_0_0.jpeg | score=1.054 | stage=0.500 | page=1.00
-5. page_336_img_0_0.jpeg | score=0.871 | stage=0.000
-6. page_338_img_0_0.jpeg | score=0.768 | stage=0.000
-7. page_333_img_0_0.jpeg | score=0.709 | stage=0.000
-8. page_136_img_1_0.jpeg | score=0.704 | stage=0.350 | page=0.70
-9. page_335_img_1_0.jpeg | score=0.697 | stage=0.000
-10. page_136_img_0_0.png | score=0.681 | stage=0.350 | page=0.70</t>
+          <t xml:space="preserve">1. page_132_img_0_0.png | score=1.336 | stage=0.500 | page=1.00
+2. page_136_img_0_0.png | score=1.332 | stage=0.500 | page=1.00
+3. page_137_img_0_0.jpeg | score=1.324 | stage=0.500 | page=1.00
+4. page_130_img_0_0.jpeg | score=1.239 | stage=0.500 | page=1.00
+5. page_135_img_0_0.jpeg | score=1.150 | stage=0.500 | page=1.00
+6. page_136_img_1_0.jpeg | score=1.113 | stage=0.500 | page=1.00
+7. page_133_img_0_0.jpeg | score=1.103 | stage=0.500 | page=1.00
+8. page_138_img_0_0.jpeg | score=1.097 | stage=0.500 | page=1.00
+9. page_138_img_1_0.jpeg | score=1.083 | stage=0.500 | page=1.00
+10. page_128_img_0_0.jpeg | score=0.887 | stage=0.350 | page=0.70</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4760,7 @@
       </c>
       <c r="H53" s="0" t="inlineStr">
         <is>
-          <t>0.0093</t>
+          <t>0.0092</t>
         </is>
       </c>
       <c r="I53" s="0" t="inlineStr">
@@ -4812,16 +4800,16 @@
       </c>
       <c r="P53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_133_img_0_0.jpeg | score=0.874 | stage=0.000
-2. page_145_img_0_0.jpeg | score=0.865 | stage=0.000
-3. page_143_img_1_0.jpeg | score=0.797 | stage=0.000
-4. page_143_img_0_0.jpeg | score=0.795 | stage=0.000
-5. page_102_img_0_0.jpeg | score=0.794 | stage=0.000
-6. page_144_img_0_0.jpeg | score=0.742 | stage=0.000
-7. page_144_img_1_0.jpeg | score=0.738 | stage=0.000
-8. page_397_img_0_0.jpeg | score=0.728 | stage=0.000
-9. page_139_img_0_0.jpeg | score=0.727 | stage=0.000
-10. page_216_img_0_0.jpeg | score=0.702 | stage=0.000</t>
+          <t xml:space="preserve">1. page_133_img_0_0.jpeg | score=0.867 | stage=0.000 | 
+2. page_145_img_0_0.jpeg | score=0.863 | stage=0.000 | 
+3. page_147_img_0_0.jpeg | score=0.850 | stage=0.000 | 
+4. page_139_img_0_0.jpeg | score=0.808 | stage=0.000 | 
+5. page_140_img_0_0.jpeg | score=0.802 | stage=0.000 | 
+6. page_144_img_0_0.jpeg | score=0.801 | stage=0.000 | 
+7. page_144_img_1_0.jpeg | score=0.797 | stage=0.000 | 
+8. page_142_img_0_0.jpeg | score=0.793 | stage=0.000 | 
+9. page_142_img_1_0.jpeg | score=0.793 | stage=0.000 | 
+10. page_242_img_0_0.jpeg | score=0.764 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -4903,16 +4891,16 @@
       </c>
       <c r="P54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_137_img_0_0.jpeg | score=1.491 | stage=0.712 | page=1.00; keyword=tben; section=tben
-2. page_138_img_0_0.jpeg | score=1.384 | stage=0.712 | page=1.00; keyword=tben; section=tben
-3. page_136_img_0_0.png | score=1.364 | stage=0.500 | page=1.00
-4. page_138_img_1_0.jpeg | score=1.329 | stage=0.712 | page=1.00; keyword=tben; section=tben
-5. page_136_img_1_0.jpeg | score=1.317 | stage=0.500 | page=1.00
-6. page_135_img_0_0.jpeg | score=1.299 | stage=0.500 | page=1.00
-7. page_140_img_0_0.jpeg | score=1.161 | stage=0.500 | page=1.00
-8. page_139_img_0_0.jpeg | score=1.007 | stage=0.500 | page=1.00
-9. page_133_img_0_0.jpeg | score=0.985 | stage=0.225 | page=0.45
-10. page_141_img_1_0.jpeg | score=0.963 | stage=0.350 | page=0.70</t>
+          <t xml:space="preserve">1. page_137_img_0_0.jpeg | score=1.382 | stage=0.500 | page=1.00
+2. page_136_img_0_0.png | score=1.336 | stage=0.500 | page=1.00
+3. page_145_img_0_0.jpeg | score=1.302 | stage=0.500 | page=1.00
+4. page_138_img_0_0.jpeg | score=1.260 | stage=0.500 | page=1.00
+5. page_138_img_1_0.jpeg | score=1.216 | stage=0.500 | page=1.00
+6. page_139_img_0_0.jpeg | score=1.186 | stage=0.500 | page=1.00
+7. page_142_img_1_0.jpeg | score=1.179 | stage=0.500 | page=1.00
+8. page_140_img_0_0.jpeg | score=1.175 | stage=0.500 | page=1.00
+9. page_142_img_0_0.jpeg | score=1.169 | stage=0.500 | page=1.00
+10. page_141_img_1_0.jpeg | score=1.160 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -4994,16 +4982,16 @@
       </c>
       <c r="P55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_139_img_0_0.jpeg | score=1.524 | stage=0.725 | page=1.00; keyword=o,16; section=o
-2. page_140_img_0_0.jpeg | score=1.491 | stage=0.725 | page=1.00; keyword=o,16; section=o
-3. page_144_img_0_0.jpeg | score=1.452 | stage=0.725 | page=1.00; keyword=o,controller; section=o
-4. page_144_img_1_0.jpeg | score=1.445 | stage=0.725 | page=1.00; keyword=o,controller; section=o
-5. page_141_img_1_0.jpeg | score=1.373 | stage=0.712 | page=1.00; keyword=o; section=o
-6. page_145_img_0_0.jpeg | score=1.286 | stage=0.725 | page=1.00; keyword=o,controller; section=o
-7. page_138_img_0_0.jpeg | score=1.264 | stage=0.712 | page=1.00; keyword=o; section=o
-8. page_143_img_1_0.jpeg | score=1.262 | stage=0.725 | page=1.00; keyword=o,16; section=o
-9. page_143_img_0_0.jpeg | score=1.257 | stage=0.725 | page=1.00; keyword=o,16; section=o
-10. page_138_img_1_0.jpeg | score=1.135 | stage=0.712 | page=1.00; keyword=o; section=o</t>
+          <t xml:space="preserve">1. page_139_img_0_0.jpeg | score=1.515 | stage=0.725 | page=1.00; keyword=o,16; section=o
+2. page_144_img_0_0.jpeg | score=1.506 | stage=0.725 | page=1.00; keyword=o,controller; section=o
+3. page_140_img_0_0.jpeg | score=1.502 | stage=0.725 | page=1.00; keyword=o,16; section=o
+4. page_144_img_1_0.jpeg | score=1.497 | stage=0.725 | page=1.00; keyword=o,controller; section=o
+5. page_145_img_0_0.jpeg | score=1.452 | stage=0.712 | page=1.00; keyword=o; section=o
+6. page_142_img_1_0.jpeg | score=1.407 | stage=0.712 | page=1.00; keyword=o; section=o
+7. page_137_img_0_0.jpeg | score=1.389 | stage=0.712 | page=1.00; keyword=o; section=o
+8. page_141_img_1_0.jpeg | score=1.360 | stage=0.712 | page=1.00; keyword=o; section=o
+9. page_142_img_0_0.jpeg | score=1.339 | stage=0.712 | page=1.00; keyword=o; section=o
+10. page_138_img_0_0.jpeg | score=1.279 | stage=0.712 | page=1.00; keyword=o; section=o</t>
         </is>
       </c>
     </row>
@@ -5085,16 +5073,16 @@
       </c>
       <c r="P56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_141_img_1_0.jpeg | score=1.420 | stage=0.537 | page=1.00; keyword=tbco,oxx,gio
-2. page_142_img_1_0.jpeg | score=1.381 | stage=0.537 | page=1.00; keyword=tbco,oxx,gio
-3. page_142_img_0_0.jpeg | score=1.368 | stage=0.537 | page=1.00; keyword=tbco,oxx,gio
-4. page_143_img_1_0.jpeg | score=1.272 | stage=0.500 | page=1.00
-5. page_143_img_0_0.jpeg | score=1.268 | stage=0.500 | page=1.00
-6. page_140_img_0_0.jpeg | score=1.206 | stage=0.500 | page=1.00
-7. page_141_img_0_0.jpeg | score=1.201 | stage=0.537 | page=1.00; keyword=tbco,oxx,gio
-8. page_144_img_0_0.jpeg | score=1.139 | stage=0.512 | page=1.00; keyword=gio
-9. page_145_img_0_0.jpeg | score=1.135 | stage=0.362 | page=0.70; keyword=gio
-10. page_144_img_1_0.jpeg | score=1.133 | stage=0.512 | page=1.00; keyword=gio</t>
+          <t xml:space="preserve">1. page_141_img_1_0.jpeg | score=1.403 | stage=0.537 | page=1.00; keyword=tbco,oxx,gio
+2. page_142_img_1_0.jpeg | score=1.346 | stage=0.512 | page=1.00; keyword=tbco
+3. page_142_img_0_0.jpeg | score=1.338 | stage=0.512 | page=1.00; keyword=tbco
+4. page_145_img_0_0.jpeg | score=1.250 | stage=0.500 | page=1.00
+5. page_144_img_0_0.jpeg | score=1.180 | stage=0.512 | page=1.00; keyword=gio
+6. page_144_img_1_0.jpeg | score=1.174 | stage=0.512 | page=1.00; keyword=gio
+7. page_143_img_1_0.jpeg | score=1.136 | stage=0.512 | page=1.00; keyword=tbco
+8. page_143_img_0_0.jpeg | score=1.133 | stage=0.512 | page=1.00; keyword=tbco
+9. page_137_img_0_0.jpeg | score=1.046 | stage=0.350 | page=0.70
+10. page_141_img_0_0.jpeg | score=0.991 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5154,7 @@
       </c>
       <c r="N57" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O57" s="0" t="inlineStr">
@@ -5176,16 +5164,16 @@
       </c>
       <c r="P57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_142_img_1_0.jpeg | score=1.563 | stage=0.829 | page=1.00; keyword=sink type,negative common,oxx,gio; section=o,sink type
-2. page_142_img_0_0.jpeg | score=1.554 | stage=0.829 | page=1.00; keyword=sink type,negative common,oxx,gio; section=o,sink type
-3. page_143_img_1_0.jpeg | score=1.429 | stage=0.792 | page=1.00; keyword=sink type,negative common; section=o,sink type
-4. page_143_img_0_0.jpeg | score=1.424 | stage=0.792 | page=1.00; keyword=sink type,negative common; section=o,sink type
-5. page_140_img_0_0.jpeg | score=1.399 | stage=0.633 | page=1.00; section=o
-6. page_144_img_0_0.jpeg | score=1.395 | stage=0.646 | page=1.00; keyword=gio; section=o
-7. page_144_img_1_0.jpeg | score=1.389 | stage=0.646 | page=1.00; keyword=gio; section=o
-8. page_141_img_1_0.jpeg | score=1.355 | stage=0.671 | page=1.00; keyword=oxx,gio,tbco; section=o
-9. page_139_img_0_0.jpeg | score=1.241 | stage=0.633 | page=1.00; section=o
-10. page_145_img_0_0.jpeg | score=1.235 | stage=0.646 | page=1.00; keyword=gio; section=o</t>
+          <t xml:space="preserve">1. page_142_img_0_0.jpeg | score=1.529 | stage=0.804 | page=1.00; keyword=sink type,negative common,tbco; section=o,sink type
+2. page_142_img_1_0.jpeg | score=1.524 | stage=0.804 | page=1.00; keyword=sink type,negative common,tbco; section=o,sink type
+3. page_144_img_0_0.jpeg | score=1.410 | stage=0.646 | page=1.00; keyword=gio; section=o
+4. page_144_img_1_0.jpeg | score=1.404 | stage=0.646 | page=1.00; keyword=gio; section=o
+5. page_141_img_1_0.jpeg | score=1.386 | stage=0.671 | page=1.00; keyword=oxx,gio,tbco; section=o
+6. page_145_img_0_0.jpeg | score=1.351 | stage=0.633 | page=1.00; section=o
+7. page_139_img_0_0.jpeg | score=1.314 | stage=0.633 | page=1.00; section=o
+8. page_143_img_1_0.jpeg | score=1.307 | stage=0.804 | page=1.00; keyword=sink type,negative common,tbco; section=o,sink type
+9. page_140_img_0_0.jpeg | score=1.305 | stage=0.633 | page=1.00; section=o
+10. page_143_img_0_0.jpeg | score=1.303 | stage=0.804 | page=1.00; keyword=sink type,negative common,tbco; section=o,sink type</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5215,7 @@
       </c>
       <c r="H58" s="0" t="inlineStr">
         <is>
-          <t>0.1484</t>
+          <t>0.1485</t>
         </is>
       </c>
       <c r="I58" s="0" t="inlineStr">
@@ -5268,15 +5256,15 @@
       <c r="P58" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">1. page_147_img_0_0.jpeg | score=1.511 | stage=0.696 | page=1.00; keyword=safety controller,si1,si2,si3; section=o
-2. page_145_img_0_0.jpeg | score=1.494 | stage=0.779 | page=1.00; keyword=safety controller; section=safety i,o
-3. page_143_img_1_0.jpeg | score=1.421 | stage=0.767 | page=1.00; section=safety i,o
-4. page_143_img_0_0.jpeg | score=1.416 | stage=0.767 | page=1.00; section=safety i,o
-5. page_148_img_0_0.jpeg | score=1.330 | stage=0.646 | page=1.00; keyword=safety controller; section=o
-6. page_144_img_0_0.jpeg | score=1.328 | stage=0.779 | page=1.00; keyword=safety controller; section=safety i,o
-7. page_144_img_1_0.jpeg | score=1.321 | stage=0.779 | page=1.00; keyword=safety controller; section=safety i,o
-8. page_142_img_1_0.jpeg | score=0.920 | stage=0.483 | page=0.70; section=o
-9. page_142_img_0_0.jpeg | score=0.918 | stage=0.483 | page=0.70; section=o
-10. page_133_img_0_0.jpeg | score=0.811 | stage=0.133 | section=o</t>
+2. page_145_img_0_0.jpeg | score=1.481 | stage=0.767 | page=1.00; section=safety i,o
+3. page_142_img_0_0.jpeg | score=1.333 | stage=0.633 | page=1.00; section=o
+4. page_142_img_1_0.jpeg | score=1.329 | stage=0.633 | page=1.00; section=o
+5. page_148_img_0_0.jpeg | score=1.322 | stage=0.633 | page=1.00; section=o
+6. page_144_img_0_0.jpeg | score=1.266 | stage=0.646 | page=1.00; keyword=safety controller; section=o
+7. page_144_img_1_0.jpeg | score=1.254 | stage=0.646 | page=1.00; keyword=safety controller; section=o
+8. page_139_img_0_0.jpeg | score=1.238 | stage=0.633 | page=1.00; section=o
+9. page_140_img_0_0.jpeg | score=1.210 | stage=0.633 | page=1.00; section=o
+10. page_143_img_0_0.jpeg | score=1.139 | stage=0.633 | page=1.00; section=o</t>
         </is>
       </c>
     </row>
@@ -5358,16 +5346,16 @@
       </c>
       <c r="P59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_148_img_0_0.jpeg | score=1.405 | stage=0.575 | page=1.00; keyword=wan,lan,tcp,ip
-2. page_355_img_1_0.jpeg | score=1.204 | stage=0.562 | page=1.00; keyword=ip,ethernet,profinet,network
-3. page_355_img_0_0.jpeg | score=1.197 | stage=0.562 | page=1.00; keyword=ip,ethernet,profinet,network
-4. page_354_img_0_0.jpeg | score=1.056 | stage=0.537 | page=1.00; keyword=ip,network,controller
-5. page_151_img_3_0.jpeg | score=1.005 | stage=0.512 | page=1.00; keyword=lan
-6. page_151_img_2_0.jpeg | score=1.002 | stage=0.512 | page=1.00; keyword=lan
-7. page_144_img_0_0.jpeg | score=0.984 | stage=0.238 | page=0.45; keyword=controller
-8. page_145_img_0_0.jpeg | score=0.983 | stage=0.362 | page=0.70; keyword=controller
-9. page_144_img_1_0.jpeg | score=0.979 | stage=0.238 | page=0.45; keyword=controller
-10. page_147_img_0_0.jpeg | score=0.880 | stage=0.500 | page=1.00</t>
+          <t xml:space="preserve">1. page_148_img_0_0.jpeg | score=1.392 | stage=0.550 | page=1.00; keyword=wan,tcp,ip,modbus
+2. page_355_img_1_0.jpeg | score=1.254 | stage=0.537 | page=1.00; keyword=ip,ethernet,profinet
+3. page_355_img_0_0.jpeg | score=1.234 | stage=0.525 | page=1.00; keyword=network,controller
+4. page_145_img_0_0.jpeg | score=1.171 | stage=0.500 | page=1.00
+5. page_152_img_3_0.jpeg | score=1.164 | stage=0.500 | page=1.00
+6. page_151_img_2_0.jpeg | score=1.124 | stage=0.500 | page=1.00
+7. page_354_img_0_0.jpeg | score=1.042 | stage=0.525 | page=1.00; keyword=network,controller
+8. page_154_img_1_0.jpeg | score=1.035 | stage=0.525 | page=1.00; keyword=ip,ethernet
+9. page_147_img_0_0.jpeg | score=1.016 | stage=0.512 | page=1.00; keyword=controller
+10. page_144_img_0_0.jpeg | score=0.960 | stage=0.238 | page=0.45; keyword=controller</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5427,7 @@
       </c>
       <c r="N60" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O60" s="0" t="inlineStr">
@@ -5449,16 +5437,16 @@
       </c>
       <c r="P60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_176_img_0_0.png | score=1.388 | stage=0.537 | page=1.00; keyword=x,y,z
-2. page_175_img_1_0.jpeg | score=1.325 | stage=0.537 | page=1.00; keyword=x,y,z
-3. page_175_img_3_0.jpeg | score=1.318 | stage=0.537 | page=1.00; keyword=x,y,z
-4. page_177_img_1_0.jpeg | score=1.250 | stage=0.500 | page=1.00
-5. page_176_img_1_0.png | score=1.196 | stage=0.537 | page=1.00; keyword=x,y,z
-6. page_176_img_3_0.jpeg | score=1.193 | stage=0.537 | page=1.00; keyword=x,y,z
-7. page_176_img_2_0.jpeg | score=1.190 | stage=0.537 | page=1.00; keyword=x,y,z
-8. page_175_img_4_0.jpeg | score=1.123 | stage=0.537 | page=1.00; keyword=x,y,z
-9. page_175_img_2_0.jpeg | score=1.112 | stage=0.537 | page=1.00; keyword=x,y,z
-10. page_174_img_1_0.jpeg | score=1.042 | stage=0.500 | page=1.00</t>
+          <t xml:space="preserve">1. page_177_img_1_0.jpeg | score=1.370 | stage=0.525 | page=1.00; keyword=x,y
+2. page_176_img_0_0.png | score=1.366 | stage=0.525 | page=1.00; keyword=x,y
+3. page_176_img_3_0.jpeg | score=1.355 | stage=0.537 | page=1.00; keyword=x,y,z
+4. page_175_img_2_0.jpeg | score=1.179 | stage=0.537 | page=1.00; keyword=x,y,z
+5. page_176_img_1_0.png | score=1.164 | stage=0.525 | page=1.00; keyword=x,y
+6. page_176_img_2_0.jpeg | score=1.161 | stage=0.525 | page=1.00; keyword=x,y
+7. page_175_img_1_0.jpeg | score=1.109 | stage=0.537 | page=1.00; keyword=x,y,z
+8. page_175_img_4_0.jpeg | score=1.106 | stage=0.537 | page=1.00; keyword=x,y,z
+9. page_175_img_3_0.jpeg | score=1.098 | stage=0.537 | page=1.00; keyword=x,y,z
+10. page_174_img_1_0.jpeg | score=0.928 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -5540,16 +5528,16 @@
       </c>
       <c r="P61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_181_img_0_0.jpeg | score=1.461 | stage=0.712 | page=1.00; keyword=recovery; section=recovery
-2. page_182_img_0_0.jpeg | score=1.414 | stage=0.712 | page=1.00; keyword=recovery; section=recovery
-3. page_184_img_0_0.jpeg | score=1.188 | stage=0.525 | page=1.00; keyword=joint,task
-4. page_186_img_0_0.jpeg | score=1.016 | stage=0.712 | page=1.00; keyword=recovery; section=recovery
-5. page_178_img_0_0.jpeg | score=0.908 | stage=0.450 | page=0.45; keyword=recovery,joint; section=recovery
-6. page_188_img_0_0.jpeg | score=0.750 | stage=0.225 | page=0.45
-7. page_179_img_1_0.jpeg | score=0.734 | stage=0.350 | page=0.70
-8. page_48_img_0_0.jpeg | score=0.704 | stage=0.000
-9. page_92_img_1_0.jpeg | score=0.638 | stage=0.213 | keyword=recovery; section=recovery
-10. page_177_img_1_0.jpeg | score=0.627 | stage=0.225 | page=0.45</t>
+          <t xml:space="preserve">1. page_181_img_0_0.jpeg | score=1.455 | stage=0.712 | page=1.00; keyword=recovery; section=recovery
+2. page_184_img_0_0.jpeg | score=1.285 | stage=0.500 | page=1.00
+3. page_178_img_0_0.jpeg | score=1.191 | stage=0.712 | page=1.00; keyword=recovery; section=recovery
+4. page_182_img_0_0.jpeg | score=1.151 | stage=0.500 | page=1.00
+5. page_179_img_1_0.jpeg | score=1.054 | stage=0.712 | page=1.00; keyword=recovery; section=recovery
+6. page_186_img_0_0.jpeg | score=0.938 | stage=0.500 | page=1.00
+7. page_192_img_0_0.jpeg | score=0.891 | stage=0.225 | page=0.45
+8. page_191_img_0_0.jpeg | score=0.739 | stage=0.225 | page=0.45
+9. page_196_img_0_0.jpeg | score=0.737 | stage=0.225 | page=0.45
+10. page_189_img_0_0.jpeg | score=0.736 | stage=0.225 | page=0.45</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5575,7 @@
       </c>
       <c r="H62" s="0" t="inlineStr">
         <is>
-          <t>0.0255</t>
+          <t>0.0254</t>
         </is>
       </c>
       <c r="I62" s="0" t="inlineStr">
@@ -5602,24 +5590,24 @@
       </c>
       <c r="K62" s="0" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L62" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M62" s="0" t="inlineStr">
+        <is>
+          <t>page_186_img_0_0.jpeg</t>
+        </is>
+      </c>
+      <c r="N62" s="0" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L62" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M62" s="0" t="inlineStr">
-        <is>
-          <t>page_186_img_0_0.jpeg</t>
-        </is>
-      </c>
-      <c r="N62" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="O62" s="0" t="inlineStr">
         <is>
           <t>O</t>
@@ -5627,16 +5615,16 @@
       </c>
       <c r="P62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_168_img_0_0.jpeg | score=0.867 | stage=0.000
-2. page_196_img_0_0.jpeg | score=0.841 | stage=0.000
-3. page_186_img_0_0.jpeg | score=0.824 | stage=0.000
-4. page_246_img_0_0.jpeg | score=0.791 | stage=0.000
-5. page_187_img_1_0.jpeg | score=0.745 | stage=0.000
-6. page_197_img_0_0.jpeg | score=0.744 | stage=0.000
-7. page_376_img_0_0.jpeg | score=0.742 | stage=0.000
-8. page_247_img_0_0.jpeg | score=0.709 | stage=0.000
-9. page_361_img_0_0.jpeg | score=0.702 | stage=0.000
-10. page_361_img_1_0.jpeg | score=0.702 | stage=0.000</t>
+          <t xml:space="preserve">1. page_168_img_0_0.jpeg | score=0.851 | stage=0.000 | 
+2. page_186_img_0_0.jpeg | score=0.837 | stage=0.000 | 
+3. page_361_img_1_0.jpeg | score=0.827 | stage=0.000 | 
+4. page_361_img_0_0.jpeg | score=0.827 | stage=0.000 | 
+5. page_248_img_0_0.jpeg | score=0.791 | stage=0.000 | 
+6. page_197_img_0_0.jpeg | score=0.781 | stage=0.000 | 
+7. page_376_img_0_0.jpeg | score=0.760 | stage=0.000 | 
+8. page_169_img_2_0.jpeg | score=0.704 | stage=0.000 | 
+9. page_184_img_0_0.jpeg | score=0.698 | stage=0.000 | 
+10. page_375_img_0_0.jpeg | score=0.691 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -5718,16 +5706,16 @@
       </c>
       <c r="P63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_196_img_0_0.jpeg | score=1.396 | stage=0.525 | page=1.00; keyword=1+2,setting
-2. page_197_img_0_0.jpeg | score=1.279 | stage=0.512 | page=1.00; keyword=setting
-3. page_195_img_0_0.jpeg | score=1.234 | stage=0.512 | page=1.00; keyword=setting
-4. page_195_img_2_0.jpeg | score=1.208 | stage=0.512 | page=1.00; keyword=setting
-5. page_192_img_0_0.jpeg | score=0.983 | stage=0.238 | page=0.45; keyword=setting
-6. page_101_img_0_0.jpeg | score=0.834 | stage=0.013 | keyword=cockpit
-7. page_191_img_0_0.jpeg | score=0.802 | stage=0.013 | keyword=setting
-8. page_189_img_0_0.jpeg | score=0.779 | stage=0.013 | keyword=setting
-9. page_220_img_0_0.jpeg | score=0.727 | stage=0.025 | keyword=setting,reset
-10. page_190_img_1_0.jpeg | score=0.710 | stage=0.013 | keyword=setting</t>
+          <t xml:space="preserve">1. page_196_img_0_0.jpeg | score=1.254 | stage=0.512 | page=1.00; keyword=setting
+2. page_197_img_0_0.jpeg | score=1.240 | stage=0.512 | page=1.00; keyword=setting
+3. page_192_img_0_0.jpeg | score=1.161 | stage=0.512 | page=1.00; keyword=setting
+4. page_195_img_2_0.jpeg | score=1.118 | stage=0.512 | page=1.00; keyword=setting
+5. page_190_img_1_0.jpeg | score=1.016 | stage=0.512 | page=1.00; keyword=setting
+6. page_199_img_0_0.jpeg | score=0.998 | stage=0.512 | page=1.00; keyword=setting
+7. page_190_img_0_0.jpeg | score=0.990 | stage=0.512 | page=1.00; keyword=setting
+8. page_195_img_0_0.jpeg | score=0.982 | stage=0.512 | page=1.00; keyword=setting
+9. page_189_img_0_0.jpeg | score=0.948 | stage=0.512 | page=1.00; keyword=setting
+10. page_191_img_0_0.jpeg | score=0.946 | stage=0.512 | page=1.00; keyword=setting</t>
         </is>
       </c>
     </row>
@@ -5809,16 +5797,16 @@
       </c>
       <c r="P64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_205_img_1_0.jpeg | score=1.612 | stage=0.938 | page=1.00; keyword=tool weight,weight,tool settings; section=tool settings,tool weight
-2. page_206_img_0_0.jpeg | score=1.503 | stage=0.938 | page=1.00; keyword=tool weight,weight,tool settings; section=tool settings,tool weight
-3. page_208_img_0_0.jpeg | score=1.218 | stage=0.712 | page=1.00; keyword=tool settings; section=tool settings
-4. page_204_img_0_0.jpeg | score=0.989 | stage=0.712 | page=1.00; keyword=tool settings; section=tool settings
-5. page_204_img_1_0.jpeg | score=0.982 | stage=0.712 | page=1.00; keyword=tool settings; section=tool settings
-6. page_279_img_0_0.jpeg | score=0.831 | stage=0.225 | keyword=tool weight,weight; section=tool weight
-7. page_188_img_0_0.jpeg | score=0.805 | stage=0.013 | keyword=robot parameters
-8. page_189_img_0_0.jpeg | score=0.744 | stage=0.000
-9. page_289_img_0_0.jpeg | score=0.668 | stage=0.000
-10. page_280_img_0_0.jpeg | score=0.666 | stage=0.000</t>
+          <t xml:space="preserve">1. page_205_img_1_0.jpeg | score=1.613 | stage=0.938 | page=1.00; keyword=tool weight,weight,tool settings; section=tool settings,tool weight
+2. page_206_img_0_0.jpeg | score=1.323 | stage=0.712 | page=1.00; keyword=tool settings; section=tool settings
+3. page_209_img_0_0.jpeg | score=1.319 | stage=0.712 | page=1.00; keyword=tool settings; section=tool settings
+4. page_210_img_2_0.jpeg | score=1.203 | stage=0.712 | page=1.00; keyword=tool settings; section=tool settings
+5. page_192_img_0_0.jpeg | score=1.196 | stage=0.350 | page=0.70
+6. page_208_img_0_0.jpeg | score=1.179 | stage=0.712 | page=1.00; keyword=tool settings; section=tool settings
+7. page_196_img_0_0.jpeg | score=1.047 | stage=0.350 | page=0.70
+8. page_195_img_0_0.jpeg | score=1.031 | stage=0.350 | page=0.70
+9. page_197_img_0_0.jpeg | score=1.022 | stage=0.350 | page=0.70
+10. page_191_img_0_0.jpeg | score=0.993 | stage=0.350 | page=0.70</t>
         </is>
       </c>
     </row>
@@ -5900,16 +5888,16 @@
       </c>
       <c r="P65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_209_img_0_0.jpeg | score=1.598 | stage=0.925 | page=1.00; keyword=tool shape,shape; section=tool settings,tool shape
-2. page_208_img_0_0.jpeg | score=1.555 | stage=0.938 | page=1.00; keyword=tool shape,simulation,shape; section=tool settings,tool shape
-3. page_210_img_0_0.jpeg | score=1.508 | stage=0.925 | page=1.00; keyword=tool shape,shape; section=tool settings,tool shape
-4. page_210_img_2_0.jpeg | score=1.504 | stage=0.925 | page=1.00; keyword=tool shape,shape; section=tool settings,tool shape
-5. page_206_img_0_0.jpeg | score=1.369 | stage=0.700 | page=1.00; section=tool settings
-6. page_210_img_1_0.jpeg | score=1.263 | stage=0.925 | page=1.00; keyword=tool shape,shape; section=tool settings,tool shape
-7. page_205_img_1_0.jpeg | score=1.066 | stage=0.550 | page=0.70; section=tool settings
-8. page_259_img_1_0.jpeg | score=0.706 | stage=0.000
-9. page_226_img_2_0.jpeg | score=0.706 | stage=0.013 | keyword=shape
-10. page_236_img_0_0.jpeg | score=0.691 | stage=0.013 | keyword=shape</t>
+          <t xml:space="preserve">1. page_209_img_0_0.jpeg | score=1.468 | stage=0.700 | page=1.00; section=tool settings
+2. page_208_img_0_0.jpeg | score=1.449 | stage=0.700 | page=1.00; section=tool settings
+3. page_210_img_0_0.jpeg | score=1.376 | stage=0.700 | page=1.00; section=tool settings
+4. page_210_img_1_0.jpeg | score=1.372 | stage=0.700 | page=1.00; section=tool settings
+5. page_210_img_2_0.jpeg | score=1.346 | stage=0.700 | page=1.00; section=tool settings
+6. page_206_img_0_0.jpeg | score=1.313 | stage=0.700 | page=1.00; section=tool settings
+7. page_205_img_1_0.jpeg | score=1.242 | stage=0.700 | page=1.00; section=tool settings
+8. page_224_img_0_0.jpeg | score=1.187 | stage=0.500 | page=1.00
+9. page_245_img_0_0.jpeg | score=1.146 | stage=0.500 | page=1.00
+10. page_235_img_1_0.jpeg | score=1.133 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5954,12 @@
       </c>
       <c r="K66" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L66" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="M66" s="0" t="inlineStr">
@@ -5979,28 +5967,24 @@
           <t>page_226_img_0_0.jpeg</t>
         </is>
       </c>
-      <c r="N66" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="N66" s="0"/>
       <c r="O66" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_224_img_0_0.jpeg | score=1.398 | stage=0.671 | page=1.00; keyword=zone,y,z; section=safety settings
-2. page_225_img_0_0.jpeg | score=1.312 | stage=0.696 | page=1.00; keyword=zone,x,y,z; section=safety settings
-3. page_226_img_0_0.jpeg | score=1.159 | stage=0.671 | page=1.00; keyword=y,z,radius; section=safety settings
-4. page_223_img_0_0.jpeg | score=1.080 | stage=0.646 | page=1.00; keyword=y; section=safety settings
-5. page_226_img_2_0.jpeg | score=0.996 | stage=0.671 | page=1.00; keyword=y,z,radius; section=safety settings
-6. page_239_img_0_0.jpeg | score=0.927 | stage=0.171 | keyword=zone,y,z; section=safety settings
-7. page_240_img_0_0.jpeg | score=0.923 | stage=0.146 | keyword=y; section=safety settings
-8. page_241_img_0_0.jpeg | score=0.872 | stage=0.183 | keyword=zone,y,z,robot parameter; section=safety settings
-9. page_228_img_0_0.jpeg | score=0.861 | stage=0.817 | page=1.00; keyword=center position,x,y,z; section=safety settings,center position
-10. page_228_img_2_0.jpeg | score=0.855 | stage=0.817 | page=1.00; keyword=center position,x,y,z; section=safety settings,center position</t>
+          <t xml:space="preserve">1. page_241_img_0_0.jpeg | score=1.415 | stage=0.658 | page=1.00; keyword=x,y; section=safety settings
+2. page_240_img_0_0.jpeg | score=1.411 | stage=0.658 | page=1.00; keyword=x,y; section=safety settings
+3. page_224_img_0_0.jpeg | score=1.406 | stage=0.658 | page=1.00; keyword=x,y; section=safety settings
+4. page_225_img_0_0.jpeg | score=1.389 | stage=0.658 | page=1.00; keyword=x,y; section=safety settings
+5. page_243_img_0_0.jpeg | score=1.345 | stage=0.658 | page=1.00; keyword=x,y; section=safety settings
+6. page_242_img_0_0.jpeg | score=1.331 | stage=0.658 | page=1.00; keyword=x,y; section=safety settings
+7. page_236_img_0_0.jpeg | score=1.295 | stage=0.658 | page=1.00; keyword=x,y; section=safety settings
+8. page_244_img_0_0.jpeg | score=1.283 | stage=0.658 | page=1.00; keyword=x,y; section=safety settings
+9. page_227_img_0_0.jpeg | score=1.248 | stage=0.683 | page=1.00; keyword=zone,x,y,z; section=safety settings
+10. page_245_img_0_0.jpeg | score=1.240 | stage=0.658 | page=1.00; keyword=x,y; section=safety settings</t>
         </is>
       </c>
     </row>
@@ -6068,26 +6052,26 @@
       </c>
       <c r="N67" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O67" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
       <c r="P67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_239_img_0_0.jpeg | score=0.885 | stage=0.000
-2. page_237_img_0_0.jpeg | score=0.861 | stage=0.000
-3. page_240_img_0_0.jpeg | score=0.835 | stage=0.000
-4. page_238_img_0_0.jpeg | score=0.816 | stage=0.000
-5. page_230_img_0_0.jpeg | score=0.809 | stage=0.000
-6. page_230_img_1_0.jpeg | score=0.758 | stage=0.000
-7. page_232_img_0_0.jpeg | score=0.741 | stage=0.000
-8. page_236_img_0_0.jpeg | score=0.736 | stage=0.000
-9. page_241_img_0_0.jpeg | score=0.735 | stage=0.000
-10. page_231_img_1_0.jpeg | score=0.719 | stage=0.000</t>
+          <t xml:space="preserve">1. page_240_img_0_0.jpeg | score=0.849 | stage=0.000 | 
+2. page_241_img_0_0.jpeg | score=0.837 | stage=0.000 | 
+3. page_237_img_0_0.jpeg | score=0.823 | stage=0.000 | 
+4. page_236_img_0_0.jpeg | score=0.811 | stage=0.000 | 
+5. page_232_img_0_0.jpeg | score=0.756 | stage=0.000 | 
+6. page_244_img_0_0.jpeg | score=0.737 | stage=0.000 | 
+7. page_242_img_0_0.jpeg | score=0.719 | stage=0.000 | 
+8. page_243_img_0_0.jpeg | score=0.715 | stage=0.000 | 
+9. page_230_img_0_0.jpeg | score=0.713 | stage=0.000 | 
+10. page_231_img_1_0.jpeg | score=0.709 | stage=0.000 | </t>
         </is>
       </c>
     </row>
@@ -6169,16 +6153,16 @@
       </c>
       <c r="P68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_243_img_0_0.jpeg | score=1.607 | stage=0.938 | page=1.00; keyword=collision sensitivity,reduction zone,sensitivity; section=safety settings,collision sensitivity reduction zone
-2. page_242_img_0_0.jpeg | score=1.464 | stage=0.712 | page=1.00; keyword=robot parameter; section=safety settings
-3. page_243_img_1_0.jpeg | score=1.405 | stage=0.938 | page=1.00; keyword=collision sensitivity,reduction zone,sensitivity; section=safety settings,collision sensitivity reduction zone
-4. page_244_img_0_0.jpeg | score=1.384 | stage=0.700 | page=1.00; section=safety settings
-5. page_241_img_0_0.jpeg | score=1.322 | stage=0.712 | page=1.00; keyword=robot parameter; section=safety settings
-6. page_240_img_0_0.jpeg | score=1.154 | stage=0.700 | page=1.00; section=safety settings
-7. page_239_img_0_0.jpeg | score=0.947 | stage=0.700 | page=1.00; section=safety settings
-8. page_245_img_0_0.jpeg | score=0.935 | stage=0.712 | page=1.00; keyword=robot parameter; section=safety settings
-9. page_295_img_0_0.jpeg | score=0.732 | stage=0.038 | keyword=collision sensitivity,sensitivity,robot parameter
-10. page_284_img_0_0.jpeg | score=0.731 | stage=0.038 | keyword=collision sensitivity,sensitivity,robot parameter</t>
+          <t xml:space="preserve">1. page_243_img_0_0.jpeg | score=1.477 | stage=0.700 | page=1.00; section=safety settings
+2. page_242_img_0_0.jpeg | score=1.412 | stage=0.700 | page=1.00; section=safety settings
+3. page_244_img_0_0.jpeg | score=1.367 | stage=0.700 | page=1.00; section=safety settings
+4. page_240_img_0_0.jpeg | score=1.133 | stage=0.700 | page=1.00; section=safety settings
+5. page_243_img_1_0.jpeg | score=1.119 | stage=0.700 | page=1.00; section=safety settings
+6. page_241_img_0_0.jpeg | score=1.111 | stage=0.700 | page=1.00; section=safety settings
+7. page_245_img_0_0.jpeg | score=1.029 | stage=0.700 | page=1.00; section=safety settings
+8. page_239_img_0_0.jpeg | score=0.810 | stage=0.700 | page=1.00; section=safety settings
+9. page_224_img_0_0.jpeg | score=0.753 | stage=0.700 | page=1.00; section=safety settings
+10. page_225_img_0_0.jpeg | score=0.740 | stage=0.700 | page=1.00; section=safety settings</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6234,7 @@
       </c>
       <c r="N69" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O69" s="0" t="inlineStr">
@@ -6260,16 +6244,16 @@
       </c>
       <c r="P69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_246_img_0_0.jpeg | score=1.601 | stage=0.950 | page=1.00; keyword=safety setting review,robot parameter,safety settings,review; section=safety setting review
-2. page_247_img_0_0.jpeg | score=1.578 | stage=0.938 | page=1.00; keyword=safety setting review,robot parameter,review; section=safety setting review
-3. page_247_img_1_0.jpeg | score=1.572 | stage=0.938 | page=1.00; keyword=safety setting review,robot parameter,review; section=safety setting review
-4. page_248_img_0_0.jpeg | score=1.244 | stage=0.925 | page=1.00; keyword=safety setting review,review; section=safety setting review
-5. page_245_img_0_0.jpeg | score=1.224 | stage=0.525 | page=1.00; keyword=robot parameter,safety settings
-6. page_244_img_0_0.jpeg | score=0.924 | stage=0.512 | page=1.00; keyword=safety settings
-7. page_223_img_0_0.jpeg | score=0.863 | stage=0.025 | keyword=safety settings,save
-8. page_208_img_0_0.jpeg | score=0.797 | stage=0.000
-9. page_224_img_0_0.jpeg | score=0.774 | stage=0.025 | keyword=safety settings,save
-10. page_251_img_2_0.jpeg | score=0.768 | stage=0.500 | page=1.00</t>
+          <t xml:space="preserve">1. page_248_img_0_0.jpeg | score=1.589 | stage=0.938 | page=1.00; keyword=safety setting review,robot parameter,review; section=safety setting review
+2. page_246_img_0_0.jpeg | score=1.379 | stage=0.938 | page=1.00; keyword=safety setting review,robot parameter,review; section=safety setting review
+3. page_247_img_0_0.jpeg | score=1.361 | stage=0.938 | page=1.00; keyword=safety setting review,robot parameter,review; section=safety setting review
+4. page_247_img_1_0.jpeg | score=1.333 | stage=0.925 | page=1.00; keyword=safety setting review,review; section=safety setting review
+5. page_249_img_0_0.jpeg | score=1.321 | stage=0.500 | page=1.00
+6. page_220_img_0_0.jpeg | score=1.300 | stage=0.512 | page=1.00; keyword=safety settings
+7. page_240_img_0_0.jpeg | score=1.279 | stage=0.512 | page=1.00; keyword=safety settings
+8. page_241_img_0_0.jpeg | score=1.271 | stage=0.512 | page=1.00; keyword=safety settings
+9. page_245_img_0_0.jpeg | score=1.233 | stage=0.512 | page=1.00; keyword=safety settings
+10. page_224_img_0_0.jpeg | score=1.188 | stage=0.512 | page=1.00; keyword=safety settings</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6295,7 @@
       </c>
       <c r="H70" s="0" t="inlineStr">
         <is>
-          <t>0.1789</t>
+          <t>0.1788</t>
         </is>
       </c>
       <c r="I70" s="0" t="inlineStr">
@@ -6341,7 +6325,7 @@
       </c>
       <c r="N70" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O70" s="0" t="inlineStr">
@@ -6351,16 +6335,16 @@
       </c>
       <c r="P70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_254_img_0_0.jpeg | score=1.440 | stage=0.712 | page=1.00; keyword=remote control; section=remote control
-2. page_249_img_0_0.jpeg | score=1.407 | stage=0.712 | page=1.00; keyword=remote control; section=remote control
-3. page_251_img_2_0.jpeg | score=1.392 | stage=0.712 | page=1.00; keyword=remote control; section=remote control
-4. page_251_img_1_0.jpeg | score=1.376 | stage=0.712 | page=1.00; keyword=remote control; section=remote control
-5. page_257_img_0_0.jpeg | score=1.336 | stage=0.738 | page=1.00; keyword=remote control,task,servo on; section=remote control
-6. page_249_img_2_0.jpeg | score=1.249 | stage=0.712 | page=1.00; keyword=remote control; section=remote control
-7. page_256_img_0_0.jpeg | score=1.248 | stage=0.500 | page=1.00
-8. page_249_img_3_0.png | score=1.226 | stage=0.712 | page=1.00; keyword=remote control; section=remote control
-9. page_258_img_0_0.jpeg | score=1.209 | stage=0.712 | page=1.00; keyword=remote control; section=remote control
-10. page_248_img_0_0.jpeg | score=1.114 | stage=0.712 | page=1.00; keyword=remote control; section=remote control</t>
+          <t xml:space="preserve">1. page_251_img_2_0.jpeg | score=1.489 | stage=0.712 | page=1.00; keyword=remote control; section=remote control
+2. page_252_img_0_0.jpeg | score=1.464 | stage=0.712 | page=1.00; keyword=remote control; section=remote control
+3. page_249_img_0_0.jpeg | score=1.383 | stage=0.712 | page=1.00; keyword=remote control; section=remote control
+4. page_249_img_2_0.jpeg | score=1.377 | stage=0.712 | page=1.00; keyword=remote control; section=remote control
+5. page_252_img_2_0.jpeg | score=1.349 | stage=0.500 | page=1.00
+6. page_257_img_0_0.jpeg | score=1.334 | stage=0.712 | page=1.00; keyword=remote control; section=remote control
+7. page_256_img_0_0.jpeg | score=1.332 | stage=0.500 | page=1.00
+8. page_251_img_1_0.jpeg | score=1.292 | stage=0.712 | page=1.00; keyword=remote control; section=remote control
+9. page_259_img_1_0.jpeg | score=1.221 | stage=0.500 | page=1.00
+10. page_258_img_0_0.jpeg | score=1.207 | stage=0.500 | page=1.00</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6416,7 @@
       </c>
       <c r="N71" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O71" s="0" t="inlineStr">
@@ -6442,16 +6426,16 @@
       </c>
       <c r="P71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. page_334_img_0_0.jpeg | score=1.544 | stage=0.817 | page=1.00; keyword=i,o overview,high,low; section=i,o overview
-2. page_336_img_0_0.jpeg | score=1.482 | stage=0.792 | page=1.00; keyword=i,o overview; section=i,o overview
-3. page_335_img_1_0.jpeg | score=1.434 | stage=0.792 | page=1.00; keyword=i,o overview; section=i,o overview
-4. page_335_img_2_0.jpeg | score=1.430 | stage=0.792 | page=1.00; keyword=i,o overview; section=i,o overview
-5. page_333_img_0_0.jpeg | score=1.392 | stage=0.792 | page=1.00; keyword=i,o overview; section=i,o overview
-6. page_335_img_0_0.jpeg | score=1.238 | stage=0.792 | page=1.00; keyword=i,o overview; section=i,o overview
-7. page_332_img_0_0.jpeg | score=1.150 | stage=0.792 | page=1.00; keyword=i,o overview; section=i,o overview
-8. page_328_img_1_0.jpeg | score=0.855 | stage=0.496 | page=0.70; keyword=i; section=i
-9. page_328_img_2_0.jpeg | score=0.835 | stage=0.496 | page=0.70; keyword=i; section=i
-10. page_139_img_0_0.jpeg | score=0.743 | stage=0.146 | keyword=i; section=i</t>
+          <t xml:space="preserve">1. page_336_img_0_0.jpeg | score=1.513 | stage=0.792 | page=1.00; keyword=i,o overview; section=i,o overview
+2. page_334_img_0_0.jpeg | score=1.472 | stage=0.792 | page=1.00; keyword=i,o overview; section=i,o overview
+3. page_333_img_0_0.jpeg | score=1.419 | stage=0.792 | page=1.00; keyword=i,o overview; section=i,o overview
+4. page_335_img_1_0.jpeg | score=1.321 | stage=0.792 | page=1.00; keyword=i,o overview; section=i,o overview
+5. page_335_img_2_0.jpeg | score=1.309 | stage=0.792 | page=1.00; keyword=i,o overview; section=i,o overview
+6. page_335_img_0_0.jpeg | score=1.282 | stage=0.792 | page=1.00; keyword=i,o overview; section=i,o overview
+7. page_332_img_0_0.jpeg | score=1.176 | stage=0.792 | page=1.00; keyword=i,o overview; section=i,o overview
+8. page_338_img_0_0.jpeg | score=1.086 | stage=0.646 | page=1.00; keyword=i; section=i
+9. page_139_img_0_0.jpeg | score=0.834 | stage=0.146 | keyword=i; section=i
+10. page_140_img_0_0.jpeg | score=0.826 | stage=0.146 | keyword=i; section=i</t>
         </is>
       </c>
     </row>
